--- a/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
+++ b/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9227" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9684" uniqueCount="1470">
   <si>
     <t>INVESTMENT ARCHETYPES  ·  CROSS-COHORT SUMMARY</t>
   </si>
   <si>
-    <t>2026-06-25  ·  18,680 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  246 backlog-inflect  ·  869 triple-lens</t>
+    <t>2026-06-25  ·  18,680 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  246 backlog-inflect  ·  1466 triple-lens</t>
   </si>
   <si>
     <t>Each archetype is a structurally distinct setup. A name may appear in multiple cohorts — the Triple-Lens Conviction block at the end shows names with ≥ 3 archetype overlaps. Segment and backlog data come from full SEC EDGAR XBRL dimensional parsing (edgartools); fundamentals from Lindy multi-method ROIC reconciliation. Every cohort row shows the specific segment name, backlog concept, and inflection magnitude that drove the flag.</t>
@@ -4105,18 +4105,69 @@
     <t>Scandinavian Investment Gr</t>
   </si>
   <si>
-    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  0 NAMES</t>
+    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  3725 NAMES</t>
+  </si>
+  <si>
+    <t>G0I.SI</t>
+  </si>
+  <si>
+    <t>Nam Lee Metal</t>
+  </si>
+  <si>
+    <t>0725.HK</t>
+  </si>
+  <si>
+    <t>PERENNIAL INT'L</t>
+  </si>
+  <si>
+    <t>HLD.F</t>
+  </si>
+  <si>
+    <t>HENDERSON LAND DEVMT CO. L</t>
+  </si>
+  <si>
+    <t>CNGKY</t>
+  </si>
+  <si>
+    <t>MTLHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi Chemical Group </t>
+  </si>
+  <si>
+    <t>BST.MI</t>
+  </si>
+  <si>
+    <t>BANCA SISTEMA</t>
+  </si>
+  <si>
+    <t>SOFT.BR</t>
+  </si>
+  <si>
+    <t>SOFTIMAT</t>
+  </si>
+  <si>
+    <t>KUH.SI</t>
+  </si>
+  <si>
+    <t>$ TSH</t>
+  </si>
+  <si>
+    <t>BLU.SI</t>
+  </si>
+  <si>
+    <t>GRP</t>
+  </si>
+  <si>
+    <t>0194.HK</t>
+  </si>
+  <si>
+    <t>LIU CHONG HING</t>
   </si>
   <si>
     <t>25. P-FORMATION — SHORT-COVER FADE (BEARISH REVERSAL CANDIDATE)  ·  1916 NAMES</t>
   </si>
   <si>
-    <t>G0I.SI</t>
-  </si>
-  <si>
-    <t>Nam Lee Metal</t>
-  </si>
-  <si>
     <t>CIADY</t>
   </si>
   <si>
@@ -4246,7 +4297,7 @@
     <t>SILVER BULL RESOURCES INC</t>
   </si>
   <si>
-    <t>26. TRIPLE-LENS CONVICTION — PASSES ≥ 3 BUY-SIDE ARCHETYPES  ·  869 NAMES</t>
+    <t>26. TRIPLE-LENS CONVICTION — PASSES ≥ 3 BUY-SIDE ARCHETYPES  ·  1466 NAMES</t>
   </si>
   <si>
     <t>AMD</t>
@@ -4258,6 +4309,60 @@
     <t>Other Countries</t>
   </si>
   <si>
+    <t>7812.T</t>
+  </si>
+  <si>
+    <t>CRESTEC INC</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Bloom Energy Corporation</t>
+  </si>
+  <si>
+    <t>Product revenue</t>
+  </si>
+  <si>
+    <t>7516.T</t>
+  </si>
+  <si>
+    <t>KOHNAN SHOJI</t>
+  </si>
+  <si>
+    <t>WTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watts Water Technologies, </t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>Cadre Holdings Inc. Common</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>General Dynamics Corporati</t>
+  </si>
+  <si>
+    <t>North America:</t>
+  </si>
+  <si>
+    <t>Contracts Accounte</t>
+  </si>
+  <si>
+    <t>Grow Brands</t>
+  </si>
+  <si>
+    <t>Digital and Licens</t>
+  </si>
+  <si>
     <t>ATI</t>
   </si>
   <si>
@@ -4270,19 +4375,10 @@
     <t>Medical</t>
   </si>
   <si>
-    <t>IEX</t>
-  </si>
-  <si>
-    <t>IDEX Corporation</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>WESCO International, Inc.</t>
-  </si>
-  <si>
-    <t>CSS</t>
+    <t>Ligand Pharmaceuticals Inc</t>
+  </si>
+  <si>
+    <t>Development and Li</t>
   </si>
   <si>
     <t>EHC</t>
@@ -4297,24 +4393,30 @@
     <t>Other income</t>
   </si>
   <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>Cadre Holdings Inc. Common</t>
-  </si>
-  <si>
-    <t>Grow Brands</t>
-  </si>
-  <si>
-    <t>Digital and Licens</t>
-  </si>
-  <si>
     <t>CIEN</t>
   </si>
   <si>
     <t>Ciena Corporation</t>
   </si>
   <si>
+    <t>3421.T</t>
+  </si>
+  <si>
+    <t>INABA SEISAKUSHO</t>
+  </si>
+  <si>
+    <t>OVV</t>
+  </si>
+  <si>
+    <t>Ovintiv Inc. (DE)</t>
+  </si>
+  <si>
+    <t>Product and Servic</t>
+  </si>
+  <si>
+    <t>First Major Custom</t>
+  </si>
+  <si>
     <t>ECL</t>
   </si>
   <si>
@@ -4322,39 +4424,6 @@
   </si>
   <si>
     <t>India, Middle East</t>
-  </si>
-  <si>
-    <t>GGG</t>
-  </si>
-  <si>
-    <t>Graco Inc.</t>
-  </si>
-  <si>
-    <t>JBI</t>
-  </si>
-  <si>
-    <t>Janus International Group,</t>
-  </si>
-  <si>
-    <t>Product revenues</t>
-  </si>
-  <si>
-    <t>Service revenues</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>GE Aerospace</t>
-  </si>
-  <si>
-    <t>Equity method inve</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>Toyota Motor Corporation</t>
   </si>
 </sst>
 </file>
@@ -4794,7 +4863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V685"/>
+  <dimension ref="A1:V710"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -44500,106 +44569,216 @@
         <v>25</v>
       </c>
     </row>
-    <row r="631" spans="1:22" ht="22" customHeight="1">
-      <c r="A631" s="4" t="s">
-        <v>1364</v>
-      </c>
-      <c r="B631" s="4"/>
-      <c r="C631" s="4"/>
-      <c r="D631" s="4"/>
-      <c r="E631" s="4"/>
-      <c r="F631" s="4"/>
-      <c r="G631" s="4"/>
-      <c r="H631" s="4"/>
-      <c r="I631" s="4"/>
-      <c r="J631" s="4"/>
-      <c r="K631" s="4"/>
-      <c r="L631" s="4"/>
-      <c r="M631" s="4"/>
-      <c r="N631" s="4"/>
-      <c r="O631" s="4"/>
-      <c r="P631" s="4"/>
-      <c r="Q631" s="4"/>
-      <c r="R631" s="4"/>
-      <c r="S631" s="4"/>
-      <c r="T631" s="4"/>
-      <c r="U631" s="4"/>
-      <c r="V631" s="4"/>
-    </row>
-    <row r="632" spans="1:22" ht="22" customHeight="1">
-      <c r="A632" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B632" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C632" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D632" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E632" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H632" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I632" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J632" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K632" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L632" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N632" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O632" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P632" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q632" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R632" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S632" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T632" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="U632" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="V632" s="5" t="s">
-        <v>25</v>
+    <row r="630" spans="1:22">
+      <c r="A630" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B630" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C630" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D630" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E630" s="8">
+        <v>1323.101696</v>
+      </c>
+      <c r="F630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J630" s="11">
+        <v>7.883643546731506</v>
+      </c>
+      <c r="K630" s="9">
+        <v>249.200811242857</v>
+      </c>
+      <c r="L630" s="9">
+        <v>-69.09999999999999</v>
+      </c>
+      <c r="M630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U630" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V630" s="11">
+        <v>102.5556745182013</v>
+      </c>
+    </row>
+    <row r="631" spans="1:22">
+      <c r="A631" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B631" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C631" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D631" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E631" s="8">
+        <v>2951.459328</v>
+      </c>
+      <c r="F631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J631" s="11">
+        <v>4.728569550991809</v>
+      </c>
+      <c r="K631" s="9">
+        <v>38.31373169442503</v>
+      </c>
+      <c r="L631" s="9">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="M631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U631" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V631" s="11">
+        <v>101.1857601713062</v>
+      </c>
+    </row>
+    <row r="632" spans="1:22">
+      <c r="A632" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B632" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C632" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D632" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E632" s="8">
+        <v>530.443712</v>
+      </c>
+      <c r="F632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J632" s="11">
+        <v>9.801189239523584E-05</v>
+      </c>
+      <c r="K632" s="9">
+        <v>573535.765607492</v>
+      </c>
+      <c r="L632" s="9">
+        <v>30.8</v>
+      </c>
+      <c r="M632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U632" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V632" s="11">
+        <v>100.5754817987152</v>
       </c>
     </row>
     <row r="633" spans="1:22">
       <c r="A633" s="6" t="s">
-        <v>426</v>
+        <v>595</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>427</v>
+        <v>596</v>
       </c>
       <c r="C633" s="7" t="s">
         <v>428</v>
@@ -44608,7 +44787,7 @@
         <v>29</v>
       </c>
       <c r="E633" s="8">
-        <v>64832.155648</v>
+        <v>6060.96128</v>
       </c>
       <c r="F633" s="10" t="s">
         <v>30</v>
@@ -44623,13 +44802,13 @@
         <v>30</v>
       </c>
       <c r="J633" s="11">
-        <v>-10.51957954924859</v>
-      </c>
-      <c r="K633" s="10" t="s">
-        <v>30</v>
+        <v>9.016844571083071</v>
+      </c>
+      <c r="K633" s="9">
+        <v>61.09179354467019</v>
       </c>
       <c r="L633" s="9">
-        <v>19</v>
+        <v>-2.9</v>
       </c>
       <c r="M633" s="10" t="s">
         <v>30</v>
@@ -44659,15 +44838,15 @@
         <v>30</v>
       </c>
       <c r="V633" s="11">
-        <v>105.100374732334</v>
+        <v>100.3410064239829</v>
       </c>
     </row>
     <row r="634" spans="1:22">
       <c r="A634" s="6" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C634" s="7" t="s">
         <v>428</v>
@@ -44676,7 +44855,7 @@
         <v>29</v>
       </c>
       <c r="E634" s="8">
-        <v>508393.324544</v>
+        <v>20998.670336</v>
       </c>
       <c r="F634" s="10" t="s">
         <v>30</v>
@@ -44691,13 +44870,13 @@
         <v>30</v>
       </c>
       <c r="J634" s="11">
-        <v>8.71738713606149</v>
-      </c>
-      <c r="K634" s="10" t="s">
-        <v>30</v>
+        <v>2.810972482219976</v>
+      </c>
+      <c r="K634" s="9">
+        <v>47.64289532584622</v>
       </c>
       <c r="L634" s="9">
-        <v>19</v>
+        <v>38.4</v>
       </c>
       <c r="M634" s="10" t="s">
         <v>30</v>
@@ -44727,24 +44906,24 @@
         <v>30</v>
       </c>
       <c r="V634" s="11">
-        <v>102.3115631691649</v>
+        <v>100.1423982869379</v>
       </c>
     </row>
     <row r="635" spans="1:22">
       <c r="A635" s="6" t="s">
-        <v>1365</v>
+        <v>460</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1366</v>
+        <v>461</v>
       </c>
       <c r="C635" s="7" t="s">
-        <v>253</v>
+        <v>462</v>
       </c>
       <c r="D635" s="7" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="E635" s="8">
-        <v>162.177776</v>
+        <v>2914.04288</v>
       </c>
       <c r="F635" s="10" t="s">
         <v>30</v>
@@ -44759,13 +44938,13 @@
         <v>30</v>
       </c>
       <c r="J635" s="11">
-        <v>4.465099482461184</v>
+        <v>1.496271937169841</v>
       </c>
       <c r="K635" s="9">
-        <v>-3.02114452475905</v>
+        <v>45.48663443140548</v>
       </c>
       <c r="L635" s="9">
-        <v>28</v>
+        <v>-15</v>
       </c>
       <c r="M635" s="10" t="s">
         <v>30</v>
@@ -44795,12 +44974,12 @@
         <v>30</v>
       </c>
       <c r="V635" s="11">
-        <v>98.71172376873662</v>
+        <v>100.0856531049251</v>
       </c>
     </row>
     <row r="636" spans="1:22">
       <c r="A636" s="6" t="s">
-        <v>1350</v>
+        <v>463</v>
       </c>
       <c r="B636" s="7" t="s">
         <v>464</v>
@@ -44812,7 +44991,7 @@
         <v>29</v>
       </c>
       <c r="E636" s="8">
-        <v>38709.911552</v>
+        <v>11987.337216</v>
       </c>
       <c r="F636" s="10" t="s">
         <v>30</v>
@@ -44827,10 +45006,10 @@
         <v>30</v>
       </c>
       <c r="J636" s="11">
-        <v>7.8300140269052</v>
+        <v>5.991768553035233</v>
       </c>
       <c r="K636" s="9">
-        <v>20.04622268789213</v>
+        <v>64.73393491961309</v>
       </c>
       <c r="L636" s="9">
         <v>5.4</v>
@@ -44863,24 +45042,24 @@
         <v>30</v>
       </c>
       <c r="V636" s="11">
-        <v>97.76498929336188</v>
+        <v>100.0567451820128</v>
       </c>
     </row>
     <row r="637" spans="1:22">
       <c r="A637" s="6" t="s">
-        <v>1367</v>
+        <v>468</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1368</v>
+        <v>469</v>
       </c>
       <c r="C637" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D637" s="7" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E637" s="8">
-        <v>8219.0208</v>
+        <v>371.099648</v>
       </c>
       <c r="F637" s="10" t="s">
         <v>30</v>
@@ -44895,13 +45074,13 @@
         <v>30</v>
       </c>
       <c r="J637" s="11">
-        <v>1.485994891319154</v>
+        <v>2.379639893114472</v>
       </c>
       <c r="K637" s="9">
-        <v>55.59947734893188</v>
+        <v>67.44334071693865</v>
       </c>
       <c r="L637" s="9">
-        <v>-7.6</v>
+        <v>-4.3</v>
       </c>
       <c r="M637" s="10" t="s">
         <v>30</v>
@@ -44931,92 +45110,92 @@
         <v>30</v>
       </c>
       <c r="V637" s="11">
-        <v>97.04175588865095</v>
+        <v>99.68094218415416</v>
       </c>
     </row>
     <row r="638" spans="1:22">
       <c r="A638" s="6" t="s">
-        <v>1369</v>
+        <v>470</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1370</v>
+        <v>471</v>
       </c>
       <c r="C638" s="7" t="s">
-        <v>28</v>
+        <v>428</v>
       </c>
       <c r="D638" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E638" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F638" s="9">
-        <v>10.83795825108153</v>
-      </c>
-      <c r="G638" s="9">
-        <v>6.40300490933652</v>
-      </c>
-      <c r="H638" s="9">
-        <v>243.2142618781592</v>
-      </c>
-      <c r="I638" s="9">
-        <v>13.64504881992278</v>
-      </c>
-      <c r="J638" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K638" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L638" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M638" s="7" t="s">
-        <v>1371</v>
-      </c>
-      <c r="N638" s="9">
-        <v>37.97959455657402</v>
-      </c>
-      <c r="O638" s="7" t="s">
-        <v>1372</v>
-      </c>
-      <c r="P638" s="9">
-        <v>23.62832373305406</v>
-      </c>
-      <c r="Q638" s="9">
-        <v>6.95427841326001</v>
-      </c>
-      <c r="R638" s="7" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="E638" s="8">
+        <v>19026.651136</v>
+      </c>
+      <c r="F638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J638" s="11">
+        <v>35.45027781537315</v>
+      </c>
+      <c r="K638" s="9">
+        <v>41.61136918635096</v>
+      </c>
+      <c r="L638" s="9">
+        <v>20</v>
+      </c>
+      <c r="M638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q638" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R638" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S638" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T638" s="12" t="s">
-        <v>41</v>
+      <c r="T638" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U638" s="10" t="s">
         <v>30</v>
       </c>
       <c r="V638" s="11">
-        <v>96.01017130620984</v>
+        <v>99.4151498929336</v>
       </c>
     </row>
     <row r="639" spans="1:22">
       <c r="A639" s="6" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="C639" s="7" t="s">
-        <v>585</v>
+        <v>253</v>
       </c>
       <c r="D639" s="7" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="E639" s="8">
-        <v>121887.064064</v>
+        <v>162.177776</v>
       </c>
       <c r="F639" s="10" t="s">
         <v>30</v>
@@ -45031,13 +45210,13 @@
         <v>30</v>
       </c>
       <c r="J639" s="11">
-        <v>5.238151175637653</v>
+        <v>4.465099482461184</v>
       </c>
       <c r="K639" s="9">
-        <v>414.8230582160164</v>
+        <v>-3.02114452475905</v>
       </c>
       <c r="L639" s="9">
-        <v>-14.8</v>
+        <v>28</v>
       </c>
       <c r="M639" s="10" t="s">
         <v>30</v>
@@ -45067,24 +45246,24 @@
         <v>30</v>
       </c>
       <c r="V639" s="11">
-        <v>94.9009635974304</v>
+        <v>98.71172376873662</v>
       </c>
     </row>
     <row r="640" spans="1:22">
       <c r="A640" s="6" t="s">
-        <v>1375</v>
+        <v>606</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1376</v>
+        <v>607</v>
       </c>
       <c r="C640" s="7" t="s">
-        <v>253</v>
+        <v>428</v>
       </c>
       <c r="D640" s="7" t="s">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="E640" s="8">
-        <v>19.9079</v>
+        <v>13279.130624</v>
       </c>
       <c r="F640" s="10" t="s">
         <v>30</v>
@@ -45099,13 +45278,13 @@
         <v>30</v>
       </c>
       <c r="J640" s="11">
-        <v>6.363989581072281</v>
+        <v>6.956134185222065</v>
       </c>
       <c r="K640" s="9">
-        <v>36.86790168726988</v>
+        <v>60.29385557462229</v>
       </c>
       <c r="L640" s="9">
-        <v>-39.1</v>
+        <v>5.1</v>
       </c>
       <c r="M640" s="10" t="s">
         <v>30</v>
@@ -45135,24 +45314,24 @@
         <v>30</v>
       </c>
       <c r="V640" s="11">
-        <v>93.3832976445396</v>
+        <v>98.12392933618844</v>
       </c>
     </row>
     <row r="641" spans="1:22">
       <c r="A641" s="6" t="s">
-        <v>1377</v>
+        <v>1350</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1378</v>
+        <v>464</v>
       </c>
       <c r="C641" s="7" t="s">
-        <v>585</v>
+        <v>428</v>
       </c>
       <c r="D641" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E641" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E641" s="8">
+        <v>38709.911552</v>
       </c>
       <c r="F641" s="10" t="s">
         <v>30</v>
@@ -45166,14 +45345,14 @@
       <c r="I641" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J641" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K641" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L641" s="10" t="s">
-        <v>30</v>
+      <c r="J641" s="11">
+        <v>7.8300140269052</v>
+      </c>
+      <c r="K641" s="9">
+        <v>20.04622268789213</v>
+      </c>
+      <c r="L641" s="9">
+        <v>5.4</v>
       </c>
       <c r="M641" s="10" t="s">
         <v>30</v>
@@ -45203,66 +45382,66 @@
         <v>30</v>
       </c>
       <c r="V641" s="11">
-        <v>92.4183618843683</v>
+        <v>97.76498929336188</v>
       </c>
     </row>
     <row r="642" spans="1:22">
       <c r="A642" s="6" t="s">
-        <v>1379</v>
+        <v>1358</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1380</v>
+        <v>1359</v>
       </c>
       <c r="C642" s="7" t="s">
-        <v>28</v>
+        <v>621</v>
       </c>
       <c r="D642" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E642" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F642" s="9">
-        <v>4.010532285140711</v>
-      </c>
-      <c r="G642" s="9">
-        <v>-10.52463272169449</v>
+        <v>307</v>
+      </c>
+      <c r="E642" s="8">
+        <v>56.32</v>
+      </c>
+      <c r="F642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G642" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="H642" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I642" s="9">
-        <v>2.17980326348073</v>
-      </c>
-      <c r="J642" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K642" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L642" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M642" s="7" t="s">
-        <v>1381</v>
-      </c>
-      <c r="N642" s="9">
-        <v>97.53328112764292</v>
-      </c>
-      <c r="O642" s="7" t="s">
-        <v>1381</v>
-      </c>
-      <c r="P642" s="9">
-        <v>-18.11308349769888</v>
-      </c>
-      <c r="Q642" s="9">
-        <v>4.73279302514139</v>
-      </c>
-      <c r="R642" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S642" s="9">
-        <v>23.19326457048476</v>
+      <c r="I642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J642" s="11">
+        <v>8.054884742041713</v>
+      </c>
+      <c r="K642" s="9">
+        <v>23.49010120738636</v>
+      </c>
+      <c r="L642" s="9">
+        <v>-49.1</v>
+      </c>
+      <c r="M642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R642" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S642" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T642" s="10" t="s">
         <v>30</v>
@@ -45271,24 +45450,24 @@
         <v>30</v>
       </c>
       <c r="V642" s="11">
-        <v>91.65792291220556</v>
+        <v>97.14186295503212</v>
       </c>
     </row>
     <row r="643" spans="1:22">
       <c r="A643" s="6" t="s">
-        <v>1382</v>
+        <v>1361</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1383</v>
+        <v>1362</v>
       </c>
       <c r="C643" s="7" t="s">
-        <v>694</v>
+        <v>603</v>
       </c>
       <c r="D643" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E643" s="10" t="s">
-        <v>30</v>
+        <v>275</v>
+      </c>
+      <c r="E643" s="8">
+        <v>164.210768</v>
       </c>
       <c r="F643" s="10" t="s">
         <v>30</v>
@@ -45305,10 +45484,10 @@
       <c r="J643" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K643" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L643" s="10" t="s">
+      <c r="K643" s="9">
+        <v>5.84614524182725</v>
+      </c>
+      <c r="L643" s="9">
         <v>30</v>
       </c>
       <c r="M643" s="10" t="s">
@@ -45339,24 +45518,24 @@
         <v>30</v>
       </c>
       <c r="V643" s="11">
-        <v>91.22189507494646</v>
+        <v>96.86723768736616</v>
       </c>
     </row>
     <row r="644" spans="1:22">
       <c r="A644" s="6" t="s">
-        <v>1265</v>
+        <v>1366</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1266</v>
+        <v>1367</v>
       </c>
       <c r="C644" s="7" t="s">
-        <v>716</v>
+        <v>428</v>
       </c>
       <c r="D644" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E644" s="10" t="s">
-        <v>30</v>
+        <v>275</v>
+      </c>
+      <c r="E644" s="8">
+        <v>198.958</v>
       </c>
       <c r="F644" s="10" t="s">
         <v>30</v>
@@ -45370,14 +45549,14 @@
       <c r="I644" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J644" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K644" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L644" s="10" t="s">
-        <v>30</v>
+      <c r="J644" s="11">
+        <v>1.588672365456391</v>
+      </c>
+      <c r="K644" s="9">
+        <v>22.26481166879441</v>
+      </c>
+      <c r="L644" s="9">
+        <v>4.100000000000001</v>
       </c>
       <c r="M644" s="10" t="s">
         <v>30</v>
@@ -45407,24 +45586,24 @@
         <v>30</v>
       </c>
       <c r="V644" s="11">
-        <v>90.89908993576016</v>
+        <v>96.49223768736616</v>
       </c>
     </row>
     <row r="645" spans="1:22">
       <c r="A645" s="6" t="s">
-        <v>1384</v>
+        <v>622</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1385</v>
+        <v>623</v>
       </c>
       <c r="C645" s="7" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="D645" s="7" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="E645" s="8">
-        <v>5142.772224</v>
+        <v>18451.95776</v>
       </c>
       <c r="F645" s="10" t="s">
         <v>30</v>
@@ -45439,13 +45618,13 @@
         <v>30</v>
       </c>
       <c r="J645" s="11">
-        <v>5.833631111111111</v>
+        <v>6.91681933355622</v>
       </c>
       <c r="K645" s="9">
-        <v>29.5438901398251</v>
+        <v>46.76874872707274</v>
       </c>
       <c r="L645" s="9">
-        <v>11.6</v>
+        <v>4.2</v>
       </c>
       <c r="M645" s="10" t="s">
         <v>30</v>
@@ -45475,45 +45654,45 @@
         <v>30</v>
       </c>
       <c r="V645" s="11">
-        <v>90.8632226980728</v>
+        <v>96.45931477516061</v>
       </c>
     </row>
     <row r="646" spans="1:22">
       <c r="A646" s="6" t="s">
-        <v>1386</v>
+        <v>1368</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1387</v>
+        <v>1369</v>
       </c>
       <c r="C646" s="7" t="s">
-        <v>28</v>
+        <v>428</v>
       </c>
       <c r="D646" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E646" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F646" s="9">
-        <v>-93.30935942912926</v>
-      </c>
-      <c r="G646" s="9">
-        <v>-126.4891121817485</v>
-      </c>
-      <c r="H646" s="9">
-        <v>200</v>
+        <v>29</v>
+      </c>
+      <c r="E646" s="8">
+        <v>16475.240448</v>
+      </c>
+      <c r="F646" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G646" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H646" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I646" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J646" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K646" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L646" s="10" t="s">
-        <v>30</v>
+      <c r="J646" s="11">
+        <v>34.88730102099494</v>
+      </c>
+      <c r="K646" s="9">
+        <v>48.05544461089251</v>
+      </c>
+      <c r="L646" s="9">
+        <v>20</v>
       </c>
       <c r="M646" s="10" t="s">
         <v>30</v>
@@ -45530,11 +45709,11 @@
       <c r="Q646" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R646" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S646" s="9">
-        <v>11.5193160318741</v>
+      <c r="R646" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S646" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T646" s="10" t="s">
         <v>30</v>
@@ -45543,30 +45722,30 @@
         <v>30</v>
       </c>
       <c r="V646" s="11">
-        <v>90.72805139186296</v>
+        <v>96.3838329764454</v>
       </c>
     </row>
     <row r="647" spans="1:22">
       <c r="A647" s="6" t="s">
-        <v>1388</v>
+        <v>673</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1389</v>
+        <v>674</v>
       </c>
       <c r="C647" s="7" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="D647" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E647" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F647" s="9">
-        <v>9.316775054105381</v>
-      </c>
-      <c r="G647" s="9">
-        <v>6.295029703908479</v>
+        <v>275</v>
+      </c>
+      <c r="E647" s="8">
+        <v>10.837523</v>
+      </c>
+      <c r="F647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G647" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="H647" s="10" t="s">
         <v>30</v>
@@ -45574,32 +45753,32 @@
       <c r="I647" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J647" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K647" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L647" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M647" s="7" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N647" s="9">
-        <v>50.32704593854579</v>
-      </c>
-      <c r="O647" s="7" t="s">
-        <v>1390</v>
-      </c>
-      <c r="P647" s="9">
-        <v>5.584809318653261</v>
-      </c>
-      <c r="Q647" s="9">
-        <v>1.936960230878426</v>
-      </c>
-      <c r="R647" s="7" t="s">
-        <v>46</v>
+      <c r="J647" s="11">
+        <v>6.710392994186637</v>
+      </c>
+      <c r="K647" s="9">
+        <v>67.19785508183006</v>
+      </c>
+      <c r="L647" s="9">
+        <v>-16.8</v>
+      </c>
+      <c r="M647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q647" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R647" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S647" s="10" t="s">
         <v>30</v>
@@ -45611,24 +45790,24 @@
         <v>30</v>
       </c>
       <c r="V647" s="11">
-        <v>89.85599571734474</v>
+        <v>96.24277301927197</v>
       </c>
     </row>
     <row r="648" spans="1:22">
       <c r="A648" s="6" t="s">
-        <v>1391</v>
+        <v>1370</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1392</v>
+        <v>459</v>
       </c>
       <c r="C648" s="7" t="s">
-        <v>603</v>
+        <v>428</v>
       </c>
       <c r="D648" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E648" s="8">
-        <v>199431.70048</v>
+        <v>21751.12192</v>
       </c>
       <c r="F648" s="10" t="s">
         <v>30</v>
@@ -45643,13 +45822,13 @@
         <v>30</v>
       </c>
       <c r="J648" s="11">
-        <v>1.864476361899484</v>
+        <v>2.869497144874218</v>
       </c>
       <c r="K648" s="9">
-        <v>-6.03677845148161</v>
+        <v>45.99475174106329</v>
       </c>
       <c r="L648" s="9">
-        <v>24</v>
+        <v>38.4</v>
       </c>
       <c r="M648" s="10" t="s">
         <v>30</v>
@@ -45679,24 +45858,24 @@
         <v>30</v>
       </c>
       <c r="V648" s="11">
-        <v>89.67264453961455</v>
+        <v>96.232869379015</v>
       </c>
     </row>
     <row r="649" spans="1:22">
       <c r="A649" s="6" t="s">
-        <v>1393</v>
+        <v>1371</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1394</v>
+        <v>1372</v>
       </c>
       <c r="C649" s="7" t="s">
-        <v>694</v>
+        <v>370</v>
       </c>
       <c r="D649" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E649" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E649" s="8">
+        <v>8341.480960000001</v>
       </c>
       <c r="F649" s="10" t="s">
         <v>30</v>
@@ -45710,14 +45889,14 @@
       <c r="I649" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J649" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K649" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L649" s="10" t="s">
-        <v>30</v>
+      <c r="J649" s="11">
+        <v>4.208555568894425</v>
+      </c>
+      <c r="K649" s="9">
+        <v>1349.103947316329</v>
+      </c>
+      <c r="L649" s="9">
+        <v>-10.1</v>
       </c>
       <c r="M649" s="10" t="s">
         <v>30</v>
@@ -45747,24 +45926,24 @@
         <v>30</v>
       </c>
       <c r="V649" s="11">
-        <v>89.61509635974303</v>
+        <v>96.22243040685224</v>
       </c>
     </row>
     <row r="650" spans="1:22">
       <c r="A650" s="6" t="s">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1396</v>
+        <v>1374</v>
       </c>
       <c r="C650" s="7" t="s">
-        <v>503</v>
+        <v>682</v>
       </c>
       <c r="D650" s="7" t="s">
         <v>307</v>
       </c>
       <c r="E650" s="8">
-        <v>2598.57536</v>
+        <v>143.149472</v>
       </c>
       <c r="F650" s="10" t="s">
         <v>30</v>
@@ -45778,14 +45957,14 @@
       <c r="I650" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J650" s="11">
-        <v>7.132551509414774</v>
-      </c>
-      <c r="K650" s="9">
-        <v>6.593439876225101</v>
+      <c r="J650" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K650" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="L650" s="9">
-        <v>12.9</v>
+        <v>56.2</v>
       </c>
       <c r="M650" s="10" t="s">
         <v>30</v>
@@ -45815,24 +45994,24 @@
         <v>30</v>
       </c>
       <c r="V650" s="11">
-        <v>89.59154175588864</v>
+        <v>96.20235546038543</v>
       </c>
     </row>
     <row r="651" spans="1:22">
       <c r="A651" s="6" t="s">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1398</v>
+        <v>1376</v>
       </c>
       <c r="C651" s="7" t="s">
-        <v>716</v>
+        <v>462</v>
       </c>
       <c r="D651" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="E651" s="10" t="s">
-        <v>30</v>
+      <c r="E651" s="8">
+        <v>3.204336</v>
       </c>
       <c r="F651" s="10" t="s">
         <v>30</v>
@@ -45846,14 +46025,14 @@
       <c r="I651" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J651" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K651" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L651" s="10" t="s">
-        <v>30</v>
+      <c r="J651" s="11">
+        <v>2.010385251112524</v>
+      </c>
+      <c r="K651" s="9">
+        <v>47.63857473123917</v>
+      </c>
+      <c r="L651" s="9">
+        <v>-13</v>
       </c>
       <c r="M651" s="10" t="s">
         <v>30</v>
@@ -45883,24 +46062,24 @@
         <v>30</v>
       </c>
       <c r="V651" s="11">
-        <v>89.58859743040685</v>
+        <v>96.16702355460384</v>
       </c>
     </row>
     <row r="652" spans="1:22">
       <c r="A652" s="6" t="s">
-        <v>1284</v>
+        <v>1377</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1285</v>
+        <v>1378</v>
       </c>
       <c r="C652" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D652" s="7" t="s">
         <v>275</v>
       </c>
       <c r="E652" s="8">
-        <v>22.405378</v>
+        <v>7.806566</v>
       </c>
       <c r="F652" s="10" t="s">
         <v>30</v>
@@ -45915,13 +46094,13 @@
         <v>30</v>
       </c>
       <c r="J652" s="11">
-        <v>7.363228016877637</v>
+        <v>4.902122453251511</v>
       </c>
       <c r="K652" s="9">
-        <v>47.73686478308912</v>
+        <v>22.44841073527079</v>
       </c>
       <c r="L652" s="9">
-        <v>-2.1</v>
+        <v>6.1</v>
       </c>
       <c r="M652" s="10" t="s">
         <v>30</v>
@@ -45951,24 +46130,24 @@
         <v>30</v>
       </c>
       <c r="V652" s="11">
-        <v>89.30326552462526</v>
+        <v>96.12285867237688</v>
       </c>
     </row>
     <row r="653" spans="1:22">
       <c r="A653" s="6" t="s">
-        <v>1399</v>
+        <v>1379</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="C653" s="7" t="s">
-        <v>423</v>
+        <v>253</v>
       </c>
       <c r="D653" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E653" s="8">
-        <v>119737.376768</v>
+        <v>13.334579</v>
       </c>
       <c r="F653" s="10" t="s">
         <v>30</v>
@@ -45983,13 +46162,13 @@
         <v>30</v>
       </c>
       <c r="J653" s="11">
-        <v>4.600395254844893</v>
+        <v>0.3422172394980906</v>
       </c>
       <c r="K653" s="9">
-        <v>8.39597909304349</v>
+        <v>15.60791683037012</v>
       </c>
       <c r="L653" s="9">
-        <v>11.6</v>
+        <v>13.8</v>
       </c>
       <c r="M653" s="10" t="s">
         <v>30</v>
@@ -46019,426 +46198,426 @@
         <v>30</v>
       </c>
       <c r="V653" s="11">
-        <v>89.27489293361884</v>
+        <v>96.07226980728051</v>
       </c>
     </row>
     <row r="654" spans="1:22">
       <c r="A654" s="6" t="s">
-        <v>1401</v>
+        <v>1381</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1402</v>
+        <v>1382</v>
       </c>
       <c r="C654" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D654" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E654" s="8">
+        <v>1760.412928</v>
+      </c>
+      <c r="F654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J654" s="11">
+        <v>54.1588989731421</v>
+      </c>
+      <c r="K654" s="9">
+        <v>3.15197367148623</v>
+      </c>
+      <c r="L654" s="9">
+        <v>-12</v>
+      </c>
+      <c r="M654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U654" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V654" s="11">
+        <v>95.77168094218416</v>
+      </c>
+    </row>
+    <row r="656" spans="1:22" ht="22" customHeight="1">
+      <c r="A656" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B656" s="4"/>
+      <c r="C656" s="4"/>
+      <c r="D656" s="4"/>
+      <c r="E656" s="4"/>
+      <c r="F656" s="4"/>
+      <c r="G656" s="4"/>
+      <c r="H656" s="4"/>
+      <c r="I656" s="4"/>
+      <c r="J656" s="4"/>
+      <c r="K656" s="4"/>
+      <c r="L656" s="4"/>
+      <c r="M656" s="4"/>
+      <c r="N656" s="4"/>
+      <c r="O656" s="4"/>
+      <c r="P656" s="4"/>
+      <c r="Q656" s="4"/>
+      <c r="R656" s="4"/>
+      <c r="S656" s="4"/>
+      <c r="T656" s="4"/>
+      <c r="U656" s="4"/>
+      <c r="V656" s="4"/>
+    </row>
+    <row r="657" spans="1:22" ht="22" customHeight="1">
+      <c r="A657" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B657" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E657" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H657" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I657" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J657" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K657" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M657" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N657" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O657" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P657" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q657" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R657" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S657" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T657" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U657" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="V657" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="658" spans="1:22">
+      <c r="A658" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B658" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C658" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D658" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E658" s="8">
+        <v>64832.155648</v>
+      </c>
+      <c r="F658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J658" s="11">
+        <v>-10.51957954924859</v>
+      </c>
+      <c r="K658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L658" s="9">
+        <v>19</v>
+      </c>
+      <c r="M658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U658" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V658" s="11">
+        <v>105.100374732334</v>
+      </c>
+    </row>
+    <row r="659" spans="1:22">
+      <c r="A659" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B659" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C659" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D659" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E659" s="8">
+        <v>508393.324544</v>
+      </c>
+      <c r="F659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J659" s="11">
+        <v>8.71738713606149</v>
+      </c>
+      <c r="K659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L659" s="9">
+        <v>19</v>
+      </c>
+      <c r="M659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U659" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V659" s="11">
+        <v>102.3115631691649</v>
+      </c>
+    </row>
+    <row r="660" spans="1:22">
+      <c r="A660" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C660" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D660" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E660" s="8">
+        <v>162.177776</v>
+      </c>
+      <c r="F660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J660" s="11">
+        <v>4.465099482461184</v>
+      </c>
+      <c r="K660" s="9">
+        <v>-3.02114452475905</v>
+      </c>
+      <c r="L660" s="9">
         <v>28</v>
       </c>
-      <c r="D654" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F654" s="9">
-        <v>14.14764495775639</v>
-      </c>
-      <c r="G654" s="9">
-        <v>-29.81694995520391</v>
-      </c>
-      <c r="H654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M654" s="7" t="s">
-        <v>1403</v>
-      </c>
-      <c r="N654" s="9">
-        <v>59.53168685927307</v>
-      </c>
-      <c r="O654" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="P654" s="9">
-        <v>9.249709639953551</v>
-      </c>
-      <c r="Q654" s="9">
-        <v>2.330235344616782</v>
-      </c>
-      <c r="R654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U654" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V654" s="11">
-        <v>89.22243040685224</v>
-      </c>
-    </row>
-    <row r="655" spans="1:22">
-      <c r="A655" s="6" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B655" s="7" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C655" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="D655" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E655" s="8">
-        <v>14.921701</v>
-      </c>
-      <c r="F655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J655" s="11">
-        <v>19.76369851213782</v>
-      </c>
-      <c r="K655" s="9">
-        <v>43.7701438998141</v>
-      </c>
-      <c r="L655" s="9">
-        <v>15</v>
-      </c>
-      <c r="M655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U655" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V655" s="11">
-        <v>89.15792291220556</v>
-      </c>
-    </row>
-    <row r="656" spans="1:22">
-      <c r="A656" s="6" t="s">
-        <v>1406</v>
-      </c>
-      <c r="B656" s="7" t="s">
-        <v>1407</v>
-      </c>
-      <c r="C656" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="D656" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U656" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V656" s="11">
-        <v>89.12125267665952</v>
-      </c>
-    </row>
-    <row r="657" spans="1:22">
-      <c r="A657" s="6" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B657" s="7" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C657" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D657" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E657" s="8">
-        <v>28.096942</v>
-      </c>
-      <c r="F657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J657" s="11">
-        <v>-87.84552340059</v>
-      </c>
-      <c r="K657" s="9">
-        <v>33.56394087299607</v>
-      </c>
-      <c r="L657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U657" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V657" s="11">
-        <v>89.01017130620986</v>
-      </c>
-    </row>
-    <row r="659" spans="1:22" ht="22" customHeight="1">
-      <c r="A659" s="4" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B659" s="4"/>
-      <c r="C659" s="4"/>
-      <c r="D659" s="4"/>
-      <c r="E659" s="4"/>
-      <c r="F659" s="4"/>
-      <c r="G659" s="4"/>
-      <c r="H659" s="4"/>
-      <c r="I659" s="4"/>
-      <c r="J659" s="4"/>
-      <c r="K659" s="4"/>
-      <c r="L659" s="4"/>
-      <c r="M659" s="4"/>
-      <c r="N659" s="4"/>
-      <c r="O659" s="4"/>
-      <c r="P659" s="4"/>
-      <c r="Q659" s="4"/>
-      <c r="R659" s="4"/>
-      <c r="S659" s="4"/>
-      <c r="T659" s="4"/>
-      <c r="U659" s="4"/>
-      <c r="V659" s="4"/>
-    </row>
-    <row r="660" spans="1:22" ht="22" customHeight="1">
-      <c r="A660" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B660" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C660" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D660" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E660" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F660" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G660" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H660" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I660" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J660" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K660" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L660" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M660" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N660" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O660" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P660" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q660" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R660" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S660" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T660" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="U660" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="V660" s="5" t="s">
-        <v>25</v>
+      <c r="M660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U660" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V660" s="11">
+        <v>98.71172376873662</v>
       </c>
     </row>
     <row r="661" spans="1:22">
       <c r="A661" s="6" t="s">
-        <v>789</v>
+        <v>1350</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>790</v>
+        <v>464</v>
       </c>
       <c r="C661" s="7" t="s">
-        <v>28</v>
+        <v>428</v>
       </c>
       <c r="D661" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E661" s="8">
-        <v>23249.096704</v>
-      </c>
-      <c r="F661" s="9">
-        <v>10.58799092293385</v>
-      </c>
-      <c r="G661" s="9">
-        <v>-0.28771197424686</v>
-      </c>
-      <c r="H661" s="9">
-        <v>-28.16427067427359</v>
-      </c>
-      <c r="I661" s="9">
-        <v>15.2922875171542</v>
+        <v>38709.911552</v>
+      </c>
+      <c r="F661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I661" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J661" s="11">
-        <v>7.34889280734496</v>
+        <v>7.8300140269052</v>
       </c>
       <c r="K661" s="9">
-        <v>-4.3921347181816</v>
+        <v>20.04622268789213</v>
       </c>
       <c r="L661" s="9">
-        <v>-16.9</v>
-      </c>
-      <c r="M661" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="N661" s="9">
-        <v>83.23873211902226</v>
-      </c>
-      <c r="O661" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="P661" s="9">
-        <v>66.5089585090408</v>
-      </c>
-      <c r="Q661" s="9">
-        <v>61.17457010769595</v>
+        <v>5.4</v>
+      </c>
+      <c r="M661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P661" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q661" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R661" s="10" t="s">
         <v>30</v>
@@ -46449,200 +46628,200 @@
       <c r="T661" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U661" s="12" t="s">
-        <v>41</v>
+      <c r="U661" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V661" s="11">
-        <v>47.91327623126338</v>
+        <v>97.76498929336188</v>
       </c>
     </row>
     <row r="662" spans="1:22">
       <c r="A662" s="6" t="s">
-        <v>1411</v>
+        <v>1384</v>
       </c>
       <c r="B662" s="7" t="s">
-        <v>1412</v>
+        <v>1385</v>
       </c>
       <c r="C662" s="7" t="s">
-        <v>28</v>
+        <v>428</v>
       </c>
       <c r="D662" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E662" s="8">
-        <v>762322.092032</v>
-      </c>
-      <c r="F662" s="9">
-        <v>14.39909228246559</v>
-      </c>
-      <c r="G662" s="9">
-        <v>0.76076645797761</v>
-      </c>
-      <c r="H662" s="9">
-        <v>47.26579989976284</v>
-      </c>
-      <c r="I662" s="9">
-        <v>17.08548321355481</v>
+        <v>8219.0208</v>
+      </c>
+      <c r="F662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I662" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J662" s="11">
-        <v>101.4597684119986</v>
+        <v>1.485994891319154</v>
       </c>
       <c r="K662" s="9">
-        <v>0.94099004226403</v>
+        <v>55.59947734893188</v>
       </c>
       <c r="L662" s="9">
-        <v>37.8</v>
-      </c>
-      <c r="M662" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="N662" s="9">
-        <v>24.53293446971835</v>
-      </c>
-      <c r="O662" s="7" t="s">
-        <v>1413</v>
-      </c>
-      <c r="P662" s="9">
-        <v>467.7697841726618</v>
-      </c>
-      <c r="Q662" s="9">
-        <v>10.34555214833951</v>
-      </c>
-      <c r="R662" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S662" s="9">
-        <v>178.9746882258184</v>
-      </c>
-      <c r="T662" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U662" s="12" t="s">
-        <v>41</v>
+        <v>-7.6</v>
+      </c>
+      <c r="M662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T662" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U662" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V662" s="11">
-        <v>56.21306209850107</v>
+        <v>97.04175588865095</v>
       </c>
     </row>
     <row r="663" spans="1:22">
       <c r="A663" s="6" t="s">
-        <v>397</v>
+        <v>1386</v>
       </c>
       <c r="B663" s="7" t="s">
-        <v>398</v>
+        <v>1387</v>
       </c>
       <c r="C663" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D663" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E663" s="8">
-        <v>12578.661376</v>
+        <v>307</v>
+      </c>
+      <c r="E663" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F663" s="9">
-        <v>20.21134884265646</v>
+        <v>10.83795825108153</v>
       </c>
       <c r="G663" s="9">
-        <v>16.4350192965183</v>
+        <v>6.40300490933652</v>
       </c>
       <c r="H663" s="9">
-        <v>-39.21585735433231</v>
+        <v>243.2142618781592</v>
       </c>
       <c r="I663" s="9">
-        <v>20.9006052706891</v>
-      </c>
-      <c r="J663" s="11">
-        <v>7.88744587549017</v>
+        <v>13.64504881992278</v>
+      </c>
+      <c r="J663" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="K663" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L663" s="9">
-        <v>-7.6</v>
+      <c r="L663" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M663" s="7" t="s">
-        <v>399</v>
+        <v>1388</v>
       </c>
       <c r="N663" s="9">
-        <v>53.42455018949013</v>
+        <v>37.97959455657402</v>
       </c>
       <c r="O663" s="7" t="s">
-        <v>400</v>
+        <v>1389</v>
       </c>
       <c r="P663" s="9">
-        <v>26.88567771615129</v>
+        <v>23.62832373305406</v>
       </c>
       <c r="Q663" s="9">
-        <v>46.64781228573134</v>
+        <v>6.95427841326001</v>
       </c>
       <c r="R663" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="S663" s="9">
-        <v>-185.986970028494</v>
-      </c>
-      <c r="T663" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U663" s="12" t="s">
+      <c r="S663" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T663" s="12" t="s">
         <v>41</v>
       </c>
+      <c r="U663" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="V663" s="11">
-        <v>44.63811563169165</v>
+        <v>96.01017130620984</v>
       </c>
     </row>
     <row r="664" spans="1:22">
       <c r="A664" s="6" t="s">
-        <v>212</v>
+        <v>1390</v>
       </c>
       <c r="B664" s="7" t="s">
-        <v>213</v>
+        <v>1391</v>
       </c>
       <c r="C664" s="7" t="s">
-        <v>28</v>
+        <v>585</v>
       </c>
       <c r="D664" s="7" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="E664" s="8">
-        <v>564107.214848</v>
-      </c>
-      <c r="F664" s="9">
-        <v>25.37691905817877</v>
-      </c>
-      <c r="G664" s="9">
-        <v>22.23484640325328</v>
-      </c>
-      <c r="H664" s="9">
-        <v>460.1372328458942</v>
-      </c>
-      <c r="I664" s="9">
-        <v>25.4315100204583</v>
+        <v>121887.064064</v>
+      </c>
+      <c r="F664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I664" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J664" s="11">
-        <v>17.39382995030982</v>
+        <v>5.238151175637653</v>
       </c>
       <c r="K664" s="9">
-        <v>2.21790734645562</v>
+        <v>414.8230582160164</v>
       </c>
       <c r="L664" s="9">
-        <v>9.9</v>
-      </c>
-      <c r="M664" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="N664" s="9">
-        <v>21.37774708778672</v>
-      </c>
-      <c r="O664" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="P664" s="9">
-        <v>355.5555555555555</v>
-      </c>
-      <c r="Q664" s="9">
-        <v>0.7092925360709185</v>
+        <v>-14.8</v>
+      </c>
+      <c r="M664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q664" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R664" s="10" t="s">
         <v>30</v>
@@ -46650,67 +46829,67 @@
       <c r="S664" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T664" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U664" s="12" t="s">
-        <v>41</v>
+      <c r="T664" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U664" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V664" s="11">
-        <v>38.20824411134903</v>
+        <v>94.9009635974304</v>
       </c>
     </row>
     <row r="665" spans="1:22">
       <c r="A665" s="6" t="s">
-        <v>248</v>
+        <v>1392</v>
       </c>
       <c r="B665" s="7" t="s">
-        <v>249</v>
+        <v>1393</v>
       </c>
       <c r="C665" s="7" t="s">
-        <v>28</v>
+        <v>253</v>
       </c>
       <c r="D665" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E665" s="8">
-        <v>11684.030464</v>
-      </c>
-      <c r="F665" s="9">
-        <v>29.01002425797337</v>
-      </c>
-      <c r="G665" s="9">
-        <v>20.90060773402971</v>
-      </c>
-      <c r="H665" s="9">
-        <v>200</v>
-      </c>
-      <c r="I665" s="9">
-        <v>27.40571931347813</v>
+        <v>19.9079</v>
+      </c>
+      <c r="F665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I665" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J665" s="11">
-        <v>10.48579969188127</v>
+        <v>6.363989581072281</v>
       </c>
       <c r="K665" s="9">
-        <v>4.5452252596934</v>
+        <v>36.86790168726988</v>
       </c>
       <c r="L665" s="9">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M665" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="N665" s="9">
-        <v>97.81444953993072</v>
-      </c>
-      <c r="O665" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="P665" s="9">
-        <v>5.080699006037381</v>
-      </c>
-      <c r="Q665" s="9">
-        <v>0.3383451667076098</v>
+        <v>-39.1</v>
+      </c>
+      <c r="M665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q665" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R665" s="10" t="s">
         <v>30</v>
@@ -46718,67 +46897,67 @@
       <c r="S665" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T665" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U665" s="12" t="s">
-        <v>41</v>
+      <c r="T665" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U665" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V665" s="11">
-        <v>58.56852248394004</v>
+        <v>93.3832976445396</v>
       </c>
     </row>
     <row r="666" spans="1:22">
       <c r="A666" s="6" t="s">
-        <v>752</v>
+        <v>1394</v>
       </c>
       <c r="B666" s="7" t="s">
-        <v>753</v>
+        <v>1395</v>
       </c>
       <c r="C666" s="7" t="s">
-        <v>28</v>
+        <v>585</v>
       </c>
       <c r="D666" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E666" s="8">
-        <v>12134.3232</v>
-      </c>
-      <c r="F666" s="9">
-        <v>14.03638757502264</v>
-      </c>
-      <c r="G666" s="9">
-        <v>6.90913608330241</v>
-      </c>
-      <c r="H666" s="9">
-        <v>15.9424688855513</v>
-      </c>
-      <c r="I666" s="9">
-        <v>21.17626443534281</v>
-      </c>
-      <c r="J666" s="11">
-        <v>9.129744194863251</v>
-      </c>
-      <c r="K666" s="9">
-        <v>10.85536511834463</v>
-      </c>
-      <c r="L666" s="9">
-        <v>5.4</v>
-      </c>
-      <c r="M666" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="N666" s="9">
-        <v>100</v>
-      </c>
-      <c r="O666" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="P666" s="9">
-        <v>-8.981387797359941</v>
-      </c>
-      <c r="Q666" s="9">
-        <v>0</v>
+        <v>307</v>
+      </c>
+      <c r="E666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P666" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q666" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R666" s="10" t="s">
         <v>30</v>
@@ -46793,66 +46972,66 @@
         <v>30</v>
       </c>
       <c r="V666" s="11">
-        <v>78.19432548179871</v>
+        <v>92.4183618843683</v>
       </c>
     </row>
     <row r="667" spans="1:22">
       <c r="A667" s="6" t="s">
-        <v>781</v>
+        <v>1396</v>
       </c>
       <c r="B667" s="7" t="s">
-        <v>782</v>
+        <v>1397</v>
       </c>
       <c r="C667" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D667" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E667" s="8">
-        <v>147615.596544</v>
+        <v>59</v>
+      </c>
+      <c r="E667" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F667" s="9">
-        <v>15.94268540560896</v>
+        <v>4.010532285140711</v>
       </c>
       <c r="G667" s="9">
-        <v>1.19662953118814</v>
+        <v>-10.52463272169449</v>
       </c>
       <c r="H667" s="10" t="s">
         <v>30</v>
       </c>
       <c r="I667" s="9">
-        <v>18.39474460776682</v>
-      </c>
-      <c r="J667" s="11">
-        <v>7.826613960296955</v>
-      </c>
-      <c r="K667" s="9">
-        <v>8.384361437248861</v>
-      </c>
-      <c r="L667" s="9">
-        <v>5.4</v>
+        <v>2.17980326348073</v>
+      </c>
+      <c r="J667" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K667" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L667" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M667" s="7" t="s">
-        <v>783</v>
+        <v>1398</v>
       </c>
       <c r="N667" s="9">
-        <v>18.86635609511109</v>
+        <v>97.53328112764292</v>
       </c>
       <c r="O667" s="7" t="s">
-        <v>784</v>
+        <v>1398</v>
       </c>
       <c r="P667" s="9">
-        <v>128.5714285714286</v>
+        <v>-18.11308349769888</v>
       </c>
       <c r="Q667" s="9">
-        <v>1.895410792529631</v>
+        <v>4.73279302514139</v>
       </c>
       <c r="R667" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="S667" s="10" t="s">
-        <v>30</v>
+      <c r="S667" s="9">
+        <v>23.19326457048476</v>
       </c>
       <c r="T667" s="10" t="s">
         <v>30</v>
@@ -46861,134 +47040,134 @@
         <v>30</v>
       </c>
       <c r="V667" s="11">
-        <v>88.94245182012848</v>
+        <v>91.65792291220556</v>
       </c>
     </row>
     <row r="668" spans="1:22">
       <c r="A668" s="6" t="s">
-        <v>1414</v>
+        <v>1399</v>
       </c>
       <c r="B668" s="7" t="s">
-        <v>1415</v>
+        <v>1400</v>
       </c>
       <c r="C668" s="7" t="s">
-        <v>28</v>
+        <v>694</v>
       </c>
       <c r="D668" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E668" s="8">
-        <v>22147.784704</v>
-      </c>
-      <c r="F668" s="9">
-        <v>27.29368094718512</v>
-      </c>
-      <c r="G668" s="9">
-        <v>23.60541611051562</v>
-      </c>
-      <c r="H668" s="9">
-        <v>31.35753410432825</v>
+        <v>307</v>
+      </c>
+      <c r="E668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H668" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I668" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J668" s="11">
-        <v>27.76022696184645</v>
-      </c>
-      <c r="K668" s="9">
-        <v>1.53875434746505</v>
-      </c>
-      <c r="L668" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="M668" s="7" t="s">
-        <v>1416</v>
-      </c>
-      <c r="N668" s="9">
-        <v>21.2542084254435</v>
-      </c>
-      <c r="O668" s="7" t="s">
-        <v>1417</v>
-      </c>
-      <c r="P668" s="9">
-        <v>27.13397399660827</v>
-      </c>
-      <c r="Q668" s="9">
-        <v>8.44242995511228</v>
-      </c>
-      <c r="R668" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S668" s="9">
-        <v>1.749078371350507</v>
-      </c>
-      <c r="T668" s="12" t="s">
-        <v>41</v>
+      <c r="J668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S668" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T668" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U668" s="10" t="s">
         <v>30</v>
       </c>
       <c r="V668" s="11">
-        <v>32.0904710920771</v>
+        <v>91.22189507494646</v>
       </c>
     </row>
     <row r="669" spans="1:22">
       <c r="A669" s="6" t="s">
-        <v>1418</v>
+        <v>1265</v>
       </c>
       <c r="B669" s="7" t="s">
-        <v>1419</v>
+        <v>1266</v>
       </c>
       <c r="C669" s="7" t="s">
-        <v>28</v>
+        <v>716</v>
       </c>
       <c r="D669" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E669" s="8">
-        <v>15452.863488</v>
-      </c>
-      <c r="F669" s="9">
-        <v>14.40609890391468</v>
-      </c>
-      <c r="G669" s="9">
-        <v>10.10694436354289</v>
-      </c>
-      <c r="H669" s="9">
-        <v>-0.8635316709933301</v>
-      </c>
-      <c r="I669" s="9">
-        <v>15.02294740921002</v>
-      </c>
-      <c r="J669" s="11">
-        <v>17.61870897015553</v>
-      </c>
-      <c r="K669" s="9">
-        <v>3.39759030685614</v>
-      </c>
-      <c r="L669" s="9">
-        <v>8.9</v>
-      </c>
-      <c r="M669" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N669" s="9">
-        <v>25.43663233318406</v>
-      </c>
-      <c r="O669" s="7" t="s">
-        <v>1113</v>
-      </c>
-      <c r="P669" s="9">
-        <v>15.20092735703247</v>
-      </c>
-      <c r="Q669" s="9">
-        <v>3.907483599359118</v>
-      </c>
-      <c r="R669" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S669" s="9">
-        <v>15.2786123366391</v>
+        <v>307</v>
+      </c>
+      <c r="E669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R669" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S669" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T669" s="10" t="s">
         <v>30</v>
@@ -46997,66 +47176,66 @@
         <v>30</v>
       </c>
       <c r="V669" s="11">
-        <v>39.56370449678801</v>
+        <v>90.89908993576016</v>
       </c>
     </row>
     <row r="670" spans="1:22">
       <c r="A670" s="6" t="s">
-        <v>1420</v>
+        <v>1401</v>
       </c>
       <c r="B670" s="7" t="s">
-        <v>1421</v>
+        <v>1402</v>
       </c>
       <c r="C670" s="7" t="s">
-        <v>28</v>
+        <v>370</v>
       </c>
       <c r="D670" s="7" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="E670" s="8">
-        <v>17707.638784</v>
-      </c>
-      <c r="F670" s="9">
-        <v>20.21337049550995</v>
-      </c>
-      <c r="G670" s="9">
-        <v>18.00401472219318</v>
-      </c>
-      <c r="H670" s="9">
-        <v>0.4401554668061201</v>
+        <v>5142.772224</v>
+      </c>
+      <c r="F670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H670" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I670" s="10" t="s">
         <v>30</v>
       </c>
       <c r="J670" s="11">
-        <v>15.58137187069422</v>
+        <v>5.833631111111111</v>
       </c>
       <c r="K670" s="9">
-        <v>1.01058081307651</v>
+        <v>29.5438901398251</v>
       </c>
       <c r="L670" s="9">
-        <v>13.8</v>
-      </c>
-      <c r="M670" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="N670" s="9">
-        <v>36.98476026013466</v>
-      </c>
-      <c r="O670" s="7" t="s">
-        <v>1422</v>
-      </c>
-      <c r="P670" s="9">
-        <v>20.7509619211888</v>
-      </c>
-      <c r="Q670" s="9">
-        <v>2.083050131214556</v>
-      </c>
-      <c r="R670" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="S670" s="9">
-        <v>27.75662331430469</v>
+        <v>11.6</v>
+      </c>
+      <c r="M670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R670" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S670" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T670" s="10" t="s">
         <v>30</v>
@@ -47065,66 +47244,66 @@
         <v>30</v>
       </c>
       <c r="V670" s="11">
-        <v>37.67665952890792</v>
+        <v>90.8632226980728</v>
       </c>
     </row>
     <row r="671" spans="1:22">
       <c r="A671" s="6" t="s">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="B671" s="7" t="s">
-        <v>1424</v>
+        <v>1404</v>
       </c>
       <c r="C671" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D671" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E671" s="8">
-        <v>10411.935744</v>
+        <v>275</v>
+      </c>
+      <c r="E671" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F671" s="9">
-        <v>7.49516988342678</v>
+        <v>-93.30935942912926</v>
       </c>
       <c r="G671" s="9">
-        <v>5.433517399693049</v>
+        <v>-126.4891121817485</v>
       </c>
       <c r="H671" s="9">
         <v>200</v>
       </c>
-      <c r="I671" s="9">
-        <v>21.17194829228418</v>
-      </c>
-      <c r="J671" s="11">
-        <v>9.194940017024711</v>
-      </c>
-      <c r="K671" s="9">
-        <v>2.72871941381047</v>
-      </c>
-      <c r="L671" s="9">
-        <v>9</v>
-      </c>
-      <c r="M671" s="7" t="s">
-        <v>1425</v>
-      </c>
-      <c r="N671" s="9">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="O671" s="7" t="s">
-        <v>1426</v>
-      </c>
-      <c r="P671" s="9">
-        <v>29.95391705069124</v>
-      </c>
-      <c r="Q671" s="9">
-        <v>0.1461085646552368</v>
-      </c>
-      <c r="R671" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S671" s="10" t="s">
-        <v>30</v>
+      <c r="I671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q671" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R671" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S671" s="9">
+        <v>11.5193160318741</v>
       </c>
       <c r="T671" s="10" t="s">
         <v>30</v>
@@ -47133,36 +47312,36 @@
         <v>30</v>
       </c>
       <c r="V671" s="11">
-        <v>89.89079229122056</v>
+        <v>90.72805139186296</v>
       </c>
     </row>
     <row r="672" spans="1:22">
       <c r="A672" s="6" t="s">
-        <v>1427</v>
+        <v>1405</v>
       </c>
       <c r="B672" s="7" t="s">
-        <v>1428</v>
+        <v>1406</v>
       </c>
       <c r="C672" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D672" s="7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E672" s="10" t="s">
         <v>30</v>
       </c>
       <c r="F672" s="9">
-        <v>9.415314575424901</v>
+        <v>9.316775054105381</v>
       </c>
       <c r="G672" s="9">
-        <v>3.39669120871233</v>
-      </c>
-      <c r="H672" s="9">
-        <v>3.66426562798681</v>
-      </c>
-      <c r="I672" s="9">
-        <v>13.45915131394612</v>
+        <v>6.295029703908479</v>
+      </c>
+      <c r="H672" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I672" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J672" s="10" t="s">
         <v>30</v>
@@ -47174,229 +47353,229 @@
         <v>30</v>
       </c>
       <c r="M672" s="7" t="s">
-        <v>28</v>
+        <v>1407</v>
       </c>
       <c r="N672" s="9">
-        <v>43.05303752030628</v>
+        <v>50.32704593854579</v>
       </c>
       <c r="O672" s="7" t="s">
-        <v>142</v>
+        <v>1407</v>
       </c>
       <c r="P672" s="9">
-        <v>32.54437343112995</v>
+        <v>5.584809318653261</v>
       </c>
       <c r="Q672" s="9">
-        <v>2.909940133716239</v>
+        <v>1.936960230878426</v>
       </c>
       <c r="R672" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S672" s="9">
-        <v>134.0457960019367</v>
+        <v>46</v>
+      </c>
+      <c r="S672" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T672" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U672" s="12" t="s">
-        <v>41</v>
+      <c r="U672" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V672" s="11">
-        <v>3.592344753747323</v>
+        <v>89.85599571734474</v>
       </c>
     </row>
     <row r="673" spans="1:22">
       <c r="A673" s="6" t="s">
-        <v>918</v>
+        <v>1408</v>
       </c>
       <c r="B673" s="7" t="s">
-        <v>919</v>
+        <v>1409</v>
       </c>
       <c r="C673" s="7" t="s">
-        <v>28</v>
+        <v>603</v>
       </c>
       <c r="D673" s="7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E673" s="8">
-        <v>12343.648256</v>
-      </c>
-      <c r="F673" s="9">
-        <v>16.32630569798057</v>
-      </c>
-      <c r="G673" s="9">
-        <v>8.34937966664376</v>
-      </c>
-      <c r="H673" s="9">
-        <v>200</v>
-      </c>
-      <c r="I673" s="9">
-        <v>14.92643595649632</v>
+        <v>199431.70048</v>
+      </c>
+      <c r="F673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I673" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J673" s="11">
-        <v>20.48611105504418</v>
+        <v>1.864476361899484</v>
       </c>
       <c r="K673" s="9">
-        <v>2.23980692147162</v>
+        <v>-6.03677845148161</v>
       </c>
       <c r="L673" s="9">
-        <v>34.4</v>
-      </c>
-      <c r="M673" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="N673" s="9">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="O673" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="P673" s="9">
-        <v>3948.102189781021</v>
-      </c>
-      <c r="Q673" s="9">
-        <v>31.90432977647047</v>
-      </c>
-      <c r="R673" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S673" s="9">
-        <v>31.73373240736936</v>
-      </c>
-      <c r="T673" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U673" s="12" t="s">
-        <v>41</v>
+        <v>24</v>
+      </c>
+      <c r="M673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T673" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U673" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V673" s="11">
-        <v>44.03078158458244</v>
+        <v>89.67264453961455</v>
       </c>
     </row>
     <row r="674" spans="1:22">
       <c r="A674" s="6" t="s">
-        <v>1171</v>
+        <v>1410</v>
       </c>
       <c r="B674" s="7" t="s">
-        <v>1172</v>
+        <v>1411</v>
       </c>
       <c r="C674" s="7" t="s">
-        <v>28</v>
+        <v>694</v>
       </c>
       <c r="D674" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E674" s="8">
-        <v>12465.329152</v>
-      </c>
-      <c r="F674" s="9">
-        <v>18.3357672256623</v>
-      </c>
-      <c r="G674" s="9">
-        <v>11.34875053232618</v>
-      </c>
-      <c r="H674" s="9">
-        <v>162.6826764963662</v>
-      </c>
-      <c r="I674" s="9">
-        <v>24.64990259395278</v>
-      </c>
-      <c r="J674" s="11">
-        <v>11.7959601299469</v>
-      </c>
-      <c r="K674" s="9">
-        <v>4.39559184774585</v>
-      </c>
-      <c r="L674" s="9">
-        <v>12.7</v>
-      </c>
-      <c r="M674" s="7" t="s">
-        <v>1429</v>
-      </c>
-      <c r="N674" s="9">
-        <v>24.41986345619947</v>
-      </c>
-      <c r="O674" s="7" t="s">
-        <v>1430</v>
-      </c>
-      <c r="P674" s="9">
-        <v>22.48766554141781</v>
-      </c>
-      <c r="Q674" s="9">
-        <v>11.57935981187805</v>
-      </c>
-      <c r="R674" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S674" s="9">
-        <v>30557.33041489141</v>
-      </c>
-      <c r="T674" s="12" t="s">
-        <v>41</v>
+        <v>275</v>
+      </c>
+      <c r="E674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S674" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T674" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U674" s="10" t="s">
         <v>30</v>
       </c>
       <c r="V674" s="11">
-        <v>45.06932548179872</v>
+        <v>89.61509635974303</v>
       </c>
     </row>
     <row r="675" spans="1:22">
       <c r="A675" s="6" t="s">
-        <v>1431</v>
+        <v>1412</v>
       </c>
       <c r="B675" s="7" t="s">
-        <v>1432</v>
+        <v>1413</v>
       </c>
       <c r="C675" s="7" t="s">
-        <v>28</v>
+        <v>503</v>
       </c>
       <c r="D675" s="7" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="E675" s="8">
-        <v>82539.92140799999</v>
-      </c>
-      <c r="F675" s="9">
-        <v>8.44733011792461</v>
-      </c>
-      <c r="G675" s="9">
-        <v>5.14659991435997</v>
-      </c>
-      <c r="H675" s="9">
-        <v>200</v>
-      </c>
-      <c r="I675" s="9">
-        <v>13.78704959722941</v>
+        <v>2598.57536</v>
+      </c>
+      <c r="F675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I675" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J675" s="11">
-        <v>145.1852238831085</v>
+        <v>7.132551509414774</v>
       </c>
       <c r="K675" s="9">
-        <v>0.8472272859860199</v>
+        <v>6.593439876225101</v>
       </c>
       <c r="L675" s="9">
-        <v>33.1</v>
-      </c>
-      <c r="M675" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N675" s="9">
-        <v>16.97306459514074</v>
-      </c>
-      <c r="O675" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P675" s="9">
-        <v>21.42857142857142</v>
-      </c>
-      <c r="Q675" s="9">
-        <v>2.563643962950055</v>
-      </c>
-      <c r="R675" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S675" s="9">
-        <v>23.78063725490197</v>
+        <v>12.9</v>
+      </c>
+      <c r="M675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R675" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S675" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T675" s="10" t="s">
         <v>30</v>
@@ -47405,66 +47584,66 @@
         <v>30</v>
       </c>
       <c r="V675" s="11">
-        <v>50.62901498929336</v>
+        <v>89.59154175588864</v>
       </c>
     </row>
     <row r="676" spans="1:22">
       <c r="A676" s="6" t="s">
-        <v>1433</v>
+        <v>1414</v>
       </c>
       <c r="B676" s="7" t="s">
-        <v>1434</v>
+        <v>1415</v>
       </c>
       <c r="C676" s="7" t="s">
-        <v>28</v>
+        <v>716</v>
       </c>
       <c r="D676" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E676" s="8">
-        <v>71293.7472</v>
-      </c>
-      <c r="F676" s="9">
-        <v>21.68056339811111</v>
-      </c>
-      <c r="G676" s="9">
-        <v>17.82389050341457</v>
-      </c>
-      <c r="H676" s="9">
-        <v>-4.58377475435458</v>
-      </c>
-      <c r="I676" s="9">
-        <v>20.99548243827234</v>
-      </c>
-      <c r="J676" s="11">
-        <v>19.80757872812305</v>
-      </c>
-      <c r="K676" s="9">
-        <v>2.22519508695427</v>
-      </c>
-      <c r="L676" s="9">
-        <v>10</v>
-      </c>
-      <c r="M676" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="N676" s="9">
-        <v>32.60474351348408</v>
-      </c>
-      <c r="O676" s="7" t="s">
-        <v>1435</v>
-      </c>
-      <c r="P676" s="9">
-        <v>336.6197183098592</v>
-      </c>
-      <c r="Q676" s="9">
-        <v>10.40315990402382</v>
-      </c>
-      <c r="R676" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S676" s="9">
-        <v>72.65687465263815</v>
+        <v>275</v>
+      </c>
+      <c r="E676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R676" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S676" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T676" s="10" t="s">
         <v>30</v>
@@ -47473,270 +47652,270 @@
         <v>30</v>
       </c>
       <c r="V676" s="11">
-        <v>50.49036402569592</v>
+        <v>89.58859743040685</v>
       </c>
     </row>
     <row r="677" spans="1:22">
       <c r="A677" s="6" t="s">
-        <v>233</v>
+        <v>1284</v>
       </c>
       <c r="B677" s="7" t="s">
-        <v>234</v>
+        <v>1285</v>
       </c>
       <c r="C677" s="7" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="D677" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E677" s="8">
-        <v>42803.822592</v>
-      </c>
-      <c r="F677" s="9">
-        <v>39.40116428899288</v>
-      </c>
-      <c r="G677" s="9">
-        <v>35.01886100401464</v>
-      </c>
-      <c r="H677" s="9">
-        <v>200</v>
-      </c>
-      <c r="I677" s="9">
-        <v>42.56823551505765</v>
+        <v>22.405378</v>
+      </c>
+      <c r="F677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I677" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J677" s="11">
-        <v>25.80039355470132</v>
+        <v>7.363228016877637</v>
       </c>
       <c r="K677" s="9">
-        <v>2.81774818921294</v>
+        <v>47.73686478308912</v>
       </c>
       <c r="L677" s="9">
-        <v>14.1</v>
-      </c>
-      <c r="M677" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="N677" s="9">
-        <v>19.6177536575438</v>
-      </c>
-      <c r="O677" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="P677" s="9">
-        <v>17.21198903119539</v>
-      </c>
-      <c r="Q677" s="9">
-        <v>0.8556176195179427</v>
-      </c>
-      <c r="R677" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S677" s="9">
-        <v>7.709412412097334</v>
-      </c>
-      <c r="T677" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U677" s="12" t="s">
-        <v>41</v>
+        <v>-2.1</v>
+      </c>
+      <c r="M677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T677" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U677" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V677" s="11">
-        <v>49.52489293361884</v>
+        <v>89.30326552462526</v>
       </c>
     </row>
     <row r="678" spans="1:22">
       <c r="A678" s="6" t="s">
-        <v>127</v>
+        <v>1416</v>
       </c>
       <c r="B678" s="7" t="s">
-        <v>128</v>
+        <v>1417</v>
       </c>
       <c r="C678" s="7" t="s">
-        <v>28</v>
+        <v>423</v>
       </c>
       <c r="D678" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E678" s="8">
-        <v>381861.855232</v>
-      </c>
-      <c r="F678" s="9">
-        <v>50.02333165939806</v>
-      </c>
-      <c r="G678" s="9">
-        <v>39.94386199076626</v>
-      </c>
-      <c r="H678" s="9">
-        <v>295.1730293649112</v>
+        <v>119737.376768</v>
+      </c>
+      <c r="F678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H678" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I678" s="10" t="s">
         <v>30</v>
       </c>
       <c r="J678" s="11">
-        <v>48.52915430829456</v>
+        <v>4.600395254844893</v>
       </c>
       <c r="K678" s="9">
-        <v>1.13976859546647</v>
+        <v>8.39597909304349</v>
       </c>
       <c r="L678" s="9">
-        <v>23.8</v>
-      </c>
-      <c r="M678" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="N678" s="9">
-        <v>29.92758121124807</v>
-      </c>
-      <c r="O678" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="P678" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q678" s="9">
-        <v>0</v>
-      </c>
-      <c r="R678" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S678" s="9">
-        <v>-21.55498884048724</v>
-      </c>
-      <c r="T678" s="12" t="s">
-        <v>41</v>
+        <v>11.6</v>
+      </c>
+      <c r="M678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S678" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T678" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U678" s="10" t="s">
         <v>30</v>
       </c>
       <c r="V678" s="11">
-        <v>48.57012847965738</v>
+        <v>89.27489293361884</v>
       </c>
     </row>
     <row r="679" spans="1:22">
       <c r="A679" s="6" t="s">
-        <v>1436</v>
+        <v>1418</v>
       </c>
       <c r="B679" s="7" t="s">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="C679" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D679" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E679" s="8">
-        <v>12552.172544</v>
+        <v>307</v>
+      </c>
+      <c r="E679" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F679" s="9">
-        <v>25.35500931525615</v>
+        <v>14.14764495775639</v>
       </c>
       <c r="G679" s="9">
-        <v>24.1038316036968</v>
-      </c>
-      <c r="H679" s="9">
-        <v>31.16469006712103</v>
-      </c>
-      <c r="I679" s="9">
-        <v>24.26887811810059</v>
-      </c>
-      <c r="J679" s="11">
-        <v>16.49899925782821</v>
-      </c>
-      <c r="K679" s="9">
-        <v>4.12027682209655</v>
-      </c>
-      <c r="L679" s="9">
-        <v>2.2</v>
+        <v>-29.81694995520391</v>
+      </c>
+      <c r="H679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L679" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M679" s="7" t="s">
-        <v>28</v>
+        <v>1420</v>
       </c>
       <c r="N679" s="9">
-        <v>54.37161314256837</v>
+        <v>59.53168685927307</v>
       </c>
       <c r="O679" s="7" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="P679" s="9">
-        <v>-1.081518964675665</v>
+        <v>9.249709639953551</v>
       </c>
       <c r="Q679" s="9">
-        <v>1.465627278073556</v>
-      </c>
-      <c r="R679" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S679" s="9">
-        <v>-4.133865042797183</v>
-      </c>
-      <c r="T679" s="12" t="s">
-        <v>41</v>
+        <v>2.330235344616782</v>
+      </c>
+      <c r="R679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S679" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T679" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U679" s="10" t="s">
         <v>30</v>
       </c>
       <c r="V679" s="11">
-        <v>48.85626338329764</v>
+        <v>89.22243040685224</v>
       </c>
     </row>
     <row r="680" spans="1:22">
       <c r="A680" s="6" t="s">
-        <v>744</v>
+        <v>1421</v>
       </c>
       <c r="B680" s="7" t="s">
-        <v>745</v>
+        <v>1422</v>
       </c>
       <c r="C680" s="7" t="s">
-        <v>28</v>
+        <v>626</v>
       </c>
       <c r="D680" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E680" s="8">
-        <v>28606.16704</v>
-      </c>
-      <c r="F680" s="9">
-        <v>23.02210928808162</v>
-      </c>
-      <c r="G680" s="9">
-        <v>12.3513454013088</v>
-      </c>
-      <c r="H680" s="9">
-        <v>-3155.200934579439</v>
-      </c>
-      <c r="I680" s="9">
-        <v>26.3762128130752</v>
+        <v>14.921701</v>
+      </c>
+      <c r="F680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I680" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J680" s="11">
-        <v>8.784983736132059</v>
+        <v>19.76369851213782</v>
       </c>
       <c r="K680" s="9">
-        <v>6.69781258468104</v>
+        <v>43.7701438998141</v>
       </c>
       <c r="L680" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="M680" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="N680" s="9">
-        <v>24.8367335547431</v>
-      </c>
-      <c r="O680" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="P680" s="9">
-        <v>196.661101836394</v>
-      </c>
-      <c r="Q680" s="9">
-        <v>0.5986147521012869</v>
-      </c>
-      <c r="R680" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="S680" s="9">
-        <v>-5.323343713571752</v>
+        <v>15</v>
+      </c>
+      <c r="M680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R680" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S680" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T680" s="10" t="s">
         <v>30</v>
@@ -47745,66 +47924,66 @@
         <v>30</v>
       </c>
       <c r="V680" s="11">
-        <v>82.39400428265525</v>
+        <v>89.15792291220556</v>
       </c>
     </row>
     <row r="681" spans="1:22">
       <c r="A681" s="6" t="s">
-        <v>1147</v>
+        <v>1423</v>
       </c>
       <c r="B681" s="7" t="s">
-        <v>1148</v>
+        <v>1424</v>
       </c>
       <c r="C681" s="7" t="s">
-        <v>28</v>
+        <v>716</v>
       </c>
       <c r="D681" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E681" s="8">
-        <v>100520.255488</v>
-      </c>
-      <c r="F681" s="9">
-        <v>19.74290983466965</v>
-      </c>
-      <c r="G681" s="9">
-        <v>2.85946953226829</v>
-      </c>
-      <c r="H681" s="9">
-        <v>-1.14691627188177</v>
-      </c>
-      <c r="I681" s="9">
-        <v>27.15547778263739</v>
-      </c>
-      <c r="J681" s="11">
-        <v>67.60467140210618</v>
-      </c>
-      <c r="K681" s="9">
-        <v>3.08019756711583</v>
-      </c>
-      <c r="L681" s="9">
-        <v>65.5</v>
-      </c>
-      <c r="M681" s="7" t="s">
-        <v>1149</v>
-      </c>
-      <c r="N681" s="9">
-        <v>25.05531709954961</v>
-      </c>
-      <c r="O681" s="7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="P681" s="9">
-        <v>44.57323978496024</v>
-      </c>
-      <c r="Q681" s="9">
-        <v>2.092357279705445</v>
-      </c>
-      <c r="R681" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S681" s="9">
-        <v>25.02212629438111</v>
+        <v>275</v>
+      </c>
+      <c r="E681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R681" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S681" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T681" s="10" t="s">
         <v>30</v>
@@ -47813,279 +47992,1869 @@
         <v>30</v>
       </c>
       <c r="V681" s="11">
-        <v>86.09823340471091</v>
+        <v>89.12125267665952</v>
       </c>
     </row>
     <row r="682" spans="1:22">
       <c r="A682" s="6" t="s">
-        <v>120</v>
+        <v>1425</v>
       </c>
       <c r="B682" s="7" t="s">
-        <v>121</v>
+        <v>1426</v>
       </c>
       <c r="C682" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E682" s="8">
+        <v>28.096942</v>
+      </c>
+      <c r="F682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J682" s="11">
+        <v>-87.84552340059</v>
+      </c>
+      <c r="K682" s="9">
+        <v>33.56394087299607</v>
+      </c>
+      <c r="L682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U682" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V682" s="11">
+        <v>89.01017130620986</v>
+      </c>
+    </row>
+    <row r="684" spans="1:22" ht="22" customHeight="1">
+      <c r="A684" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B684" s="4"/>
+      <c r="C684" s="4"/>
+      <c r="D684" s="4"/>
+      <c r="E684" s="4"/>
+      <c r="F684" s="4"/>
+      <c r="G684" s="4"/>
+      <c r="H684" s="4"/>
+      <c r="I684" s="4"/>
+      <c r="J684" s="4"/>
+      <c r="K684" s="4"/>
+      <c r="L684" s="4"/>
+      <c r="M684" s="4"/>
+      <c r="N684" s="4"/>
+      <c r="O684" s="4"/>
+      <c r="P684" s="4"/>
+      <c r="Q684" s="4"/>
+      <c r="R684" s="4"/>
+      <c r="S684" s="4"/>
+      <c r="T684" s="4"/>
+      <c r="U684" s="4"/>
+      <c r="V684" s="4"/>
+    </row>
+    <row r="685" spans="1:22" ht="22" customHeight="1">
+      <c r="A685" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D685" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E685" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F685" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G685" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H685" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I685" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J685" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K685" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L685" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M685" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N685" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O685" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P685" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q685" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R685" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S685" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T685" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U685" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="V685" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="686" spans="1:22">
+      <c r="A686" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B686" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="C686" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D682" s="7" t="s">
+      <c r="D686" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E686" s="8">
+        <v>23249.096704</v>
+      </c>
+      <c r="F686" s="9">
+        <v>10.58799092293385</v>
+      </c>
+      <c r="G686" s="9">
+        <v>-0.28771197424686</v>
+      </c>
+      <c r="H686" s="9">
+        <v>-28.16427067427359</v>
+      </c>
+      <c r="I686" s="9">
+        <v>15.2922875171542</v>
+      </c>
+      <c r="J686" s="11">
+        <v>7.34889280734496</v>
+      </c>
+      <c r="K686" s="9">
+        <v>-4.3921347181816</v>
+      </c>
+      <c r="L686" s="9">
+        <v>-16.9</v>
+      </c>
+      <c r="M686" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="N686" s="9">
+        <v>83.23873211902226</v>
+      </c>
+      <c r="O686" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="P686" s="9">
+        <v>66.5089585090408</v>
+      </c>
+      <c r="Q686" s="9">
+        <v>61.17457010769595</v>
+      </c>
+      <c r="R686" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S686" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T686" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U686" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V686" s="11">
+        <v>47.91327623126338</v>
+      </c>
+    </row>
+    <row r="687" spans="1:22">
+      <c r="A687" s="6" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B687" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C687" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D687" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E682" s="8">
-        <v>343117.49632</v>
-      </c>
-      <c r="F682" s="9">
-        <v>56.16048279606593</v>
-      </c>
-      <c r="G682" s="9">
-        <v>45.03073679491686</v>
-      </c>
-      <c r="H682" s="9">
-        <v>-44.74109110086793</v>
-      </c>
-      <c r="I682" s="9">
-        <v>58.23011867639675</v>
-      </c>
-      <c r="J682" s="11">
-        <v>36.88889522486986</v>
-      </c>
-      <c r="K682" s="9">
-        <v>0.8861031782431901</v>
-      </c>
-      <c r="L682" s="9">
-        <v>11.4</v>
-      </c>
-      <c r="M682" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="N682" s="9">
-        <v>46.22234535164444</v>
-      </c>
-      <c r="O682" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="P682" s="9">
-        <v>50.52770448548814</v>
-      </c>
-      <c r="Q682" s="9">
-        <v>5.238834997307484</v>
-      </c>
-      <c r="R682" s="7" t="s">
+      <c r="E687" s="8">
+        <v>762322.092032</v>
+      </c>
+      <c r="F687" s="9">
+        <v>14.39909228246559</v>
+      </c>
+      <c r="G687" s="9">
+        <v>0.76076645797761</v>
+      </c>
+      <c r="H687" s="9">
+        <v>47.26579989976284</v>
+      </c>
+      <c r="I687" s="9">
+        <v>17.08548321355481</v>
+      </c>
+      <c r="J687" s="11">
+        <v>101.4597684119986</v>
+      </c>
+      <c r="K687" s="9">
+        <v>0.94099004226403</v>
+      </c>
+      <c r="L687" s="9">
+        <v>37.8</v>
+      </c>
+      <c r="M687" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="N687" s="9">
+        <v>24.53293446971835</v>
+      </c>
+      <c r="O687" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="P687" s="9">
+        <v>467.7697841726618</v>
+      </c>
+      <c r="Q687" s="9">
+        <v>10.34555214833951</v>
+      </c>
+      <c r="R687" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S687" s="9">
+        <v>178.9746882258184</v>
+      </c>
+      <c r="T687" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U687" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V687" s="11">
+        <v>56.21306209850107</v>
+      </c>
+    </row>
+    <row r="688" spans="1:22">
+      <c r="A688" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B688" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C688" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D688" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E688" s="8">
+        <v>12578.661376</v>
+      </c>
+      <c r="F688" s="9">
+        <v>20.21134884265646</v>
+      </c>
+      <c r="G688" s="9">
+        <v>16.4350192965183</v>
+      </c>
+      <c r="H688" s="9">
+        <v>-39.21585735433231</v>
+      </c>
+      <c r="I688" s="9">
+        <v>20.9006052706891</v>
+      </c>
+      <c r="J688" s="11">
+        <v>7.88744587549017</v>
+      </c>
+      <c r="K688" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L688" s="9">
+        <v>-7.6</v>
+      </c>
+      <c r="M688" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="N688" s="9">
+        <v>53.42455018949013</v>
+      </c>
+      <c r="O688" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="P688" s="9">
+        <v>26.88567771615129</v>
+      </c>
+      <c r="Q688" s="9">
+        <v>46.64781228573134</v>
+      </c>
+      <c r="R688" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="S682" s="9">
-        <v>13.62692432441163</v>
-      </c>
-      <c r="T682" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U682" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V682" s="11">
-        <v>41.9710920770878</v>
-      </c>
-    </row>
-    <row r="683" spans="1:22">
-      <c r="A683" s="6" t="s">
+      <c r="S688" s="9">
+        <v>-185.986970028494</v>
+      </c>
+      <c r="T688" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U688" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V688" s="11">
+        <v>44.63811563169165</v>
+      </c>
+    </row>
+    <row r="689" spans="1:22">
+      <c r="A689" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B689" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C689" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D689" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E689" s="8">
+        <v>11684.030464</v>
+      </c>
+      <c r="F689" s="9">
+        <v>29.01002425797337</v>
+      </c>
+      <c r="G689" s="9">
+        <v>20.90060773402971</v>
+      </c>
+      <c r="H689" s="9">
+        <v>200</v>
+      </c>
+      <c r="I689" s="9">
+        <v>27.40571931347813</v>
+      </c>
+      <c r="J689" s="11">
+        <v>10.48579969188127</v>
+      </c>
+      <c r="K689" s="9">
+        <v>4.5452252596934</v>
+      </c>
+      <c r="L689" s="9">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M689" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="N689" s="9">
+        <v>97.81444953993072</v>
+      </c>
+      <c r="O689" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="P689" s="9">
+        <v>5.080699006037381</v>
+      </c>
+      <c r="Q689" s="9">
+        <v>0.3383451667076098</v>
+      </c>
+      <c r="R689" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S689" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T689" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U689" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V689" s="11">
+        <v>58.56852248394004</v>
+      </c>
+    </row>
+    <row r="690" spans="1:22">
+      <c r="A690" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B690" s="7" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C690" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D690" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E690" s="8">
+        <v>5982.524928</v>
+      </c>
+      <c r="F690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J690" s="11">
+        <v>2.384461875584978</v>
+      </c>
+      <c r="K690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L690" s="9">
+        <v>-2.6</v>
+      </c>
+      <c r="M690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U690" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V690" s="11">
+        <v>80.55594218415418</v>
+      </c>
+    </row>
+    <row r="691" spans="1:22">
+      <c r="A691" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B691" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C691" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D691" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E691" s="8">
+        <v>564107.214848</v>
+      </c>
+      <c r="F691" s="9">
+        <v>25.37691905817877</v>
+      </c>
+      <c r="G691" s="9">
+        <v>22.23484640325328</v>
+      </c>
+      <c r="H691" s="9">
+        <v>460.1372328458942</v>
+      </c>
+      <c r="I691" s="9">
+        <v>25.4315100204583</v>
+      </c>
+      <c r="J691" s="11">
+        <v>17.39382995030982</v>
+      </c>
+      <c r="K691" s="9">
+        <v>2.21790734645562</v>
+      </c>
+      <c r="L691" s="9">
+        <v>9.9</v>
+      </c>
+      <c r="M691" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="N691" s="9">
+        <v>21.37774708778672</v>
+      </c>
+      <c r="O691" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="P691" s="9">
+        <v>355.5555555555555</v>
+      </c>
+      <c r="Q691" s="9">
+        <v>0.7092925360709185</v>
+      </c>
+      <c r="R691" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S691" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T691" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U691" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V691" s="11">
+        <v>38.20824411134903</v>
+      </c>
+    </row>
+    <row r="692" spans="1:22">
+      <c r="A692" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B692" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="C692" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D692" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E692" s="8">
+        <v>12134.3232</v>
+      </c>
+      <c r="F692" s="9">
+        <v>14.03638757502264</v>
+      </c>
+      <c r="G692" s="9">
+        <v>6.90913608330241</v>
+      </c>
+      <c r="H692" s="9">
+        <v>15.9424688855513</v>
+      </c>
+      <c r="I692" s="9">
+        <v>21.17626443534281</v>
+      </c>
+      <c r="J692" s="11">
+        <v>9.129744194863251</v>
+      </c>
+      <c r="K692" s="9">
+        <v>10.85536511834463</v>
+      </c>
+      <c r="L692" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="M692" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="N692" s="9">
+        <v>100</v>
+      </c>
+      <c r="O692" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="P692" s="9">
+        <v>-8.981387797359941</v>
+      </c>
+      <c r="Q692" s="9">
+        <v>0</v>
+      </c>
+      <c r="R692" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S692" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T692" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U692" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V692" s="11">
+        <v>78.19432548179871</v>
+      </c>
+    </row>
+    <row r="693" spans="1:22">
+      <c r="A693" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B693" s="7" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C693" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D693" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E693" s="8">
+        <v>86041.427968</v>
+      </c>
+      <c r="F693" s="9">
+        <v>-22.76937883819234</v>
+      </c>
+      <c r="G693" s="9">
+        <v>-61.74195098692925</v>
+      </c>
+      <c r="H693" s="9">
+        <v>200</v>
+      </c>
+      <c r="I693" s="9">
+        <v>-52.32238133357679</v>
+      </c>
+      <c r="J693" s="11">
+        <v>373.5170470572995</v>
+      </c>
+      <c r="K693" s="9">
+        <v>0.3085969797</v>
+      </c>
+      <c r="L693" s="9">
+        <v>130.4</v>
+      </c>
+      <c r="M693" s="7" t="s">
+        <v>1435</v>
+      </c>
+      <c r="N693" s="9">
+        <v>52.91868502365007</v>
+      </c>
+      <c r="O693" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="P693" s="9">
+        <v>163.4464651714993</v>
+      </c>
+      <c r="Q693" s="9">
+        <v>12.2696971103034</v>
+      </c>
+      <c r="R693" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S693" s="9">
+        <v>22.10992696590466</v>
+      </c>
+      <c r="T693" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U693" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V693" s="11">
+        <v>75.28827623126338</v>
+      </c>
+    </row>
+    <row r="694" spans="1:22">
+      <c r="A694" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="B694" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="C694" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D694" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E694" s="8">
+        <v>12343.648256</v>
+      </c>
+      <c r="F694" s="9">
+        <v>16.32630569798057</v>
+      </c>
+      <c r="G694" s="9">
+        <v>8.34937966664376</v>
+      </c>
+      <c r="H694" s="9">
+        <v>200</v>
+      </c>
+      <c r="I694" s="9">
+        <v>14.92643595649632</v>
+      </c>
+      <c r="J694" s="11">
+        <v>20.48611105504418</v>
+      </c>
+      <c r="K694" s="9">
+        <v>2.23980692147162</v>
+      </c>
+      <c r="L694" s="9">
+        <v>34.4</v>
+      </c>
+      <c r="M694" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="N694" s="9">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="O694" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="P694" s="9">
+        <v>3948.102189781021</v>
+      </c>
+      <c r="Q694" s="9">
+        <v>31.90432977647047</v>
+      </c>
+      <c r="R694" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S694" s="9">
+        <v>31.73373240736936</v>
+      </c>
+      <c r="T694" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U694" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V694" s="11">
+        <v>44.03078158458244</v>
+      </c>
+    </row>
+    <row r="695" spans="1:22">
+      <c r="A695" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B695" s="7" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C695" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D695" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E695" s="8">
+        <v>117310.226432</v>
+      </c>
+      <c r="F695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J695" s="11">
+        <v>7.661885357875487</v>
+      </c>
+      <c r="K695" s="9">
+        <v>4.31857047257225</v>
+      </c>
+      <c r="L695" s="9">
+        <v>15.6</v>
+      </c>
+      <c r="M695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U695" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V695" s="11">
+        <v>87.10519271948608</v>
+      </c>
+    </row>
+    <row r="696" spans="1:22">
+      <c r="A696" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B696" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C696" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D696" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E696" s="8">
+        <v>139.989664</v>
+      </c>
+      <c r="F696" s="9">
+        <v>68.97923279422618</v>
+      </c>
+      <c r="G696" s="9">
+        <v>-6.563535963905689</v>
+      </c>
+      <c r="H696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I696" s="9">
+        <v>94.56183874333236</v>
+      </c>
+      <c r="J696" s="11">
+        <v>3.225931242158093</v>
+      </c>
+      <c r="K696" s="9">
+        <v>3.15112550023693</v>
+      </c>
+      <c r="L696" s="9">
+        <v>-34.3</v>
+      </c>
+      <c r="M696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R696" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U696" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V696" s="11">
+        <v>66.00669164882227</v>
+      </c>
+    </row>
+    <row r="697" spans="1:22">
+      <c r="A697" s="6" t="s">
         <v>1438</v>
       </c>
-      <c r="B683" s="7" t="s">
+      <c r="B697" s="7" t="s">
         <v>1439</v>
       </c>
-      <c r="C683" s="7" t="s">
+      <c r="C697" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D683" s="7" t="s">
+      <c r="D697" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E697" s="8">
+        <v>10098.741248</v>
+      </c>
+      <c r="F697" s="9">
+        <v>20.477195149346</v>
+      </c>
+      <c r="G697" s="9">
+        <v>16.54853951890034</v>
+      </c>
+      <c r="H697" s="9">
+        <v>15.94916966003723</v>
+      </c>
+      <c r="I697" s="9">
+        <v>21.42672873942377</v>
+      </c>
+      <c r="J697" s="11">
+        <v>17.95710263675431</v>
+      </c>
+      <c r="K697" s="9">
+        <v>1.82609388112129</v>
+      </c>
+      <c r="L697" s="9">
+        <v>21.4</v>
+      </c>
+      <c r="M697" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="N697" s="9">
+        <v>20.39838349932646</v>
+      </c>
+      <c r="O697" s="7" t="s">
+        <v>1440</v>
+      </c>
+      <c r="P697" s="9">
+        <v>17.12488350419385</v>
+      </c>
+      <c r="Q697" s="9">
+        <v>0.4816441383707154</v>
+      </c>
+      <c r="R697" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S697" s="9">
+        <v>6.833357346207379</v>
+      </c>
+      <c r="T697" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U697" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V697" s="11">
+        <v>74.52087794432549</v>
+      </c>
+    </row>
+    <row r="698" spans="1:22">
+      <c r="A698" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B698" s="7" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C698" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D698" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E683" s="8">
-        <v>709.240768</v>
-      </c>
-      <c r="F683" s="9">
-        <v>10.67763396984633</v>
-      </c>
-      <c r="G683" s="9">
-        <v>7.02173275861261</v>
-      </c>
-      <c r="H683" s="9">
-        <v>-329.46879962913</v>
-      </c>
-      <c r="I683" s="9">
-        <v>10.5115828482743</v>
-      </c>
-      <c r="J683" s="11">
-        <v>7.821643636363636</v>
-      </c>
-      <c r="K683" s="9">
-        <v>8.540823191934729</v>
-      </c>
-      <c r="L683" s="9">
-        <v>5.800000000000001</v>
-      </c>
-      <c r="M683" s="7" t="s">
-        <v>1440</v>
-      </c>
-      <c r="N683" s="9">
-        <v>77.68604388147477</v>
-      </c>
-      <c r="O683" s="7" t="s">
-        <v>1441</v>
-      </c>
-      <c r="P683" s="9">
-        <v>6.995661605206083</v>
-      </c>
-      <c r="Q683" s="9">
-        <v>3.181355994018062</v>
-      </c>
-      <c r="R683" s="7" t="s">
+      <c r="E698" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F698" s="9">
+        <v>9.415314575424901</v>
+      </c>
+      <c r="G698" s="9">
+        <v>3.39669120871233</v>
+      </c>
+      <c r="H698" s="9">
+        <v>3.66426562798681</v>
+      </c>
+      <c r="I698" s="9">
+        <v>13.45915131394612</v>
+      </c>
+      <c r="J698" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K698" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L698" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M698" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N698" s="9">
+        <v>43.05303752030628</v>
+      </c>
+      <c r="O698" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="P698" s="9">
+        <v>32.54437343112995</v>
+      </c>
+      <c r="Q698" s="9">
+        <v>2.909940133716239</v>
+      </c>
+      <c r="R698" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="S683" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T683" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U683" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V683" s="11">
-        <v>41.40604925053533</v>
-      </c>
-    </row>
-    <row r="684" spans="1:22">
-      <c r="A684" s="6" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B684" s="7" t="s">
+      <c r="S698" s="9">
+        <v>134.0457960019367</v>
+      </c>
+      <c r="T698" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U698" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V698" s="11">
+        <v>3.592344753747323</v>
+      </c>
+    </row>
+    <row r="699" spans="1:22">
+      <c r="A699" s="6" t="s">
         <v>1443</v>
       </c>
-      <c r="C684" s="7" t="s">
+      <c r="B699" s="7" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C699" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D684" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E684" s="8">
-        <v>316416.196608</v>
-      </c>
-      <c r="F684" s="9">
-        <v>7.105064761849279</v>
-      </c>
-      <c r="G684" s="9">
-        <v>5.982680344439021</v>
-      </c>
-      <c r="H684" s="9">
-        <v>8.718370604228911</v>
-      </c>
-      <c r="I684" s="9">
-        <v>11.96801965473218</v>
-      </c>
-      <c r="J684" s="11">
-        <v>29.6417692182084</v>
-      </c>
-      <c r="K684" s="9">
-        <v>1.79131150831129</v>
-      </c>
-      <c r="L684" s="9">
-        <v>24.7</v>
-      </c>
-      <c r="M684" s="7" t="s">
-        <v>1444</v>
-      </c>
-      <c r="N684" s="9">
-        <v>27.31445406924166</v>
-      </c>
-      <c r="O684" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="P684" s="9">
-        <v>49.49564736769378</v>
-      </c>
-      <c r="Q684" s="9">
-        <v>3.371631767229602</v>
-      </c>
-      <c r="R684" s="7" t="s">
+      <c r="D699" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E699" s="8">
+        <v>92727.803904</v>
+      </c>
+      <c r="F699" s="9">
+        <v>12.16832467586076</v>
+      </c>
+      <c r="G699" s="9">
+        <v>11.8119306083982</v>
+      </c>
+      <c r="H699" s="9">
+        <v>25.2816769962534</v>
+      </c>
+      <c r="I699" s="9">
+        <v>11.87076192256857</v>
+      </c>
+      <c r="J699" s="11">
+        <v>15.2467708167422</v>
+      </c>
+      <c r="K699" s="9">
+        <v>5.70433024109592</v>
+      </c>
+      <c r="L699" s="9">
+        <v>10.3</v>
+      </c>
+      <c r="M699" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="N699" s="9">
+        <v>12.7768650489863</v>
+      </c>
+      <c r="O699" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="P699" s="9">
+        <v>71.59090909090908</v>
+      </c>
+      <c r="Q699" s="9">
+        <v>1.149159869153103</v>
+      </c>
+      <c r="R699" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="S684" s="9">
-        <v>30.61461997847589</v>
-      </c>
-      <c r="T684" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U684" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V684" s="11">
-        <v>80.95503211991435</v>
-      </c>
-    </row>
-    <row r="685" spans="1:22">
-      <c r="A685" s="6" t="s">
-        <v>1445</v>
-      </c>
-      <c r="B685" s="7" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C685" s="7" t="s">
+      <c r="S699" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T699" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U699" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="V699" s="11">
+        <v>67.19860813704497</v>
+      </c>
+    </row>
+    <row r="700" spans="1:22">
+      <c r="A700" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="B700" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="C700" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D700" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E700" s="8">
+        <v>147615.596544</v>
+      </c>
+      <c r="F700" s="9">
+        <v>15.94268540560896</v>
+      </c>
+      <c r="G700" s="9">
+        <v>1.19662953118814</v>
+      </c>
+      <c r="H700" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I700" s="9">
+        <v>18.39474460776682</v>
+      </c>
+      <c r="J700" s="11">
+        <v>7.826613960296955</v>
+      </c>
+      <c r="K700" s="9">
+        <v>8.384361437248861</v>
+      </c>
+      <c r="L700" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="M700" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="N700" s="9">
+        <v>18.86635609511109</v>
+      </c>
+      <c r="O700" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="P700" s="9">
+        <v>128.5714285714286</v>
+      </c>
+      <c r="Q700" s="9">
+        <v>1.895410792529631</v>
+      </c>
+      <c r="R700" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S700" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T700" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U700" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V700" s="11">
+        <v>88.94245182012848</v>
+      </c>
+    </row>
+    <row r="701" spans="1:22">
+      <c r="A701" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B701" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C701" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D701" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E701" s="8">
+        <v>12465.329152</v>
+      </c>
+      <c r="F701" s="9">
+        <v>18.3357672256623</v>
+      </c>
+      <c r="G701" s="9">
+        <v>11.34875053232618</v>
+      </c>
+      <c r="H701" s="9">
+        <v>162.6826764963662</v>
+      </c>
+      <c r="I701" s="9">
+        <v>24.64990259395278</v>
+      </c>
+      <c r="J701" s="11">
+        <v>11.7959601299469</v>
+      </c>
+      <c r="K701" s="9">
+        <v>4.39559184774585</v>
+      </c>
+      <c r="L701" s="9">
+        <v>12.7</v>
+      </c>
+      <c r="M701" s="7" t="s">
+        <v>1447</v>
+      </c>
+      <c r="N701" s="9">
+        <v>24.41986345619947</v>
+      </c>
+      <c r="O701" s="7" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P701" s="9">
+        <v>22.48766554141781</v>
+      </c>
+      <c r="Q701" s="9">
+        <v>11.57935981187805</v>
+      </c>
+      <c r="R701" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S701" s="9">
+        <v>30557.33041489141</v>
+      </c>
+      <c r="T701" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U701" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V701" s="11">
+        <v>45.06932548179872</v>
+      </c>
+    </row>
+    <row r="702" spans="1:22">
+      <c r="A702" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B702" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C702" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D702" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E702" s="8">
+        <v>22147.784704</v>
+      </c>
+      <c r="F702" s="9">
+        <v>27.29368094718512</v>
+      </c>
+      <c r="G702" s="9">
+        <v>23.60541611051562</v>
+      </c>
+      <c r="H702" s="9">
+        <v>31.35753410432825</v>
+      </c>
+      <c r="I702" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J702" s="11">
+        <v>27.76022696184645</v>
+      </c>
+      <c r="K702" s="9">
+        <v>1.53875434746505</v>
+      </c>
+      <c r="L702" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="M702" s="7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="N702" s="9">
+        <v>21.2542084254435</v>
+      </c>
+      <c r="O702" s="7" t="s">
+        <v>1452</v>
+      </c>
+      <c r="P702" s="9">
+        <v>27.13397399660827</v>
+      </c>
+      <c r="Q702" s="9">
+        <v>8.44242995511228</v>
+      </c>
+      <c r="R702" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S702" s="9">
+        <v>1.749078371350507</v>
+      </c>
+      <c r="T702" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U702" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V702" s="11">
+        <v>32.0904710920771</v>
+      </c>
+    </row>
+    <row r="703" spans="1:22">
+      <c r="A703" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B703" s="7" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C703" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D703" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E703" s="8">
+        <v>4596.016128</v>
+      </c>
+      <c r="F703" s="9">
+        <v>4.0228449328489</v>
+      </c>
+      <c r="G703" s="9">
+        <v>-1.42599432456186</v>
+      </c>
+      <c r="H703" s="9">
+        <v>51.57783481534709</v>
+      </c>
+      <c r="I703" s="9">
+        <v>11.12084488599668</v>
+      </c>
+      <c r="J703" s="11">
+        <v>31.74922366438976</v>
+      </c>
+      <c r="K703" s="9">
+        <v>3.09196861025462</v>
+      </c>
+      <c r="L703" s="9">
+        <v>14.1</v>
+      </c>
+      <c r="M703" s="7" t="s">
+        <v>1454</v>
+      </c>
+      <c r="N703" s="9">
+        <v>29.75735645069985</v>
+      </c>
+      <c r="O703" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="P703" s="9">
+        <v>1506.869009584664</v>
+      </c>
+      <c r="Q703" s="9">
+        <v>5.890932501581734</v>
+      </c>
+      <c r="R703" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S703" s="9">
+        <v>326.8664985984774</v>
+      </c>
+      <c r="T703" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U703" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V703" s="11">
+        <v>60.26258029978587</v>
+      </c>
+    </row>
+    <row r="704" spans="1:22">
+      <c r="A704" s="6" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B704" s="7" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C704" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D704" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E704" s="8">
+        <v>10411.935744</v>
+      </c>
+      <c r="F704" s="9">
+        <v>7.49516988342678</v>
+      </c>
+      <c r="G704" s="9">
+        <v>5.433517399693049</v>
+      </c>
+      <c r="H704" s="9">
+        <v>200</v>
+      </c>
+      <c r="I704" s="9">
+        <v>21.17194829228418</v>
+      </c>
+      <c r="J704" s="11">
+        <v>9.194940017024711</v>
+      </c>
+      <c r="K704" s="9">
+        <v>2.72871941381047</v>
+      </c>
+      <c r="L704" s="9">
+        <v>9</v>
+      </c>
+      <c r="M704" s="7" t="s">
+        <v>1457</v>
+      </c>
+      <c r="N704" s="9">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="O704" s="7" t="s">
+        <v>1458</v>
+      </c>
+      <c r="P704" s="9">
+        <v>29.95391705069124</v>
+      </c>
+      <c r="Q704" s="9">
+        <v>0.1461085646552368</v>
+      </c>
+      <c r="R704" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S704" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T704" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U704" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V704" s="11">
+        <v>89.89079229122056</v>
+      </c>
+    </row>
+    <row r="705" spans="1:22">
+      <c r="A705" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B705" s="7" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C705" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D705" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E705" s="8">
+        <v>82539.92140799999</v>
+      </c>
+      <c r="F705" s="9">
+        <v>8.44733011792461</v>
+      </c>
+      <c r="G705" s="9">
+        <v>5.14659991435997</v>
+      </c>
+      <c r="H705" s="9">
+        <v>200</v>
+      </c>
+      <c r="I705" s="9">
+        <v>13.78704959722941</v>
+      </c>
+      <c r="J705" s="11">
+        <v>145.1852238831085</v>
+      </c>
+      <c r="K705" s="9">
+        <v>0.8472272859860199</v>
+      </c>
+      <c r="L705" s="9">
+        <v>33.1</v>
+      </c>
+      <c r="M705" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N705" s="9">
+        <v>16.97306459514074</v>
+      </c>
+      <c r="O705" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P705" s="9">
+        <v>21.42857142857142</v>
+      </c>
+      <c r="Q705" s="9">
+        <v>2.563643962950055</v>
+      </c>
+      <c r="R705" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S705" s="9">
+        <v>23.78063725490197</v>
+      </c>
+      <c r="T705" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U705" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V705" s="11">
+        <v>50.62901498929336</v>
+      </c>
+    </row>
+    <row r="706" spans="1:22">
+      <c r="A706" s="6" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B706" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C706" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="D685" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E685" s="8">
-        <v>246435.217408</v>
-      </c>
-      <c r="F685" s="9">
-        <v>2.46623396135968</v>
-      </c>
-      <c r="G685" s="9">
-        <v>0.87130980675874</v>
-      </c>
-      <c r="H685" s="9">
-        <v>337.6522296549983</v>
-      </c>
-      <c r="I685" s="9">
-        <v>11.48889112620727</v>
-      </c>
-      <c r="J685" s="11">
-        <v>4.799222930846946</v>
-      </c>
-      <c r="K685" s="9">
-        <v>-379.9774379883748</v>
-      </c>
-      <c r="L685" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="M685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S685" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T685" s="12" t="s">
+      <c r="D706" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E706" s="8">
+        <v>26033.324032</v>
+      </c>
+      <c r="F706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J706" s="11">
+        <v>2.447425401459854</v>
+      </c>
+      <c r="K706" s="9">
+        <v>3.94734465232657</v>
+      </c>
+      <c r="L706" s="9">
+        <v>-3.3</v>
+      </c>
+      <c r="M706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U706" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V706" s="11">
+        <v>73.06263383297645</v>
+      </c>
+    </row>
+    <row r="707" spans="1:22">
+      <c r="A707" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B707" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C707" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D707" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E707" s="8">
+        <v>52635.680768</v>
+      </c>
+      <c r="F707" s="9">
+        <v>12.95310160476074</v>
+      </c>
+      <c r="G707" s="9">
+        <v>10.98132023977103</v>
+      </c>
+      <c r="H707" s="9">
+        <v>200</v>
+      </c>
+      <c r="I707" s="9">
+        <v>11.52721423938888</v>
+      </c>
+      <c r="J707" s="11">
+        <v>26.55906833398058</v>
+      </c>
+      <c r="K707" s="9">
+        <v>1.59563815979103</v>
+      </c>
+      <c r="L707" s="9">
+        <v>16.9</v>
+      </c>
+      <c r="M707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R707" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S707" s="9">
+        <v>33.0858372417175</v>
+      </c>
+      <c r="T707" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="U685" s="12" t="s">
+      <c r="U707" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V707" s="11">
+        <v>60.03533190578159</v>
+      </c>
+    </row>
+    <row r="708" spans="1:22">
+      <c r="A708" s="6" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B708" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C708" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D708" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E708" s="8">
+        <v>16507.032576</v>
+      </c>
+      <c r="F708" s="9">
+        <v>15.58608160554067</v>
+      </c>
+      <c r="G708" s="9">
+        <v>6.58630328441649</v>
+      </c>
+      <c r="H708" s="9">
+        <v>-22.15173053427627</v>
+      </c>
+      <c r="I708" s="9">
+        <v>12.05096674017734</v>
+      </c>
+      <c r="J708" s="11">
+        <v>5.530745092896175</v>
+      </c>
+      <c r="K708" s="9">
+        <v>5.30455743616265</v>
+      </c>
+      <c r="L708" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="M708" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="N708" s="9">
+        <v>63.40903066183618</v>
+      </c>
+      <c r="O708" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="P708" s="9">
+        <v>12600</v>
+      </c>
+      <c r="Q708" s="9">
+        <v>8.897851712612685</v>
+      </c>
+      <c r="R708" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S708" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T708" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U708" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="V685" s="11">
-        <v>57.62419700214133</v>
+      <c r="V708" s="11">
+        <v>90.01043897216273</v>
+      </c>
+    </row>
+    <row r="709" spans="1:22">
+      <c r="A709" s="6" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B709" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C709" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D709" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E709" s="8">
+        <v>71293.7472</v>
+      </c>
+      <c r="F709" s="9">
+        <v>21.68056339811111</v>
+      </c>
+      <c r="G709" s="9">
+        <v>17.82389050341457</v>
+      </c>
+      <c r="H709" s="9">
+        <v>-4.58377475435458</v>
+      </c>
+      <c r="I709" s="9">
+        <v>20.99548243827234</v>
+      </c>
+      <c r="J709" s="11">
+        <v>19.80757872812305</v>
+      </c>
+      <c r="K709" s="9">
+        <v>2.22519508695427</v>
+      </c>
+      <c r="L709" s="9">
+        <v>10</v>
+      </c>
+      <c r="M709" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="N709" s="9">
+        <v>32.60474351348408</v>
+      </c>
+      <c r="O709" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="P709" s="9">
+        <v>336.6197183098592</v>
+      </c>
+      <c r="Q709" s="9">
+        <v>10.40315990402382</v>
+      </c>
+      <c r="R709" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S709" s="9">
+        <v>72.65687465263815</v>
+      </c>
+      <c r="T709" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U709" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V709" s="11">
+        <v>50.49036402569592</v>
+      </c>
+    </row>
+    <row r="710" spans="1:22">
+      <c r="A710" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B710" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C710" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D710" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E710" s="8">
+        <v>637.646208</v>
+      </c>
+      <c r="F710" s="9">
+        <v>22.0490862132175</v>
+      </c>
+      <c r="G710" s="9">
+        <v>-2.23702343652924</v>
+      </c>
+      <c r="H710" s="9">
+        <v>200</v>
+      </c>
+      <c r="I710" s="9">
+        <v>58.97856558496406</v>
+      </c>
+      <c r="J710" s="11">
+        <v>6.264878590717654</v>
+      </c>
+      <c r="K710" s="9">
+        <v>18.09633971821565</v>
+      </c>
+      <c r="L710" s="9">
+        <v>-1.2</v>
+      </c>
+      <c r="M710" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="N710" s="9">
+        <v>38.46849508383634</v>
+      </c>
+      <c r="O710" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="P710" s="9">
+        <v>34.99265545944181</v>
+      </c>
+      <c r="Q710" s="9">
+        <v>0.7618225630187242</v>
+      </c>
+      <c r="R710" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S710" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T710" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U710" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V710" s="11">
+        <v>67.06745182012848</v>
       </c>
     </row>
   </sheetData>
@@ -48118,8 +49887,8 @@
     <mergeCell ref="A572:V572"/>
     <mergeCell ref="A600:V600"/>
     <mergeCell ref="A628:V628"/>
-    <mergeCell ref="A631:V631"/>
-    <mergeCell ref="A659:V659"/>
+    <mergeCell ref="A656:V656"/>
+    <mergeCell ref="A684:V684"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
+++ b/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13133" uniqueCount="2505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13121" uniqueCount="2491">
   <si>
     <t>INVESTMENT ARCHETYPES  ·  CROSS-COHORT SUMMARY</t>
   </si>
   <si>
-    <t>2026-06-27  ·  18,680 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  246 backlog-inflect  ·  1554 triple-lens</t>
+    <t>2026-06-27  ·  18,680 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  246 backlog-inflect  ·  1556 triple-lens</t>
   </si>
   <si>
     <t>Each archetype is a structurally distinct setup. A name may appear in multiple cohorts — the Triple-Lens Conviction block at the end shows names with ≥ 3 archetype overlaps. Segment and backlog data come from full SEC EDGAR XBRL dimensional parsing (edgartools); fundamentals from Lindy multi-method ROIC reconciliation. Every cohort row shows the specific segment name, backlog concept, and inflection magnitude that drove the flag.</t>
@@ -1045,7 +1045,7 @@
     <t>Royalty</t>
   </si>
   <si>
-    <t>4. DEEP VALUE QUALITY — EV/EBIT ≤ 8 WITH ROIC ≥ 10 %  ·  108 NAMES</t>
+    <t>4. DEEP VALUE QUALITY — EV/EBIT ≤ 8 WITH ROIC ≥ 10 %  ·  110 NAMES</t>
   </si>
   <si>
     <t>THC</t>
@@ -2209,7 +2209,7 @@
     <t>NEOWIZ HOLDINDS</t>
   </si>
   <si>
-    <t>16. HIDDEN FCF GENERATORS — FCF MARGIN ≥ 10 % + EV/EBITDA ≤ 12  ·  76 NAMES</t>
+    <t>16. HIDDEN FCF GENERATORS — FCF MARGIN ≥ 10 % + EV/EBITDA ≤ 12  ·  79 NAMES</t>
   </si>
   <si>
     <t>FCAP</t>
@@ -2401,15 +2401,15 @@
     <t>Outside North Amer</t>
   </si>
   <si>
+    <t>FMCQF</t>
+  </si>
+  <si>
+    <t>Fresenius Medical Care AG</t>
+  </si>
+  <si>
     <t>FMS</t>
   </si>
   <si>
-    <t>Fresenius Medical Care AG</t>
-  </si>
-  <si>
-    <t>FMCQF</t>
-  </si>
-  <si>
     <t>17. REINVESTMENT HEROES — HIGH ROIIC + SIGNIFICANT CAPITAL DEPLOYMENT  ·  462 NAMES</t>
   </si>
   <si>
@@ -7237,7 +7237,7 @@
     <t>Scandinavian Investment Gr</t>
   </si>
   <si>
-    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  3988 NAMES</t>
+    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  3989 NAMES</t>
   </si>
   <si>
     <t>G0I.SI</t>
@@ -7414,7 +7414,7 @@
     <t>SILVER BULL RESOURCES INC</t>
   </si>
   <si>
-    <t>26. TRIPLE-LENS CONVICTION — PASSES ≥ 3 BUY-SIDE ARCHETYPES  ·  1554 NAMES</t>
+    <t>26. TRIPLE-LENS CONVICTION — PASSES ≥ 3 BUY-SIDE ARCHETYPES  ·  1556 NAMES</t>
   </si>
   <si>
     <t>Advanced Micro Devices, In</t>
@@ -7429,25 +7429,22 @@
     <t>CRESTEC INC</t>
   </si>
   <si>
-    <t>Investment Banking</t>
-  </si>
-  <si>
-    <t>ILMN</t>
-  </si>
-  <si>
-    <t>Illumina, Inc.</t>
-  </si>
-  <si>
-    <t>Sequencing</t>
-  </si>
-  <si>
-    <t>WTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watts Water Technologies, </t>
-  </si>
-  <si>
-    <t>Specialty</t>
+    <t>General Dynamics Corporati</t>
+  </si>
+  <si>
+    <t>Contracts Accounte</t>
+  </si>
+  <si>
+    <t>7516.T</t>
+  </si>
+  <si>
+    <t>KOHNAN SHOJI</t>
+  </si>
+  <si>
+    <t>Modine Manufacturing Compa</t>
+  </si>
+  <si>
+    <t>Digital and Licens</t>
   </si>
   <si>
     <t>PFE</t>
@@ -7462,73 +7459,34 @@
     <t>Elrexfio</t>
   </si>
   <si>
-    <t>GDS.PA</t>
-  </si>
-  <si>
-    <t>RAMSAY GENERALE DE SANTE</t>
-  </si>
-  <si>
-    <t>EMN</t>
-  </si>
-  <si>
-    <t>Eastman Chemical Company</t>
-  </si>
-  <si>
-    <t>All Foreign Countr</t>
-  </si>
-  <si>
-    <t>Additives And Func</t>
-  </si>
-  <si>
-    <t>EHC</t>
-  </si>
-  <si>
-    <t>Encompass Health Corporati</t>
-  </si>
-  <si>
-    <t>Inpatient Rehabili</t>
-  </si>
-  <si>
-    <t>ORI</t>
-  </si>
-  <si>
-    <t>Old Republic International</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>GE Aerospace</t>
-  </si>
-  <si>
-    <t>Equity method inve</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>PayPal Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Transaction revenu</t>
-  </si>
-  <si>
-    <t>Revenues From Othe</t>
-  </si>
-  <si>
-    <t>Product and Servic</t>
-  </si>
-  <si>
-    <t>First Major Custom</t>
-  </si>
-  <si>
-    <t>8030.T</t>
-  </si>
-  <si>
-    <t>CHUO GYORUI CO LTD</t>
-  </si>
-  <si>
-    <t>L3Harris Technologies, Inc</t>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>Neurocrine Biosciences, In</t>
+  </si>
+  <si>
+    <t>CRENESSITY net pro</t>
+  </si>
+  <si>
+    <t>7264.T</t>
+  </si>
+  <si>
+    <t>MURO CORPORATION</t>
+  </si>
+  <si>
+    <t>FFIV</t>
+  </si>
+  <si>
+    <t>F5, Inc.</t>
+  </si>
+  <si>
+    <t>Total Americas</t>
+  </si>
+  <si>
+    <t>JBI</t>
+  </si>
+  <si>
+    <t>Janus International Group,</t>
   </si>
 </sst>
 </file>
@@ -31848,7 +31806,7 @@
         <v>29</v>
       </c>
       <c r="E384" s="8">
-        <v>11623.477248</v>
+        <v>11279.715328</v>
       </c>
       <c r="F384" s="9">
         <v>9.84352572669953</v>
@@ -31863,10 +31821,10 @@
         <v>7.36287272875356</v>
       </c>
       <c r="J384" s="11">
-        <v>8.266542903324851</v>
+        <v>8.133928882692162</v>
       </c>
       <c r="K384" s="9">
-        <v>14.38746602517546</v>
+        <v>14.82594011791004</v>
       </c>
       <c r="L384" s="9">
         <v>-5.5</v>
@@ -31899,7 +31857,7 @@
         <v>30</v>
       </c>
       <c r="V384" s="11">
-        <v>69.4595824411135</v>
+        <v>71.07441113490363</v>
       </c>
     </row>
     <row r="385" spans="1:22">
@@ -31916,7 +31874,7 @@
         <v>29</v>
       </c>
       <c r="E385" s="8">
-        <v>11279.715328</v>
+        <v>11623.477248</v>
       </c>
       <c r="F385" s="9">
         <v>9.84352572669953</v>
@@ -31931,10 +31889,10 @@
         <v>7.36287272875356</v>
       </c>
       <c r="J385" s="11">
-        <v>8.133928882692162</v>
+        <v>8.266542903324851</v>
       </c>
       <c r="K385" s="9">
-        <v>14.82594011791004</v>
+        <v>14.38746602517546</v>
       </c>
       <c r="L385" s="9">
         <v>-5.5</v>
@@ -31967,7 +31925,7 @@
         <v>30</v>
       </c>
       <c r="V385" s="11">
-        <v>71.07441113490363</v>
+        <v>69.4595824411135</v>
       </c>
     </row>
     <row r="387" spans="1:22" ht="22" customHeight="1">
@@ -35211,8 +35169,8 @@
       <c r="T436" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U436" s="10" t="s">
-        <v>30</v>
+      <c r="U436" s="11">
+        <v>18.27730411367763</v>
       </c>
       <c r="V436" s="11">
         <v>70.76231263383298</v>
@@ -43575,8 +43533,8 @@
       <c r="T559" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U559" s="10" t="s">
-        <v>30</v>
+      <c r="U559" s="11">
+        <v>11.69403989340236</v>
       </c>
       <c r="V559" s="11">
         <v>75.69111349036403</v>
@@ -59046,10 +59004,10 @@
         <v>30</v>
       </c>
       <c r="O790" s="8">
-        <v>3593.527898567871</v>
+        <v>3415.832898567871</v>
       </c>
       <c r="P790" s="11">
-        <v>0.0011498449759209</v>
+        <v>0.0012096610468657</v>
       </c>
       <c r="Q790" s="9">
         <v>-7.923636466348261</v>
@@ -59114,10 +59072,10 @@
         <v>30</v>
       </c>
       <c r="O791" s="8">
-        <v>2045.064322196083</v>
+        <v>2016.193322196083</v>
       </c>
       <c r="P791" s="11">
-        <v>0.0008801679147514</v>
+        <v>0.0008927715314716</v>
       </c>
       <c r="Q791" s="9">
         <v>-28.90813072165297</v>
@@ -59182,10 +59140,10 @@
         <v>0.0534529753720722</v>
       </c>
       <c r="O792" s="8">
-        <v>308.4474645</v>
+        <v>298.6534645</v>
       </c>
       <c r="P792" s="11">
-        <v>0.0071843676964314</v>
+        <v>0.0074199708471823</v>
       </c>
       <c r="Q792" s="9">
         <v>5.05593634957493</v>
@@ -59250,10 +59208,10 @@
         <v>0.4801656793921028</v>
       </c>
       <c r="O793" s="8">
-        <v>98.13520722165775</v>
+        <v>146.1832072216578</v>
       </c>
       <c r="P793" s="11">
-        <v>0.6426235984559292</v>
+        <v>0.4314038609398957</v>
       </c>
       <c r="Q793" s="9">
         <v>5.31940257538757</v>
@@ -59386,10 +59344,10 @@
         <v>9.229655872631827E-06</v>
       </c>
       <c r="O795" s="8">
-        <v>58.82066565805078</v>
+        <v>63.23466565805077</v>
       </c>
       <c r="P795" s="11">
-        <v>2.905441447968533E-05</v>
+        <v>2.702631511079109E-05</v>
       </c>
       <c r="Q795" s="9">
         <v>-14.94478982766374</v>
@@ -59454,10 +59412,10 @@
         <v>30</v>
       </c>
       <c r="O796" s="8">
-        <v>28.99893278182984</v>
+        <v>32.50425478182984</v>
       </c>
       <c r="P796" s="11">
-        <v>0.0015354013313172</v>
+        <v>0.0013698206680588</v>
       </c>
       <c r="Q796" s="9">
         <v>-192.9559070228838</v>
@@ -59522,10 +59480,10 @@
         <v>30</v>
       </c>
       <c r="O797" s="8">
-        <v>1860.478791775177</v>
+        <v>1703.101791775177</v>
       </c>
       <c r="P797" s="11">
-        <v>0.0026874802454637</v>
+        <v>0.002935819822483</v>
       </c>
       <c r="Q797" s="9">
         <v>4.09292371790951</v>
@@ -59726,10 +59684,10 @@
         <v>0.1821366024518388</v>
       </c>
       <c r="O800" s="8">
-        <v>24.43764225</v>
+        <v>24.20564725</v>
       </c>
       <c r="P800" s="11">
-        <v>0.0085114594064408</v>
+        <v>0.0085930360734311</v>
       </c>
       <c r="Q800" s="9">
         <v>-84.36971799652343</v>
@@ -59794,7 +59752,7 @@
         <v>30</v>
       </c>
       <c r="O801" s="8">
-        <v>174.1593132094502</v>
+        <v>85.55931320945024</v>
       </c>
       <c r="P801" s="11">
         <v>0</v>
@@ -59862,10 +59820,10 @@
         <v>30</v>
       </c>
       <c r="O802" s="8">
-        <v>11.49093503085476</v>
+        <v>11.35593503085476</v>
       </c>
       <c r="P802" s="11">
-        <v>0.0363765001610062</v>
+        <v>0.0368089460589787</v>
       </c>
       <c r="Q802" s="9">
         <v>-23.4322448250743</v>
@@ -59930,10 +59888,10 @@
         <v>0.0077674883923761</v>
       </c>
       <c r="O803" s="8">
-        <v>121.6679051485062</v>
+        <v>124.6889051485062</v>
       </c>
       <c r="P803" s="11">
-        <v>0.0248874178963142</v>
+        <v>0.0242844381093378</v>
       </c>
       <c r="Q803" s="9">
         <v>5.50919798972899</v>
@@ -59998,10 +59956,10 @@
         <v>30</v>
       </c>
       <c r="O804" s="8">
-        <v>90.87370453641176</v>
+        <v>83.32959753641177</v>
       </c>
       <c r="P804" s="11">
-        <v>0.0021853626526299</v>
+        <v>0.0023832108383005</v>
       </c>
       <c r="Q804" s="9">
         <v>-39.87834427298205</v>
@@ -60066,10 +60024,10 @@
         <v>0.1349228890864358</v>
       </c>
       <c r="O805" s="8">
-        <v>478.8987191348124</v>
+        <v>407.2467191348124</v>
       </c>
       <c r="P805" s="11">
-        <v>0.0763794066229337</v>
+        <v>0.08981778926963301</v>
       </c>
       <c r="Q805" s="9">
         <v>-27.68875261121275</v>
@@ -60134,10 +60092,10 @@
         <v>30</v>
       </c>
       <c r="O806" s="8">
-        <v>3561.385401522064</v>
+        <v>6168.685401522064</v>
       </c>
       <c r="P806" s="11">
-        <v>0.0192060089791931</v>
+        <v>0.0110882620117282</v>
       </c>
       <c r="Q806" s="9">
         <v>2.66863929893312</v>
@@ -60202,10 +60160,10 @@
         <v>30</v>
       </c>
       <c r="O807" s="8">
-        <v>48.97052133011818</v>
+        <v>88.19952133011817</v>
       </c>
       <c r="P807" s="11">
-        <v>0.2153744684256263</v>
+        <v>0.1195811478446021</v>
       </c>
       <c r="Q807" s="9">
         <v>-5.53381200735645</v>
@@ -60270,10 +60228,10 @@
         <v>0.1079811973656467</v>
       </c>
       <c r="O808" s="8">
-        <v>86.06846457688617</v>
-      </c>
-      <c r="P808" s="11">
-        <v>0.5057717738314379</v>
+        <v>-80.76153542311383</v>
+      </c>
+      <c r="P808" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="Q808" s="9">
         <v>-30.9163890684529</v>
@@ -60338,10 +60296,10 @@
         <v>30</v>
       </c>
       <c r="O809" s="8">
-        <v>488.6488407275962</v>
+        <v>482.5738407275962</v>
       </c>
       <c r="P809" s="11">
-        <v>0.0008574664771047</v>
+        <v>0.0008682609056642</v>
       </c>
       <c r="Q809" s="9">
         <v>-27.64249887755216</v>
@@ -60474,7 +60432,7 @@
         <v>30</v>
       </c>
       <c r="O811" s="8">
-        <v>2911.235683953965</v>
+        <v>2705.909683953965</v>
       </c>
       <c r="P811" s="11">
         <v>0</v>
@@ -60610,10 +60568,10 @@
         <v>0.050581338833265</v>
       </c>
       <c r="O813" s="8">
-        <v>2244.875886780533</v>
+        <v>1882.757886780533</v>
       </c>
       <c r="P813" s="11">
-        <v>0.04798127176397</v>
+        <v>0.0572096926303066</v>
       </c>
       <c r="Q813" s="9">
         <v>38.76866695640053</v>
@@ -60678,10 +60636,10 @@
         <v>0.0210824130692707</v>
       </c>
       <c r="O814" s="8">
-        <v>110.1124877091591</v>
+        <v>301.2234877091591</v>
       </c>
       <c r="P814" s="11">
-        <v>0.0188806923106784</v>
+        <v>0.0069018522287589</v>
       </c>
       <c r="Q814" s="9">
         <v>-7.002080052003739</v>
@@ -60746,10 +60704,10 @@
         <v>0.0557043385109801</v>
       </c>
       <c r="O815" s="8">
-        <v>3835.6261369468</v>
+        <v>4836.6261369468</v>
       </c>
       <c r="P815" s="11">
-        <v>0.0271142171543301</v>
+        <v>0.0215025923144127</v>
       </c>
       <c r="Q815" s="9">
         <v>2.07805985698824</v>
@@ -60814,10 +60772,10 @@
         <v>30</v>
       </c>
       <c r="O816" s="8">
-        <v>39.76181969904901</v>
+        <v>89.790819699049</v>
       </c>
       <c r="P816" s="11">
-        <v>0.2187525637869142</v>
+        <v>0.0968695912249492</v>
       </c>
       <c r="Q816" s="9">
         <v>-5.34485212061657</v>
@@ -61086,10 +61044,10 @@
         <v>0.0382982588989762</v>
       </c>
       <c r="O820" s="8">
-        <v>10995.61919360275</v>
+        <v>11011.60619360275</v>
       </c>
       <c r="P820" s="11">
-        <v>0.0050228185450558</v>
+        <v>0.0050155262573851</v>
       </c>
       <c r="Q820" s="9">
         <v>17.79581484188693</v>
@@ -61222,10 +61180,10 @@
         <v>30</v>
       </c>
       <c r="O822" s="8">
-        <v>51.97174673283005</v>
+        <v>165.59443673283</v>
       </c>
       <c r="P822" s="11">
-        <v>0.470024610209398</v>
+        <v>0.1475170330716612</v>
       </c>
       <c r="Q822" s="9">
         <v>-0.24148789738567</v>
@@ -61290,10 +61248,10 @@
         <v>30</v>
       </c>
       <c r="O823" s="8">
-        <v>60.26884763805008</v>
+        <v>173.8915376380501</v>
       </c>
       <c r="P823" s="11">
-        <v>0.4053171905111663</v>
+        <v>0.1404783713560928</v>
       </c>
       <c r="Q823" s="9">
         <v>-0.24148789738567</v>
@@ -61630,10 +61588,10 @@
         <v>30</v>
       </c>
       <c r="O828" s="8">
-        <v>107.931804</v>
+        <v>103.473736</v>
       </c>
       <c r="P828" s="11">
-        <v>0.0041746638460708</v>
+        <v>0.0043545252874603</v>
       </c>
       <c r="Q828" s="9">
         <v>0.18734908473256</v>
@@ -63189,8 +63147,8 @@
       <c r="D853" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E853" s="10" t="s">
-        <v>30</v>
+      <c r="E853" s="8">
+        <v>55444.61966705322</v>
       </c>
       <c r="F853" s="9">
         <v>2.87828660024318</v>
@@ -70720,61 +70678,61 @@
     </row>
     <row r="972" spans="1:22">
       <c r="A972" s="6" t="s">
-        <v>130</v>
+        <v>1459</v>
       </c>
       <c r="B972" s="7" t="s">
-        <v>131</v>
+        <v>1460</v>
       </c>
       <c r="C972" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D972" s="7" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E972" s="8">
-        <v>3569.760046005249</v>
+        <v>23249.096704</v>
       </c>
       <c r="F972" s="9">
-        <v>44.56422400643385</v>
+        <v>10.58799092293385</v>
       </c>
       <c r="G972" s="9">
-        <v>39.32576921819311</v>
-      </c>
-      <c r="H972" s="10" t="s">
-        <v>30</v>
+        <v>-0.28771197424686</v>
+      </c>
+      <c r="H972" s="9">
+        <v>-28.16427067427359</v>
       </c>
       <c r="I972" s="9">
-        <v>44.16783713667234</v>
+        <v>15.2922875171542</v>
       </c>
       <c r="J972" s="11">
-        <v>4.12189438130252</v>
-      </c>
-      <c r="K972" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L972" s="10" t="s">
-        <v>30</v>
+        <v>7.34889280734496</v>
+      </c>
+      <c r="K972" s="9">
+        <v>-4.3921347181816</v>
+      </c>
+      <c r="L972" s="9">
+        <v>-16.9</v>
       </c>
       <c r="M972" s="7" t="s">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="N972" s="9">
-        <v>69.19229807451863</v>
+        <v>83.23873211902226</v>
       </c>
       <c r="O972" s="7" t="s">
-        <v>132</v>
+        <v>1462</v>
       </c>
       <c r="P972" s="9">
-        <v>0.4902850917014811</v>
+        <v>66.5089585090408</v>
       </c>
       <c r="Q972" s="9">
-        <v>1.638323589729629</v>
-      </c>
-      <c r="R972" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S972" s="9">
-        <v>10.69455163709715</v>
+        <v>61.17457010769595</v>
+      </c>
+      <c r="R972" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S972" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T972" s="10" t="s">
         <v>30</v>
@@ -70783,151 +70741,151 @@
         <v>41</v>
       </c>
       <c r="V972" s="11">
-        <v>26.81986081370449</v>
+        <v>47.91327623126338</v>
       </c>
     </row>
     <row r="973" spans="1:22">
       <c r="A973" s="6" t="s">
-        <v>1083</v>
+        <v>130</v>
       </c>
       <c r="B973" s="7" t="s">
-        <v>2467</v>
+        <v>131</v>
       </c>
       <c r="C973" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D973" s="7" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="E973" s="8">
-        <v>762322.092032</v>
+        <v>3569.760046005249</v>
       </c>
       <c r="F973" s="9">
-        <v>14.39909228246559</v>
+        <v>44.56422400643385</v>
       </c>
       <c r="G973" s="9">
-        <v>0.76076645797761</v>
-      </c>
-      <c r="H973" s="9">
-        <v>47.26579989976284</v>
+        <v>39.32576921819311</v>
+      </c>
+      <c r="H973" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I973" s="9">
-        <v>17.08548321355481</v>
+        <v>44.16783713667234</v>
       </c>
       <c r="J973" s="11">
-        <v>101.4597684119986</v>
-      </c>
-      <c r="K973" s="9">
-        <v>0.94099004226403</v>
-      </c>
-      <c r="L973" s="9">
-        <v>37.8</v>
+        <v>4.12189438130252</v>
+      </c>
+      <c r="K973" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L973" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M973" s="7" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="N973" s="9">
-        <v>24.53293446971835</v>
+        <v>69.19229807451863</v>
       </c>
       <c r="O973" s="7" t="s">
-        <v>1085</v>
+        <v>132</v>
       </c>
       <c r="P973" s="9">
-        <v>467.7697841726618</v>
+        <v>0.4902850917014811</v>
       </c>
       <c r="Q973" s="9">
-        <v>10.34555214833951</v>
+        <v>1.638323589729629</v>
       </c>
       <c r="R973" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="S973" s="9">
-        <v>178.9746882258184</v>
-      </c>
-      <c r="T973" s="12" t="s">
-        <v>41</v>
+        <v>10.69455163709715</v>
+      </c>
+      <c r="T973" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="U973" s="12" t="s">
         <v>41</v>
       </c>
       <c r="V973" s="11">
-        <v>56.21306209850107</v>
+        <v>26.81986081370449</v>
       </c>
     </row>
     <row r="974" spans="1:22">
       <c r="A974" s="6" t="s">
-        <v>1459</v>
+        <v>1083</v>
       </c>
       <c r="B974" s="7" t="s">
-        <v>1460</v>
+        <v>2467</v>
       </c>
       <c r="C974" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D974" s="7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E974" s="8">
-        <v>23249.096704</v>
+        <v>762322.092032</v>
       </c>
       <c r="F974" s="9">
-        <v>10.58799092293385</v>
+        <v>14.39909228246559</v>
       </c>
       <c r="G974" s="9">
-        <v>-0.28771197424686</v>
+        <v>0.76076645797761</v>
       </c>
       <c r="H974" s="9">
-        <v>-28.16427067427359</v>
+        <v>47.26579989976284</v>
       </c>
       <c r="I974" s="9">
-        <v>15.2922875171542</v>
+        <v>17.08548321355481</v>
       </c>
       <c r="J974" s="11">
-        <v>7.34889280734496</v>
+        <v>101.4597684119986</v>
       </c>
       <c r="K974" s="9">
-        <v>-4.3921347181816</v>
+        <v>0.94099004226403</v>
       </c>
       <c r="L974" s="9">
-        <v>-16.9</v>
+        <v>37.8</v>
       </c>
       <c r="M974" s="7" t="s">
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="N974" s="9">
-        <v>83.23873211902226</v>
+        <v>24.53293446971835</v>
       </c>
       <c r="O974" s="7" t="s">
-        <v>1462</v>
+        <v>1085</v>
       </c>
       <c r="P974" s="9">
-        <v>66.5089585090408</v>
+        <v>467.7697841726618</v>
       </c>
       <c r="Q974" s="9">
-        <v>61.17457010769595</v>
-      </c>
-      <c r="R974" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S974" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T974" s="10" t="s">
-        <v>30</v>
+        <v>10.34555214833951</v>
+      </c>
+      <c r="R974" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="S974" s="9">
+        <v>178.9746882258184</v>
+      </c>
+      <c r="T974" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="U974" s="12" t="s">
         <v>41</v>
       </c>
       <c r="V974" s="11">
-        <v>47.91327623126338</v>
+        <v>56.21306209850107</v>
       </c>
     </row>
     <row r="975" spans="1:22">
       <c r="A975" s="6" t="s">
-        <v>786</v>
+        <v>1701</v>
       </c>
       <c r="B975" s="7" t="s">
-        <v>787</v>
+        <v>1702</v>
       </c>
       <c r="C975" s="7" t="s">
         <v>28</v>
@@ -70936,126 +70894,126 @@
         <v>29</v>
       </c>
       <c r="E975" s="8">
-        <v>12134.3232</v>
+        <v>12578.661376</v>
       </c>
       <c r="F975" s="9">
-        <v>14.03638757502264</v>
+        <v>20.21134884265646</v>
       </c>
       <c r="G975" s="9">
-        <v>6.90913608330241</v>
+        <v>16.4350192965183</v>
       </c>
       <c r="H975" s="9">
-        <v>15.9424688855513</v>
+        <v>-39.21585735433231</v>
       </c>
       <c r="I975" s="9">
-        <v>21.17626443534281</v>
+        <v>20.9006052706891</v>
       </c>
       <c r="J975" s="11">
-        <v>9.129744194863251</v>
-      </c>
-      <c r="K975" s="9">
-        <v>10.85536511834463</v>
+        <v>7.88744587549017</v>
+      </c>
+      <c r="K975" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="L975" s="9">
-        <v>5.4</v>
+        <v>-7.6</v>
       </c>
       <c r="M975" s="7" t="s">
-        <v>81</v>
+        <v>1703</v>
       </c>
       <c r="N975" s="9">
-        <v>100</v>
+        <v>53.42455018949013</v>
       </c>
       <c r="O975" s="7" t="s">
-        <v>81</v>
+        <v>2468</v>
       </c>
       <c r="P975" s="9">
-        <v>-8.981387797359941</v>
+        <v>26.88567771615129</v>
       </c>
       <c r="Q975" s="9">
-        <v>0</v>
-      </c>
-      <c r="R975" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S975" s="10" t="s">
-        <v>30</v>
+        <v>46.64781228573134</v>
+      </c>
+      <c r="R975" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S975" s="9">
+        <v>-185.986970028494</v>
       </c>
       <c r="T975" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U975" s="10" t="s">
-        <v>30</v>
+      <c r="U975" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="V975" s="11">
-        <v>78.19432548179871</v>
+        <v>44.63811563169165</v>
       </c>
     </row>
     <row r="976" spans="1:22">
       <c r="A976" s="6" t="s">
-        <v>1701</v>
+        <v>2469</v>
       </c>
       <c r="B976" s="7" t="s">
-        <v>1702</v>
+        <v>2470</v>
       </c>
       <c r="C976" s="7" t="s">
-        <v>28</v>
+        <v>431</v>
       </c>
       <c r="D976" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E976" s="8">
-        <v>12578.661376</v>
-      </c>
-      <c r="F976" s="9">
-        <v>20.21134884265646</v>
-      </c>
-      <c r="G976" s="9">
-        <v>16.4350192965183</v>
-      </c>
-      <c r="H976" s="9">
-        <v>-39.21585735433231</v>
-      </c>
-      <c r="I976" s="9">
-        <v>20.9006052706891</v>
+        <v>5982.524928</v>
+      </c>
+      <c r="F976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I976" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J976" s="11">
-        <v>7.88744587549017</v>
+        <v>2.384461875584978</v>
       </c>
       <c r="K976" s="10" t="s">
         <v>30</v>
       </c>
       <c r="L976" s="9">
-        <v>-7.6</v>
-      </c>
-      <c r="M976" s="7" t="s">
-        <v>1703</v>
-      </c>
-      <c r="N976" s="9">
-        <v>53.42455018949013</v>
-      </c>
-      <c r="O976" s="7" t="s">
-        <v>2468</v>
-      </c>
-      <c r="P976" s="9">
-        <v>26.88567771615129</v>
-      </c>
-      <c r="Q976" s="9">
-        <v>46.64781228573134</v>
-      </c>
-      <c r="R976" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S976" s="9">
-        <v>-185.986970028494</v>
+        <v>-2.6</v>
+      </c>
+      <c r="M976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R976" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S976" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T976" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U976" s="12" t="s">
-        <v>41</v>
+      <c r="U976" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V976" s="11">
-        <v>44.63811563169165</v>
+        <v>80.55594218415418</v>
       </c>
     </row>
     <row r="977" spans="1:22">
@@ -71128,55 +71086,55 @@
     </row>
     <row r="978" spans="1:22">
       <c r="A978" s="6" t="s">
-        <v>2469</v>
+        <v>212</v>
       </c>
       <c r="B978" s="7" t="s">
-        <v>2470</v>
+        <v>213</v>
       </c>
       <c r="C978" s="7" t="s">
-        <v>431</v>
+        <v>28</v>
       </c>
       <c r="D978" s="7" t="s">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="E978" s="8">
-        <v>5982.524928</v>
-      </c>
-      <c r="F978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I978" s="10" t="s">
-        <v>30</v>
+        <v>564107.214848</v>
+      </c>
+      <c r="F978" s="9">
+        <v>25.37691905817877</v>
+      </c>
+      <c r="G978" s="9">
+        <v>22.23484640325328</v>
+      </c>
+      <c r="H978" s="9">
+        <v>460.1372328458942</v>
+      </c>
+      <c r="I978" s="9">
+        <v>25.4315100204583</v>
       </c>
       <c r="J978" s="11">
-        <v>2.384461875584978</v>
-      </c>
-      <c r="K978" s="10" t="s">
-        <v>30</v>
+        <v>17.39382995030982</v>
+      </c>
+      <c r="K978" s="9">
+        <v>2.21790734645562</v>
       </c>
       <c r="L978" s="9">
-        <v>-2.6</v>
-      </c>
-      <c r="M978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q978" s="10" t="s">
-        <v>30</v>
+        <v>9.9</v>
+      </c>
+      <c r="M978" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="N978" s="9">
+        <v>21.37774708778672</v>
+      </c>
+      <c r="O978" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="P978" s="9">
+        <v>355.5555555555555</v>
+      </c>
+      <c r="Q978" s="9">
+        <v>0.7092925360709185</v>
       </c>
       <c r="R978" s="10" t="s">
         <v>30</v>
@@ -71184,67 +71142,67 @@
       <c r="S978" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T978" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U978" s="10" t="s">
-        <v>30</v>
+      <c r="T978" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U978" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="V978" s="11">
-        <v>80.55594218415418</v>
+        <v>38.20824411134903</v>
       </c>
     </row>
     <row r="979" spans="1:22">
       <c r="A979" s="6" t="s">
-        <v>212</v>
+        <v>786</v>
       </c>
       <c r="B979" s="7" t="s">
-        <v>213</v>
+        <v>787</v>
       </c>
       <c r="C979" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D979" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E979" s="8">
-        <v>564107.214848</v>
+        <v>12134.3232</v>
       </c>
       <c r="F979" s="9">
-        <v>25.37691905817877</v>
+        <v>14.03638757502264</v>
       </c>
       <c r="G979" s="9">
-        <v>22.23484640325328</v>
+        <v>6.90913608330241</v>
       </c>
       <c r="H979" s="9">
-        <v>460.1372328458942</v>
+        <v>15.9424688855513</v>
       </c>
       <c r="I979" s="9">
-        <v>25.4315100204583</v>
+        <v>21.17626443534281</v>
       </c>
       <c r="J979" s="11">
-        <v>17.39382995030982</v>
+        <v>9.129744194863251</v>
       </c>
       <c r="K979" s="9">
-        <v>2.21790734645562</v>
+        <v>10.85536511834463</v>
       </c>
       <c r="L979" s="9">
-        <v>9.9</v>
+        <v>5.4</v>
       </c>
       <c r="M979" s="7" t="s">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="N979" s="9">
-        <v>21.37774708778672</v>
+        <v>100</v>
       </c>
       <c r="O979" s="7" t="s">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="P979" s="9">
-        <v>355.5555555555555</v>
+        <v>-8.981387797359941</v>
       </c>
       <c r="Q979" s="9">
-        <v>0.7092925360709185</v>
+        <v>0</v>
       </c>
       <c r="R979" s="10" t="s">
         <v>30</v>
@@ -71252,22 +71210,22 @@
       <c r="S979" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T979" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U979" s="12" t="s">
-        <v>41</v>
+      <c r="T979" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U979" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V979" s="11">
-        <v>38.20824411134903</v>
+        <v>78.19432548179871</v>
       </c>
     </row>
     <row r="980" spans="1:22">
       <c r="A980" s="6" t="s">
-        <v>2049</v>
+        <v>1986</v>
       </c>
       <c r="B980" s="7" t="s">
-        <v>2050</v>
+        <v>2471</v>
       </c>
       <c r="C980" s="7" t="s">
         <v>28</v>
@@ -71276,117 +71234,117 @@
         <v>29</v>
       </c>
       <c r="E980" s="8">
-        <v>13388.781568</v>
+        <v>92727.803904</v>
       </c>
       <c r="F980" s="9">
-        <v>36.47155849611668</v>
+        <v>12.16832467586076</v>
       </c>
       <c r="G980" s="9">
-        <v>19.02096509492922</v>
+        <v>11.8119306083982</v>
       </c>
       <c r="H980" s="9">
-        <v>200</v>
-      </c>
-      <c r="I980" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J980" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K980" s="10" t="s">
-        <v>30</v>
+        <v>25.2816769962534</v>
+      </c>
+      <c r="I980" s="9">
+        <v>11.87076192256857</v>
+      </c>
+      <c r="J980" s="11">
+        <v>15.2467708167422</v>
+      </c>
+      <c r="K980" s="9">
+        <v>5.70433024109592</v>
       </c>
       <c r="L980" s="9">
-        <v>100.3</v>
+        <v>10.3</v>
       </c>
       <c r="M980" s="7" t="s">
-        <v>2471</v>
+        <v>1988</v>
       </c>
       <c r="N980" s="9">
-        <v>48.14443778928729</v>
+        <v>12.7768650489863</v>
       </c>
       <c r="O980" s="7" t="s">
-        <v>2052</v>
+        <v>2472</v>
       </c>
       <c r="P980" s="9">
-        <v>33.86381655368238</v>
+        <v>71.59090909090908</v>
       </c>
       <c r="Q980" s="9">
-        <v>1.118296032840677</v>
+        <v>1.149159869153103</v>
       </c>
       <c r="R980" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S980" s="9">
-        <v>139.17336501721</v>
+        <v>52</v>
+      </c>
+      <c r="S980" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T980" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U980" s="10" t="s">
-        <v>30</v>
+      <c r="U980" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="V980" s="11">
-        <v>53.42826552462527</v>
+        <v>67.19860813704497</v>
       </c>
     </row>
     <row r="981" spans="1:22">
       <c r="A981" s="6" t="s">
-        <v>2472</v>
+        <v>174</v>
       </c>
       <c r="B981" s="7" t="s">
-        <v>2473</v>
+        <v>175</v>
       </c>
       <c r="C981" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D981" s="7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E981" s="8">
-        <v>21849.233408</v>
+        <v>456181.284864</v>
       </c>
       <c r="F981" s="9">
-        <v>-11.74199733282329</v>
+        <v>30.37976197045843</v>
       </c>
       <c r="G981" s="9">
-        <v>-38.48741508262834</v>
+        <v>27.99861973775017</v>
       </c>
       <c r="H981" s="9">
-        <v>368.4856669297553</v>
+        <v>58.3123045780253</v>
       </c>
       <c r="I981" s="9">
-        <v>14.7476304816127</v>
+        <v>46.45975544187588</v>
       </c>
       <c r="J981" s="11">
-        <v>20.11968143406094</v>
+        <v>33.82491037527318</v>
       </c>
       <c r="K981" s="9">
-        <v>3.87027319544482</v>
+        <v>1.46660448159213</v>
       </c>
       <c r="L981" s="9">
-        <v>4.8</v>
+        <v>21.5</v>
       </c>
       <c r="M981" s="7" t="s">
-        <v>2474</v>
+        <v>176</v>
       </c>
       <c r="N981" s="9">
-        <v>20.94963273871983</v>
+        <v>49.52110586060094</v>
       </c>
       <c r="O981" s="7" t="s">
-        <v>1066</v>
+        <v>177</v>
       </c>
       <c r="P981" s="9">
-        <v>3.947368421052633</v>
+        <v>7.014416611939822</v>
       </c>
       <c r="Q981" s="9">
-        <v>1.223071606310058</v>
+        <v>0.1267569180761707</v>
       </c>
       <c r="R981" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S981" s="9">
-        <v>7.556287570432973</v>
+        <v>139</v>
+      </c>
+      <c r="S981" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T981" s="12" t="s">
         <v>41</v>
@@ -71395,66 +71353,66 @@
         <v>30</v>
       </c>
       <c r="V981" s="11">
-        <v>65.34716274089935</v>
+        <v>71.76472162740899</v>
       </c>
     </row>
     <row r="982" spans="1:22">
       <c r="A982" s="6" t="s">
-        <v>2475</v>
+        <v>2004</v>
       </c>
       <c r="B982" s="7" t="s">
-        <v>2476</v>
+        <v>2005</v>
       </c>
       <c r="C982" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D982" s="7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E982" s="8">
-        <v>10098.741248</v>
+        <v>1549098.287104</v>
       </c>
       <c r="F982" s="9">
-        <v>20.477195149346</v>
+        <v>27.26877121915166</v>
       </c>
       <c r="G982" s="9">
-        <v>16.54853951890034</v>
+        <v>17.17879328340446</v>
       </c>
       <c r="H982" s="9">
-        <v>15.94916966003723</v>
+        <v>-3.63716543141238</v>
       </c>
       <c r="I982" s="9">
-        <v>21.42672873942377</v>
+        <v>27.48178207412952</v>
       </c>
       <c r="J982" s="11">
-        <v>17.95710263675431</v>
+        <v>14.22299607097575</v>
       </c>
       <c r="K982" s="9">
-        <v>1.82609388112129</v>
+        <v>1.64987913838446</v>
       </c>
       <c r="L982" s="9">
-        <v>21.4</v>
+        <v>33.1</v>
       </c>
       <c r="M982" s="7" t="s">
-        <v>256</v>
+        <v>2006</v>
       </c>
       <c r="N982" s="9">
-        <v>20.39838349932646</v>
+        <v>29.42524549536546</v>
       </c>
       <c r="O982" s="7" t="s">
-        <v>2477</v>
+        <v>401</v>
       </c>
       <c r="P982" s="9">
-        <v>17.12488350419385</v>
+        <v>50.05807200929154</v>
       </c>
       <c r="Q982" s="9">
-        <v>0.4816441383707154</v>
+        <v>0.9137508085080848</v>
       </c>
       <c r="R982" s="7" t="s">
         <v>46</v>
       </c>
       <c r="S982" s="9">
-        <v>6.833357346207379</v>
+        <v>19.1781681298909</v>
       </c>
       <c r="T982" s="10" t="s">
         <v>30</v>
@@ -71463,63 +71421,63 @@
         <v>30</v>
       </c>
       <c r="V982" s="11">
-        <v>74.52087794432549</v>
+        <v>77.56263383297643</v>
       </c>
     </row>
     <row r="983" spans="1:22">
       <c r="A983" s="6" t="s">
-        <v>2478</v>
+        <v>2473</v>
       </c>
       <c r="B983" s="7" t="s">
-        <v>2479</v>
+        <v>2474</v>
       </c>
       <c r="C983" s="7" t="s">
-        <v>28</v>
+        <v>431</v>
       </c>
       <c r="D983" s="7" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E983" s="8">
-        <v>147615.596544</v>
-      </c>
-      <c r="F983" s="9">
-        <v>15.94268540560896</v>
-      </c>
-      <c r="G983" s="9">
-        <v>1.19662953118814</v>
+        <v>117310.226432</v>
+      </c>
+      <c r="F983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G983" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="H983" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I983" s="9">
-        <v>18.39474460776682</v>
+      <c r="I983" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J983" s="11">
-        <v>7.826613960296955</v>
+        <v>7.661885357875487</v>
       </c>
       <c r="K983" s="9">
-        <v>8.384361437248861</v>
+        <v>4.31857047257225</v>
       </c>
       <c r="L983" s="9">
-        <v>5.4</v>
-      </c>
-      <c r="M983" s="7" t="s">
-        <v>2480</v>
-      </c>
-      <c r="N983" s="9">
-        <v>18.86635609511109</v>
-      </c>
-      <c r="O983" s="7" t="s">
-        <v>2481</v>
-      </c>
-      <c r="P983" s="9">
-        <v>128.5714285714286</v>
-      </c>
-      <c r="Q983" s="9">
-        <v>1.895410792529631</v>
-      </c>
-      <c r="R983" s="7" t="s">
-        <v>52</v>
+        <v>15.6</v>
+      </c>
+      <c r="M983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q983" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R983" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S983" s="10" t="s">
         <v>30</v>
@@ -71531,66 +71489,66 @@
         <v>30</v>
       </c>
       <c r="V983" s="11">
-        <v>88.94245182012848</v>
+        <v>87.10519271948608</v>
       </c>
     </row>
     <row r="984" spans="1:22">
       <c r="A984" s="6" t="s">
-        <v>2482</v>
+        <v>1429</v>
       </c>
       <c r="B984" s="7" t="s">
-        <v>2483</v>
+        <v>2475</v>
       </c>
       <c r="C984" s="7" t="s">
-        <v>620</v>
+        <v>28</v>
       </c>
       <c r="D984" s="7" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E984" s="8">
-        <v>1175.433984</v>
-      </c>
-      <c r="F984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I984" s="10" t="s">
-        <v>30</v>
+        <v>13737.530368</v>
+      </c>
+      <c r="F984" s="9">
+        <v>22.70878427501843</v>
+      </c>
+      <c r="G984" s="9">
+        <v>19.44603562228006</v>
+      </c>
+      <c r="H984" s="9">
+        <v>6.887117924925961</v>
+      </c>
+      <c r="I984" s="9">
+        <v>9.297987617174019</v>
       </c>
       <c r="J984" s="11">
-        <v>13.35091224105461</v>
-      </c>
-      <c r="K984" s="10" t="s">
-        <v>30</v>
+        <v>34.29916682554814</v>
+      </c>
+      <c r="K984" s="9">
+        <v>-0.79763244968136</v>
       </c>
       <c r="L984" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="M984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R984" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S984" s="10" t="s">
-        <v>30</v>
+        <v>30.5</v>
+      </c>
+      <c r="M984" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="N984" s="9">
+        <v>21.07988238904674</v>
+      </c>
+      <c r="O984" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="P984" s="9">
+        <v>72.6327227569078</v>
+      </c>
+      <c r="Q984" s="9">
+        <v>8.712708267897144</v>
+      </c>
+      <c r="R984" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S984" s="9">
+        <v>187.5059661147017</v>
       </c>
       <c r="T984" s="10" t="s">
         <v>30</v>
@@ -71599,151 +71557,151 @@
         <v>30</v>
       </c>
       <c r="V984" s="11">
-        <v>64.33377944325483</v>
+        <v>77.20342612419699</v>
       </c>
     </row>
     <row r="985" spans="1:22">
       <c r="A985" s="6" t="s">
-        <v>778</v>
+        <v>1829</v>
       </c>
       <c r="B985" s="7" t="s">
-        <v>779</v>
+        <v>1830</v>
       </c>
       <c r="C985" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D985" s="7" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E985" s="8">
-        <v>534.154257935852</v>
+        <v>15452.863488</v>
       </c>
       <c r="F985" s="9">
-        <v>23.05551234768749</v>
+        <v>14.40609890391468</v>
       </c>
       <c r="G985" s="9">
-        <v>19.47457747625621</v>
+        <v>10.10694436354289</v>
       </c>
       <c r="H985" s="9">
-        <v>37.07233835745288</v>
+        <v>-0.8635316709933301</v>
       </c>
       <c r="I985" s="9">
-        <v>23.60027064751609</v>
+        <v>15.02294740921002</v>
       </c>
       <c r="J985" s="11">
-        <v>6.023709596476647</v>
-      </c>
-      <c r="K985" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L985" s="10" t="s">
-        <v>30</v>
+        <v>17.61870897015553</v>
+      </c>
+      <c r="K985" s="9">
+        <v>3.39759030685614</v>
+      </c>
+      <c r="L985" s="9">
+        <v>8.9</v>
       </c>
       <c r="M985" s="7" t="s">
-        <v>780</v>
+        <v>44</v>
       </c>
       <c r="N985" s="9">
-        <v>38.52531915082372</v>
+        <v>25.43663233318406</v>
       </c>
       <c r="O985" s="7" t="s">
-        <v>781</v>
+        <v>1831</v>
       </c>
       <c r="P985" s="9">
-        <v>114.9436090225564</v>
+        <v>15.20092735703247</v>
       </c>
       <c r="Q985" s="9">
-        <v>0.3878347631318946</v>
+        <v>3.907483599359118</v>
       </c>
       <c r="R985" s="7" t="s">
         <v>46</v>
       </c>
       <c r="S985" s="9">
-        <v>-1.15935796408976</v>
-      </c>
-      <c r="T985" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U985" s="12" t="s">
-        <v>41</v>
+        <v>15.2786123366391</v>
+      </c>
+      <c r="T985" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U985" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V985" s="11">
-        <v>75.28640256959315</v>
+        <v>39.56370449678801</v>
       </c>
     </row>
     <row r="986" spans="1:22">
       <c r="A986" s="6" t="s">
-        <v>2484</v>
+        <v>325</v>
       </c>
       <c r="B986" s="7" t="s">
-        <v>2485</v>
+        <v>326</v>
       </c>
       <c r="C986" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D986" s="7" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E986" s="8">
-        <v>16598.28865870422</v>
+        <v>12360.63232</v>
       </c>
       <c r="F986" s="9">
-        <v>21.53079305137872</v>
+        <v>73.73796759418487</v>
       </c>
       <c r="G986" s="9">
-        <v>16.14584250459642</v>
+        <v>36.3960657302815</v>
       </c>
       <c r="H986" s="9">
-        <v>41.14270959837187</v>
+        <v>200</v>
       </c>
       <c r="I986" s="9">
-        <v>18.39271566857261</v>
+        <v>156.7465978512902</v>
       </c>
       <c r="J986" s="11">
-        <v>10.20649812161575</v>
-      </c>
-      <c r="K986" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L986" s="10" t="s">
-        <v>30</v>
+        <v>20.05709800490741</v>
+      </c>
+      <c r="K986" s="9">
+        <v>3.97017617946587</v>
+      </c>
+      <c r="L986" s="9">
+        <v>26.5</v>
       </c>
       <c r="M986" s="7" t="s">
-        <v>2486</v>
+        <v>327</v>
       </c>
       <c r="N986" s="9">
-        <v>23.67472979927946</v>
+        <v>28.35376468633872</v>
       </c>
       <c r="O986" s="7" t="s">
-        <v>2487</v>
+        <v>166</v>
       </c>
       <c r="P986" s="9">
-        <v>0.6289308176100628</v>
+        <v>62.81718399622329</v>
       </c>
       <c r="Q986" s="9">
-        <v>1.202120236842841</v>
+        <v>7.54196831711613</v>
       </c>
       <c r="R986" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S986" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T986" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U986" s="12" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="S986" s="9">
+        <v>-6.179504129237912</v>
+      </c>
+      <c r="T986" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U986" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V986" s="11">
-        <v>76.63543897216273</v>
+        <v>68.06316916488223</v>
       </c>
     </row>
     <row r="987" spans="1:22">
       <c r="A987" s="6" t="s">
-        <v>1242</v>
+        <v>1736</v>
       </c>
       <c r="B987" s="7" t="s">
-        <v>1243</v>
+        <v>1737</v>
       </c>
       <c r="C987" s="7" t="s">
         <v>28</v>
@@ -71752,66 +71710,66 @@
         <v>29</v>
       </c>
       <c r="E987" s="8">
-        <v>86041.427968</v>
+        <v>12465.329152</v>
       </c>
       <c r="F987" s="9">
-        <v>-22.76937883819234</v>
+        <v>18.3357672256623</v>
       </c>
       <c r="G987" s="9">
-        <v>-61.74195098692925</v>
+        <v>11.34875053232618</v>
       </c>
       <c r="H987" s="9">
-        <v>200</v>
+        <v>162.6826764963662</v>
       </c>
       <c r="I987" s="9">
-        <v>-52.32238133357679</v>
+        <v>24.64990259395278</v>
       </c>
       <c r="J987" s="11">
-        <v>373.5170470572995</v>
+        <v>11.7959601299469</v>
       </c>
       <c r="K987" s="9">
-        <v>0.3085969797</v>
+        <v>4.39559184774585</v>
       </c>
       <c r="L987" s="9">
-        <v>130.4</v>
+        <v>12.7</v>
       </c>
       <c r="M987" s="7" t="s">
-        <v>1186</v>
+        <v>1738</v>
       </c>
       <c r="N987" s="9">
-        <v>52.91868502365007</v>
+        <v>24.41986345619947</v>
       </c>
       <c r="O987" s="7" t="s">
-        <v>470</v>
+        <v>2476</v>
       </c>
       <c r="P987" s="9">
-        <v>163.4464651714993</v>
+        <v>22.48766554141781</v>
       </c>
       <c r="Q987" s="9">
-        <v>12.2696971103034</v>
+        <v>11.57935981187805</v>
       </c>
       <c r="R987" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="S987" s="9">
-        <v>22.10992696590466</v>
+        <v>30557.33041489141</v>
       </c>
       <c r="T987" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="U987" s="12" t="s">
-        <v>41</v>
+      <c r="U987" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V987" s="11">
-        <v>75.28827623126338</v>
+        <v>45.06932548179872</v>
       </c>
     </row>
     <row r="988" spans="1:22">
       <c r="A988" s="6" t="s">
-        <v>2488</v>
+        <v>2477</v>
       </c>
       <c r="B988" s="7" t="s">
-        <v>2489</v>
+        <v>2478</v>
       </c>
       <c r="C988" s="7" t="s">
         <v>28</v>
@@ -71820,46 +71778,46 @@
         <v>29</v>
       </c>
       <c r="E988" s="8">
-        <v>10411.935744</v>
+        <v>147615.596544</v>
       </c>
       <c r="F988" s="9">
-        <v>7.49516988342678</v>
+        <v>15.94268540560896</v>
       </c>
       <c r="G988" s="9">
-        <v>5.433517399693049</v>
-      </c>
-      <c r="H988" s="9">
-        <v>200</v>
+        <v>1.19662953118814</v>
+      </c>
+      <c r="H988" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="I988" s="9">
-        <v>21.17194829228418</v>
+        <v>18.39474460776682</v>
       </c>
       <c r="J988" s="11">
-        <v>9.194940017024711</v>
+        <v>7.826613960296955</v>
       </c>
       <c r="K988" s="9">
-        <v>2.72871941381047</v>
+        <v>8.384361437248861</v>
       </c>
       <c r="L988" s="9">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="M988" s="7" t="s">
-        <v>2490</v>
+        <v>2479</v>
       </c>
       <c r="N988" s="9">
-        <v>33.33333333333333</v>
+        <v>18.86635609511109</v>
       </c>
       <c r="O988" s="7" t="s">
-        <v>1421</v>
+        <v>2480</v>
       </c>
       <c r="P988" s="9">
-        <v>29.95391705069124</v>
+        <v>128.5714285714286</v>
       </c>
       <c r="Q988" s="9">
-        <v>0.1461085646552368</v>
-      </c>
-      <c r="R988" s="10" t="s">
-        <v>30</v>
+        <v>1.895410792529631</v>
+      </c>
+      <c r="R988" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="S988" s="10" t="s">
         <v>30</v>
@@ -71871,131 +71829,131 @@
         <v>30</v>
       </c>
       <c r="V988" s="11">
-        <v>89.89079229122056</v>
+        <v>88.94245182012848</v>
       </c>
     </row>
     <row r="989" spans="1:22">
       <c r="A989" s="6" t="s">
-        <v>751</v>
+        <v>2481</v>
       </c>
       <c r="B989" s="7" t="s">
-        <v>752</v>
+        <v>2482</v>
       </c>
       <c r="C989" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D989" s="7" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E989" s="8">
-        <v>2926.623191579819</v>
+        <v>15756.182528</v>
       </c>
       <c r="F989" s="9">
-        <v>8.990214670930561</v>
+        <v>17.10413168579105</v>
       </c>
       <c r="G989" s="9">
-        <v>0.8193503242969901</v>
+        <v>10.90675747723766</v>
       </c>
       <c r="H989" s="9">
-        <v>109.0641279681346</v>
+        <v>10.58118615531343</v>
       </c>
       <c r="I989" s="9">
-        <v>17.44300098669742</v>
+        <v>23.25626384143405</v>
       </c>
       <c r="J989" s="11">
-        <v>8.135008743252369</v>
-      </c>
-      <c r="K989" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L989" s="10" t="s">
-        <v>30</v>
+        <v>17.98634153029206</v>
+      </c>
+      <c r="K989" s="9">
+        <v>3.74805264505247</v>
+      </c>
+      <c r="L989" s="9">
+        <v>42.2</v>
       </c>
       <c r="M989" s="7" t="s">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="N989" s="9">
-        <v>25</v>
+        <v>49.53504632057333</v>
       </c>
       <c r="O989" s="7" t="s">
-        <v>754</v>
+        <v>2483</v>
       </c>
       <c r="P989" s="9">
-        <v>166.3685825085373</v>
+        <v>17617.64705882353</v>
       </c>
       <c r="Q989" s="9">
-        <v>2.892338671864557</v>
+        <v>16.47126241409279</v>
       </c>
       <c r="R989" s="7" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="S989" s="9">
-        <v>4.245780791290596</v>
+        <v>-15.51812380815701</v>
       </c>
       <c r="T989" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U989" s="10" t="s">
-        <v>30</v>
+      <c r="U989" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="V989" s="11">
-        <v>53.18870449678801</v>
+        <v>75.96359743040685</v>
       </c>
     </row>
     <row r="990" spans="1:22">
       <c r="A990" s="6" t="s">
-        <v>2491</v>
+        <v>352</v>
       </c>
       <c r="B990" s="7" t="s">
-        <v>2492</v>
+        <v>353</v>
       </c>
       <c r="C990" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D990" s="7" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="E990" s="8">
-        <v>9583.85152</v>
+        <v>139.989664</v>
       </c>
       <c r="F990" s="9">
-        <v>14.76466103126517</v>
+        <v>68.97923279422618</v>
       </c>
       <c r="G990" s="9">
-        <v>9.339073736097459</v>
-      </c>
-      <c r="H990" s="9">
-        <v>38.10949529512403</v>
-      </c>
-      <c r="I990" s="10" t="s">
-        <v>30</v>
+        <v>-6.563535963905689</v>
+      </c>
+      <c r="H990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I990" s="9">
+        <v>94.56183874333236</v>
       </c>
       <c r="J990" s="11">
-        <v>7.119610978040907</v>
+        <v>3.225931242158093</v>
       </c>
       <c r="K990" s="9">
-        <v>22.39222403979814</v>
+        <v>3.15112550023693</v>
       </c>
       <c r="L990" s="9">
-        <v>13.5</v>
-      </c>
-      <c r="M990" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="N990" s="9">
-        <v>100</v>
-      </c>
-      <c r="O990" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="P990" s="9">
-        <v>-26.19047619047618</v>
-      </c>
-      <c r="Q990" s="9">
-        <v>0</v>
-      </c>
-      <c r="R990" s="10" t="s">
-        <v>30</v>
+        <v>-34.3</v>
+      </c>
+      <c r="M990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q990" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R990" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="S990" s="10" t="s">
         <v>30</v>
@@ -72007,66 +71965,66 @@
         <v>30</v>
       </c>
       <c r="V990" s="11">
-        <v>63.61509635974304</v>
+        <v>66.00669164882227</v>
       </c>
     </row>
     <row r="991" spans="1:22">
       <c r="A991" s="6" t="s">
-        <v>762</v>
+        <v>2484</v>
       </c>
       <c r="B991" s="7" t="s">
-        <v>763</v>
+        <v>2485</v>
       </c>
       <c r="C991" s="7" t="s">
-        <v>28</v>
+        <v>431</v>
       </c>
       <c r="D991" s="7" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="E991" s="8">
-        <v>28606.16704</v>
-      </c>
-      <c r="F991" s="9">
-        <v>23.02210928808162</v>
-      </c>
-      <c r="G991" s="9">
-        <v>12.3513454013088</v>
-      </c>
-      <c r="H991" s="9">
-        <v>-3155.200934579439</v>
-      </c>
-      <c r="I991" s="9">
-        <v>26.3762128130752</v>
+        <v>7860.636672</v>
+      </c>
+      <c r="F991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I991" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J991" s="11">
-        <v>8.784983736132059</v>
+        <v>0.3665657232603735</v>
       </c>
       <c r="K991" s="9">
-        <v>6.69781258468104</v>
+        <v>9.900597324033141</v>
       </c>
       <c r="L991" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="M991" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="N991" s="9">
-        <v>24.8367335547431</v>
-      </c>
-      <c r="O991" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="P991" s="9">
-        <v>196.661101836394</v>
-      </c>
-      <c r="Q991" s="9">
-        <v>0.5986147521012869</v>
-      </c>
-      <c r="R991" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="S991" s="9">
-        <v>-5.323343713571752</v>
+        <v>3.1</v>
+      </c>
+      <c r="M991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R991" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S991" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T991" s="10" t="s">
         <v>30</v>
@@ -72075,66 +72033,66 @@
         <v>30</v>
       </c>
       <c r="V991" s="11">
-        <v>82.39400428265525</v>
+        <v>71.8953426124197</v>
       </c>
     </row>
     <row r="992" spans="1:22">
       <c r="A992" s="6" t="s">
-        <v>2493</v>
+        <v>2025</v>
       </c>
       <c r="B992" s="7" t="s">
-        <v>2494</v>
+        <v>2026</v>
       </c>
       <c r="C992" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D992" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E992" s="8">
-        <v>316416.196608</v>
+        <v>100520.255488</v>
       </c>
       <c r="F992" s="9">
-        <v>7.105064761849279</v>
+        <v>19.74290983466965</v>
       </c>
       <c r="G992" s="9">
-        <v>5.982680344439021</v>
+        <v>2.85946953226829</v>
       </c>
       <c r="H992" s="9">
-        <v>8.718370604228911</v>
+        <v>-1.14691627188177</v>
       </c>
       <c r="I992" s="9">
-        <v>11.96801965473218</v>
+        <v>27.15547778263739</v>
       </c>
       <c r="J992" s="11">
-        <v>29.6417692182084</v>
+        <v>67.60467140210618</v>
       </c>
       <c r="K992" s="9">
-        <v>1.79131150831129</v>
+        <v>3.08019756711583</v>
       </c>
       <c r="L992" s="9">
-        <v>24.7</v>
+        <v>65.5</v>
       </c>
       <c r="M992" s="7" t="s">
-        <v>2495</v>
+        <v>2027</v>
       </c>
       <c r="N992" s="9">
-        <v>27.31445406924166</v>
+        <v>25.05531709954961</v>
       </c>
       <c r="O992" s="7" t="s">
-        <v>45</v>
+        <v>1066</v>
       </c>
       <c r="P992" s="9">
-        <v>49.49564736769378</v>
+        <v>44.57323978496024</v>
       </c>
       <c r="Q992" s="9">
-        <v>3.371631767229602</v>
+        <v>2.092357279705445</v>
       </c>
       <c r="R992" s="7" t="s">
         <v>52</v>
       </c>
       <c r="S992" s="9">
-        <v>30.61461997847589</v>
+        <v>25.02212629438111</v>
       </c>
       <c r="T992" s="10" t="s">
         <v>30</v>
@@ -72143,66 +72101,66 @@
         <v>30</v>
       </c>
       <c r="V992" s="11">
-        <v>80.95503211991435</v>
+        <v>86.09823340471091</v>
       </c>
     </row>
     <row r="993" spans="1:22">
       <c r="A993" s="6" t="s">
-        <v>2496</v>
+        <v>120</v>
       </c>
       <c r="B993" s="7" t="s">
-        <v>2497</v>
+        <v>121</v>
       </c>
       <c r="C993" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D993" s="7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E993" s="8">
-        <v>39015.5264</v>
+        <v>343117.49632</v>
       </c>
       <c r="F993" s="9">
-        <v>17.42239589095219</v>
+        <v>56.16048279606593</v>
       </c>
       <c r="G993" s="9">
-        <v>12.03354799162836</v>
+        <v>45.03073679491686</v>
       </c>
       <c r="H993" s="9">
-        <v>200</v>
+        <v>-44.74109110086793</v>
       </c>
       <c r="I993" s="9">
-        <v>23.0751023443879</v>
+        <v>58.23011867639675</v>
       </c>
       <c r="J993" s="11">
-        <v>6.290858837118098</v>
+        <v>36.88889522486986</v>
       </c>
       <c r="K993" s="9">
-        <v>10.4663461159914</v>
+        <v>0.8861031782431901</v>
       </c>
       <c r="L993" s="9">
-        <v>7.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="M993" s="7" t="s">
-        <v>2498</v>
+        <v>122</v>
       </c>
       <c r="N993" s="9">
-        <v>44.91438562643193</v>
+        <v>46.22234535164444</v>
       </c>
       <c r="O993" s="7" t="s">
-        <v>2499</v>
+        <v>123</v>
       </c>
       <c r="P993" s="9">
-        <v>14.17935702199662</v>
+        <v>50.52770448548814</v>
       </c>
       <c r="Q993" s="9">
-        <v>9.664266463869753</v>
-      </c>
-      <c r="R993" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S993" s="10" t="s">
-        <v>30</v>
+        <v>5.238834997307484</v>
+      </c>
+      <c r="R993" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S993" s="9">
+        <v>13.62692432441163</v>
       </c>
       <c r="T993" s="10" t="s">
         <v>30</v>
@@ -72211,15 +72169,15 @@
         <v>30</v>
       </c>
       <c r="V993" s="11">
-        <v>41.95931477516059</v>
+        <v>41.9710920770878</v>
       </c>
     </row>
     <row r="994" spans="1:22">
       <c r="A994" s="6" t="s">
-        <v>902</v>
+        <v>2486</v>
       </c>
       <c r="B994" s="7" t="s">
-        <v>903</v>
+        <v>2487</v>
       </c>
       <c r="C994" s="7" t="s">
         <v>28</v>
@@ -72228,194 +72186,194 @@
         <v>29</v>
       </c>
       <c r="E994" s="8">
-        <v>16507.032576</v>
+        <v>22208.309248</v>
       </c>
       <c r="F994" s="9">
-        <v>15.58608160554067</v>
+        <v>21.31256916296736</v>
       </c>
       <c r="G994" s="9">
-        <v>6.58630328441649</v>
+        <v>15.70131812244106</v>
       </c>
       <c r="H994" s="9">
-        <v>-22.15173053427627</v>
+        <v>61.85351566119409</v>
       </c>
       <c r="I994" s="9">
-        <v>12.05096674017734</v>
+        <v>31.15588367065784</v>
       </c>
       <c r="J994" s="11">
-        <v>5.530745092896175</v>
+        <v>23.28198974227121</v>
       </c>
       <c r="K994" s="9">
-        <v>5.30455743616265</v>
+        <v>3.41846161957767</v>
       </c>
       <c r="L994" s="9">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M994" s="7" t="s">
-        <v>2500</v>
+        <v>2488</v>
       </c>
       <c r="N994" s="9">
-        <v>63.40903066183618</v>
+        <v>35.82748302678579</v>
       </c>
       <c r="O994" s="7" t="s">
-        <v>2501</v>
+        <v>332</v>
       </c>
       <c r="P994" s="9">
-        <v>12600</v>
+        <v>12.09423821395907</v>
       </c>
       <c r="Q994" s="9">
-        <v>8.897851712612685</v>
+        <v>0.2649807808230181</v>
       </c>
       <c r="R994" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="S994" s="10" t="s">
-        <v>30</v>
+      <c r="S994" s="9">
+        <v>2.192982456140358</v>
       </c>
       <c r="T994" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U994" s="12" t="s">
-        <v>41</v>
+      <c r="U994" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V994" s="11">
-        <v>90.01043897216273</v>
+        <v>72.3661670235546</v>
       </c>
     </row>
     <row r="995" spans="1:22">
       <c r="A995" s="6" t="s">
-        <v>2502</v>
+        <v>937</v>
       </c>
       <c r="B995" s="7" t="s">
-        <v>2503</v>
+        <v>938</v>
       </c>
       <c r="C995" s="7" t="s">
-        <v>431</v>
+        <v>28</v>
       </c>
       <c r="D995" s="7" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="E995" s="8">
-        <v>13979.88864</v>
-      </c>
-      <c r="F995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I995" s="10" t="s">
-        <v>30</v>
+        <v>12343.648256</v>
+      </c>
+      <c r="F995" s="9">
+        <v>16.32630569798057</v>
+      </c>
+      <c r="G995" s="9">
+        <v>8.34937966664376</v>
+      </c>
+      <c r="H995" s="9">
+        <v>200</v>
+      </c>
+      <c r="I995" s="9">
+        <v>14.92643595649632</v>
       </c>
       <c r="J995" s="11">
-        <v>5.149601967536442</v>
+        <v>20.48611105504418</v>
       </c>
       <c r="K995" s="9">
-        <v>-13.5739633473933</v>
+        <v>2.23980692147162</v>
       </c>
       <c r="L995" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="M995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T995" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U995" s="10" t="s">
-        <v>30</v>
+        <v>34.4</v>
+      </c>
+      <c r="M995" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="N995" s="9">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="O995" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="P995" s="9">
+        <v>3948.102189781021</v>
+      </c>
+      <c r="Q995" s="9">
+        <v>31.90432977647047</v>
+      </c>
+      <c r="R995" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S995" s="9">
+        <v>31.73373240736936</v>
+      </c>
+      <c r="T995" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U995" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="V995" s="11">
-        <v>75.90497858672377</v>
+        <v>44.03078158458244</v>
       </c>
     </row>
     <row r="996" spans="1:22">
       <c r="A996" s="6" t="s">
-        <v>1887</v>
+        <v>2489</v>
       </c>
       <c r="B996" s="7" t="s">
-        <v>2504</v>
+        <v>2490</v>
       </c>
       <c r="C996" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D996" s="7" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E996" s="8">
-        <v>58120.298496</v>
+        <v>709.240768</v>
       </c>
       <c r="F996" s="9">
-        <v>8.10095776525935</v>
+        <v>10.67763396984633</v>
       </c>
       <c r="G996" s="9">
-        <v>5.32340163435406</v>
-      </c>
-      <c r="H996" s="10" t="s">
-        <v>30</v>
+        <v>7.02173275861261</v>
+      </c>
+      <c r="H996" s="9">
+        <v>-329.46879962913</v>
       </c>
       <c r="I996" s="9">
-        <v>11.49500056642986</v>
+        <v>10.5115828482743</v>
       </c>
       <c r="J996" s="11">
-        <v>30.31001799813607</v>
-      </c>
-      <c r="K996" s="10" t="s">
-        <v>30</v>
+        <v>7.821643636363636</v>
+      </c>
+      <c r="K996" s="9">
+        <v>8.540823191934729</v>
       </c>
       <c r="L996" s="9">
-        <v>190</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="M996" s="7" t="s">
-        <v>28</v>
+        <v>1643</v>
       </c>
       <c r="N996" s="9">
-        <v>32.70637408568443</v>
+        <v>77.68604388147477</v>
       </c>
       <c r="O996" s="7" t="s">
-        <v>1889</v>
+        <v>1788</v>
       </c>
       <c r="P996" s="9">
-        <v>12.88696904247659</v>
+        <v>6.995661605206083</v>
       </c>
       <c r="Q996" s="9">
-        <v>18.57941017706166</v>
+        <v>3.181355994018062</v>
       </c>
       <c r="R996" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="S996" s="9">
-        <v>11.10354778258158</v>
+      <c r="S996" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T996" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U996" s="12" t="s">
-        <v>41</v>
+      <c r="U996" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V996" s="11">
-        <v>81.39105995717344</v>
+        <v>41.40604925053533</v>
       </c>
     </row>
   </sheetData>

--- a/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
+++ b/data/synthesis/workbook/archetypes_workbook_harvard.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13121" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13232" uniqueCount="2511">
   <si>
     <t>INVESTMENT ARCHETYPES  ·  CROSS-COHORT SUMMARY</t>
   </si>
   <si>
-    <t>2026-06-27  ·  18,680 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  246 backlog-inflect  ·  1556 triple-lens</t>
+    <t>2026-06-27  ·  20,659 ranked  ·  78 enduring  ·  97 turning  ·  509 cash  ·  277 segment-inflect  ·  556 backlog-inflect  ·  1556 triple-lens</t>
   </si>
   <si>
     <t>Each archetype is a structurally distinct setup. A name may appear in multiple cohorts — the Triple-Lens Conviction block at the end shows names with ≥ 3 archetype overlaps. Segment and backlog data come from full SEC EDGAR XBRL dimensional parsing (edgartools); fundamentals from Lindy multi-method ROIC reconciliation. Every cohort row shows the specific segment name, backlog concept, and inflection magnitude that drove the flag.</t>
@@ -6676,7 +6676,7 @@
     <t>Joint Ventures</t>
   </si>
   <si>
-    <t>20. BACKLOG INFLECTION — RPO / DEFERRED-REV GROWTH ACCELERATING (LEADING-INDICATOR)  ·  246 NAMES</t>
+    <t>20. BACKLOG INFLECTION — RPO / DEFERRED-REV GROWTH ACCELERATING (LEADING-INDICATOR)  ·  556 NAMES</t>
   </si>
   <si>
     <t>Latest Backlog (M)</t>
@@ -6712,12 +6712,51 @@
     <t>EV/EBITDA</t>
   </si>
   <si>
+    <t>NNBR</t>
+  </si>
+  <si>
+    <t>NN, Inc.</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>ContractWithCustomerLiabilit</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>NMTC</t>
+  </si>
+  <si>
+    <t>NeuroOne Medical Technol</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>SDEV</t>
+  </si>
+  <si>
+    <t>Stablecoin Development C</t>
+  </si>
+  <si>
+    <t>2024-09-30</t>
+  </si>
+  <si>
     <t>RevenueRemainingPerformanceO</t>
   </si>
   <si>
     <t>2026-03-29</t>
   </si>
   <si>
+    <t>JANX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janux Therapeutics Inc. </t>
+  </si>
+  <si>
     <t>ACAD</t>
   </si>
   <si>
@@ -6730,10 +6769,16 @@
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>ContractWithCustomerLiabilit</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
+    <t>STEK</t>
+  </si>
+  <si>
+    <t>Stemtech Corp</t>
+  </si>
+  <si>
+    <t>QRHC</t>
+  </si>
+  <si>
+    <t>Quest Resource Holding C</t>
   </si>
   <si>
     <t>SWKHL</t>
@@ -6745,16 +6790,46 @@
     <t>2024-06-30</t>
   </si>
   <si>
+    <t>FMC</t>
+  </si>
+  <si>
+    <t>FMC Corporation</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
+    <t>TRNR</t>
+  </si>
+  <si>
+    <t>Interactive Strength Inc</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>Dorian LPG Ltd.</t>
+  </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>IDEAYA Biosciences, Inc.</t>
+  </si>
+  <si>
     <t>AES</t>
   </si>
   <si>
     <t>The AES Corporation</t>
   </si>
   <si>
-    <t>2023-06-30</t>
+    <t>ONDS</t>
+  </si>
+  <si>
+    <t>Ondas Holdings Inc.</t>
   </si>
   <si>
     <t>ASTI</t>
@@ -6766,9 +6841,6 @@
     <t>ANI Pharmaceuticals, Inc</t>
   </si>
   <si>
-    <t>2024-09-30</t>
-  </si>
-  <si>
     <t>ALB</t>
   </si>
   <si>
@@ -6778,12 +6850,39 @@
     <t>2025-12-31</t>
   </si>
   <si>
+    <t>TPICQ</t>
+  </si>
+  <si>
+    <t>TPI COMPOSITES, INC</t>
+  </si>
+  <si>
+    <t>HYMC</t>
+  </si>
+  <si>
+    <t>Hycroft Mining Holding C</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>HYMCW</t>
+  </si>
+  <si>
     <t>AIFF</t>
   </si>
   <si>
     <t>Firefly Neuroscience Inc</t>
   </si>
   <si>
+    <t>CTGL</t>
+  </si>
+  <si>
+    <t>SKYTECH ORION GLOBAL COR</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>DTIL</t>
   </si>
   <si>
@@ -6799,22 +6898,367 @@
     <t>2021-09-30</t>
   </si>
   <si>
+    <t>NTRP</t>
+  </si>
+  <si>
+    <t>NextTrip Inc. Common Sto</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
     <t>EVI</t>
   </si>
   <si>
     <t>EVI Industries, Inc.</t>
   </si>
   <si>
-    <t>AIFA</t>
-  </si>
-  <si>
-    <t>All In FutureTech Allian</t>
-  </si>
-  <si>
-    <t>ASPN</t>
-  </si>
-  <si>
-    <t>Aspen Aerogels, Inc.</t>
+    <t>SRXH</t>
+  </si>
+  <si>
+    <t>SRX Health Solutions Inc</t>
+  </si>
+  <si>
+    <t>2025-03-31</t>
+  </si>
+  <si>
+    <t>MITI</t>
+  </si>
+  <si>
+    <t>Mitesco, Inc.</t>
+  </si>
+  <si>
+    <t>FLYW</t>
+  </si>
+  <si>
+    <t>Flywire Corporation</t>
+  </si>
+  <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
+    <t>LITS</t>
+  </si>
+  <si>
+    <t>Lite Strategy Inc. Commo</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>SLNG</t>
+  </si>
+  <si>
+    <t>Stabilis Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
+    <t>HROW</t>
+  </si>
+  <si>
+    <t>Harrow Health, Inc.</t>
+  </si>
+  <si>
+    <t>XXII</t>
+  </si>
+  <si>
+    <t>22nd Century Group, Inc.</t>
+  </si>
+  <si>
+    <t>VEEE</t>
+  </si>
+  <si>
+    <t>Twin Vee PowerCats Co. C</t>
+  </si>
+  <si>
+    <t>BURUW</t>
+  </si>
+  <si>
+    <t>Nuburu, Inc.</t>
+  </si>
+  <si>
+    <t>21. VALUE AREA RULE TRIGGER — DALTON BRACKET-RULE CONTINUATION (OPEN OUTSIDE, ACCEPT INSIDE)  ·  965 NAMES</t>
+  </si>
+  <si>
+    <t>025560.KS</t>
+  </si>
+  <si>
+    <t>Mirae</t>
+  </si>
+  <si>
+    <t>HRPK.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7C Solarparken AG         </t>
+  </si>
+  <si>
+    <t>CFEB.BR</t>
+  </si>
+  <si>
+    <t>CFE</t>
+  </si>
+  <si>
+    <t>AMIX</t>
+  </si>
+  <si>
+    <t>Autonomix Medical Inc. Com</t>
+  </si>
+  <si>
+    <t>BJCHI.BK</t>
+  </si>
+  <si>
+    <t>BJC Heavy Industries Publi</t>
+  </si>
+  <si>
+    <t>PTTGC-R.BK</t>
+  </si>
+  <si>
+    <t>AIMH</t>
+  </si>
+  <si>
+    <t>Aimrite Holdings Corporati</t>
+  </si>
+  <si>
+    <t>ALLR</t>
+  </si>
+  <si>
+    <t>Allarity Therapeutics Inc.</t>
+  </si>
+  <si>
+    <t>ASST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Entities Inc. Class </t>
+  </si>
+  <si>
+    <t>SUS.ST</t>
+  </si>
+  <si>
+    <t>Surgical Science Sweden AB</t>
+  </si>
+  <si>
+    <t>DAAV.VI</t>
+  </si>
+  <si>
+    <t>DAAV.VI,0P0001KR9K,0</t>
+  </si>
+  <si>
+    <t>JPXGY</t>
+  </si>
+  <si>
+    <t>STRINV.CO</t>
+  </si>
+  <si>
+    <t>Strategic Investments A/S</t>
+  </si>
+  <si>
+    <t>OBL.AX</t>
+  </si>
+  <si>
+    <t>OMNIBRIDGE FPO FORUS [OBL]</t>
+  </si>
+  <si>
+    <t>VTX.V</t>
+  </si>
+  <si>
+    <t>VERTEX RESOURCE GROUP LTD</t>
+  </si>
+  <si>
+    <t>HUMAN.BK</t>
+  </si>
+  <si>
+    <t>Humanica Public Company Li</t>
+  </si>
+  <si>
+    <t>6428.TWO</t>
+  </si>
+  <si>
+    <t>TAOMEE</t>
+  </si>
+  <si>
+    <t>009190.KS</t>
+  </si>
+  <si>
+    <t>Daiyang Metal Co., Ltd.</t>
+  </si>
+  <si>
+    <t>EBGEF</t>
+  </si>
+  <si>
+    <t>ENBRIDGE INC</t>
+  </si>
+  <si>
+    <t>SMPNY</t>
+  </si>
+  <si>
+    <t>Sompo Hldgs Inc</t>
+  </si>
+  <si>
+    <t>CTPNV.AS</t>
+  </si>
+  <si>
+    <t>CTP NV</t>
+  </si>
+  <si>
+    <t>AINO.ST</t>
+  </si>
+  <si>
+    <t>Aino Health AB (publ)</t>
+  </si>
+  <si>
+    <t>22. ACCEPTED OUTSIDE — VAR SUCCEEDED (FULL VALUE-AREA MIGRATION)  ·  1071 NAMES</t>
+  </si>
+  <si>
+    <t>DNQA.SG</t>
+  </si>
+  <si>
+    <t>DHER.HM</t>
+  </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
+    <t>Equinor ASA</t>
+  </si>
+  <si>
+    <t>41B.SI</t>
+  </si>
+  <si>
+    <t>$ Huationg Global</t>
+  </si>
+  <si>
+    <t>SMO.F</t>
+  </si>
+  <si>
+    <t>SUMITOMO ELECTRIC IND. LTD</t>
+  </si>
+  <si>
+    <t>FUC.F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanuc Corp.               </t>
+  </si>
+  <si>
+    <t>0Y3M.L</t>
+  </si>
+  <si>
+    <t>PROTHENA CORPORATION PLC P</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>DDT.AX</t>
+  </si>
+  <si>
+    <t>DATADOT FPO [DDT]</t>
+  </si>
+  <si>
+    <t>TEP.VI</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE</t>
+  </si>
+  <si>
+    <t>PERM-R.BK</t>
+  </si>
+  <si>
+    <t>Permsin Steel Works Public</t>
+  </si>
+  <si>
+    <t>JAT.VI</t>
+  </si>
+  <si>
+    <t>JAPAN TOBACCO INC</t>
+  </si>
+  <si>
+    <t>RICHY-R.BK</t>
+  </si>
+  <si>
+    <t>Richy Place 2002 Public Co</t>
+  </si>
+  <si>
+    <t>MLNMA.PA</t>
+  </si>
+  <si>
+    <t>MIGUET ET ASSOCIES</t>
+  </si>
+  <si>
+    <t>FANCY-R.BK</t>
+  </si>
+  <si>
+    <t>Fancy Wood Industries Publ</t>
+  </si>
+  <si>
+    <t>6191.T</t>
+  </si>
+  <si>
+    <t>AIRTRIP CORP</t>
+  </si>
+  <si>
+    <t>KCM-R.BK</t>
+  </si>
+  <si>
+    <t>K.C. Metalsheet Public Com</t>
+  </si>
+  <si>
+    <t>PORT-R.BK</t>
+  </si>
+  <si>
+    <t>Sahathai Terminal Public C</t>
+  </si>
+  <si>
+    <t>DNQ.F</t>
+  </si>
+  <si>
+    <t>BSM.BK</t>
+  </si>
+  <si>
+    <t>BuilderSmart Public Compan</t>
+  </si>
+  <si>
+    <t>8333.HK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astrum Financial Holdings </t>
+  </si>
+  <si>
+    <t>EVER.BK</t>
+  </si>
+  <si>
+    <t>Everland Public Company Li</t>
+  </si>
+  <si>
+    <t>23. LONG-TERM EXCESS BUY — DALTON STRUCTURAL BUYERS + BULL WEEKLY STATE  ·  7034 NAMES</t>
+  </si>
+  <si>
+    <t>Products delivered</t>
+  </si>
+  <si>
+    <t>DTEA.SG</t>
+  </si>
+  <si>
+    <t>CMCOM.AS</t>
+  </si>
+  <si>
+    <t>CM.COM</t>
+  </si>
+  <si>
+    <t>038010.KQ</t>
+  </si>
+  <si>
+    <t>Jeil Technos Co.,Ltd</t>
+  </si>
+  <si>
+    <t>SWRAY</t>
+  </si>
+  <si>
+    <t>DGV.MI</t>
+  </si>
+  <si>
+    <t>DIGITAL VALUE</t>
   </si>
   <si>
     <t>DK</t>
@@ -6823,390 +7267,6 @@
     <t>Delek US Holdings Inc</t>
   </si>
   <si>
-    <t>EHTH</t>
-  </si>
-  <si>
-    <t>eHealth, Inc.</t>
-  </si>
-  <si>
-    <t>Esperion Therapeutics, I</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>DNLI</t>
-  </si>
-  <si>
-    <t>Denali Therapeutics Inc.</t>
-  </si>
-  <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>Alpha Metallurgical Reso</t>
-  </si>
-  <si>
-    <t>BAER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridger Aerospace Group </t>
-  </si>
-  <si>
-    <t>DAN</t>
-  </si>
-  <si>
-    <t>Dana Incorporated</t>
-  </si>
-  <si>
-    <t>CREX</t>
-  </si>
-  <si>
-    <t>Creative Realities, Inc.</t>
-  </si>
-  <si>
-    <t>AMKR</t>
-  </si>
-  <si>
-    <t>Amkor Technology, Inc.</t>
-  </si>
-  <si>
-    <t>REZI</t>
-  </si>
-  <si>
-    <t>Resideo Technologies, In</t>
-  </si>
-  <si>
-    <t>2025-03-29</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>Broadcom Inc.</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>nVent Electric plc</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc.</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>SBIG</t>
-  </si>
-  <si>
-    <t>SpringBig Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>CPSH</t>
-  </si>
-  <si>
-    <t>CPS Technologies Corpora</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>21. VALUE AREA RULE TRIGGER — DALTON BRACKET-RULE CONTINUATION (OPEN OUTSIDE, ACCEPT INSIDE)  ·  965 NAMES</t>
-  </si>
-  <si>
-    <t>025560.KS</t>
-  </si>
-  <si>
-    <t>Mirae</t>
-  </si>
-  <si>
-    <t>HRPK.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7C Solarparken AG         </t>
-  </si>
-  <si>
-    <t>CFEB.BR</t>
-  </si>
-  <si>
-    <t>CFE</t>
-  </si>
-  <si>
-    <t>AMIX</t>
-  </si>
-  <si>
-    <t>Autonomix Medical Inc. Com</t>
-  </si>
-  <si>
-    <t>BJCHI.BK</t>
-  </si>
-  <si>
-    <t>BJC Heavy Industries Publi</t>
-  </si>
-  <si>
-    <t>PTTGC-R.BK</t>
-  </si>
-  <si>
-    <t>AIMH</t>
-  </si>
-  <si>
-    <t>Aimrite Holdings Corporati</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>ALLR</t>
-  </si>
-  <si>
-    <t>Allarity Therapeutics Inc.</t>
-  </si>
-  <si>
-    <t>ASST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset Entities Inc. Class </t>
-  </si>
-  <si>
-    <t>SUS.ST</t>
-  </si>
-  <si>
-    <t>Surgical Science Sweden AB</t>
-  </si>
-  <si>
-    <t>DAAV.VI</t>
-  </si>
-  <si>
-    <t>DAAV.VI,0P0001KR9K,0</t>
-  </si>
-  <si>
-    <t>JPXGY</t>
-  </si>
-  <si>
-    <t>STRINV.CO</t>
-  </si>
-  <si>
-    <t>Strategic Investments A/S</t>
-  </si>
-  <si>
-    <t>OBL.AX</t>
-  </si>
-  <si>
-    <t>OMNIBRIDGE FPO FORUS [OBL]</t>
-  </si>
-  <si>
-    <t>VTX.V</t>
-  </si>
-  <si>
-    <t>VERTEX RESOURCE GROUP LTD</t>
-  </si>
-  <si>
-    <t>HUMAN.BK</t>
-  </si>
-  <si>
-    <t>Humanica Public Company Li</t>
-  </si>
-  <si>
-    <t>6428.TWO</t>
-  </si>
-  <si>
-    <t>TAOMEE</t>
-  </si>
-  <si>
-    <t>009190.KS</t>
-  </si>
-  <si>
-    <t>Daiyang Metal Co., Ltd.</t>
-  </si>
-  <si>
-    <t>EBGEF</t>
-  </si>
-  <si>
-    <t>ENBRIDGE INC</t>
-  </si>
-  <si>
-    <t>SMPNY</t>
-  </si>
-  <si>
-    <t>Sompo Hldgs Inc</t>
-  </si>
-  <si>
-    <t>CTPNV.AS</t>
-  </si>
-  <si>
-    <t>CTP NV</t>
-  </si>
-  <si>
-    <t>AINO.ST</t>
-  </si>
-  <si>
-    <t>Aino Health AB (publ)</t>
-  </si>
-  <si>
-    <t>22. ACCEPTED OUTSIDE — VAR SUCCEEDED (FULL VALUE-AREA MIGRATION)  ·  1071 NAMES</t>
-  </si>
-  <si>
-    <t>DNQA.SG</t>
-  </si>
-  <si>
-    <t>DHER.HM</t>
-  </si>
-  <si>
-    <t>EQNR</t>
-  </si>
-  <si>
-    <t>Equinor ASA</t>
-  </si>
-  <si>
-    <t>41B.SI</t>
-  </si>
-  <si>
-    <t>$ Huationg Global</t>
-  </si>
-  <si>
-    <t>SMO.F</t>
-  </si>
-  <si>
-    <t>SUMITOMO ELECTRIC IND. LTD</t>
-  </si>
-  <si>
-    <t>FUC.F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fanuc Corp.               </t>
-  </si>
-  <si>
-    <t>0Y3M.L</t>
-  </si>
-  <si>
-    <t>PROTHENA CORPORATION PLC P</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>DDT.AX</t>
-  </si>
-  <si>
-    <t>DATADOT FPO [DDT]</t>
-  </si>
-  <si>
-    <t>TEP.VI</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE</t>
-  </si>
-  <si>
-    <t>PERM-R.BK</t>
-  </si>
-  <si>
-    <t>Permsin Steel Works Public</t>
-  </si>
-  <si>
-    <t>JAT.VI</t>
-  </si>
-  <si>
-    <t>JAPAN TOBACCO INC</t>
-  </si>
-  <si>
-    <t>RICHY-R.BK</t>
-  </si>
-  <si>
-    <t>Richy Place 2002 Public Co</t>
-  </si>
-  <si>
-    <t>MLNMA.PA</t>
-  </si>
-  <si>
-    <t>MIGUET ET ASSOCIES</t>
-  </si>
-  <si>
-    <t>FANCY-R.BK</t>
-  </si>
-  <si>
-    <t>Fancy Wood Industries Publ</t>
-  </si>
-  <si>
-    <t>6191.T</t>
-  </si>
-  <si>
-    <t>AIRTRIP CORP</t>
-  </si>
-  <si>
-    <t>KCM-R.BK</t>
-  </si>
-  <si>
-    <t>K.C. Metalsheet Public Com</t>
-  </si>
-  <si>
-    <t>PORT-R.BK</t>
-  </si>
-  <si>
-    <t>Sahathai Terminal Public C</t>
-  </si>
-  <si>
-    <t>DNQ.F</t>
-  </si>
-  <si>
-    <t>BSM.BK</t>
-  </si>
-  <si>
-    <t>BuilderSmart Public Compan</t>
-  </si>
-  <si>
-    <t>8333.HK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrum Financial Holdings </t>
-  </si>
-  <si>
-    <t>EVER.BK</t>
-  </si>
-  <si>
-    <t>Everland Public Company Li</t>
-  </si>
-  <si>
-    <t>23. LONG-TERM EXCESS BUY — DALTON STRUCTURAL BUYERS + BULL WEEKLY STATE  ·  7034 NAMES</t>
-  </si>
-  <si>
-    <t>Products delivered</t>
-  </si>
-  <si>
-    <t>DTEA.SG</t>
-  </si>
-  <si>
-    <t>CMCOM.AS</t>
-  </si>
-  <si>
-    <t>CM.COM</t>
-  </si>
-  <si>
-    <t>038010.KQ</t>
-  </si>
-  <si>
-    <t>Jeil Technos Co.,Ltd</t>
-  </si>
-  <si>
-    <t>SWRAY</t>
-  </si>
-  <si>
-    <t>DGV.MI</t>
-  </si>
-  <si>
-    <t>DIGITAL VALUE</t>
-  </si>
-  <si>
     <t>Inter-segment fees</t>
   </si>
   <si>
@@ -7237,7 +7297,7 @@
     <t>Scandinavian Investment Gr</t>
   </si>
   <si>
-    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  3989 NAMES</t>
+    <t>24. SUB BOOK VALUE — GRAHAM DEEP VALUE (P/B &lt; 1)  ·  4262 NAMES</t>
   </si>
   <si>
     <t>G0I.SI</t>
@@ -58894,129 +58954,129 @@
     </row>
     <row r="789" spans="1:22">
       <c r="A789" s="6" t="s">
-        <v>1736</v>
+        <v>2232</v>
       </c>
       <c r="B789" s="7" t="s">
-        <v>1737</v>
+        <v>2233</v>
       </c>
       <c r="C789" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D789" s="7" t="s">
-        <v>29</v>
+        <v>2234</v>
       </c>
       <c r="E789" s="8">
-        <v>12465.329152</v>
+        <v>129.295104</v>
       </c>
       <c r="F789" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G789" s="8">
-        <v>976.6</v>
+        <v>0.5</v>
       </c>
       <c r="H789" s="7" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="I789" s="9">
-        <v>1.160140874249005</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="J789" s="9">
-        <v>69657.14285714286</v>
+        <v>124999900</v>
       </c>
       <c r="K789" s="9">
-        <v>48473.71031746031</v>
+        <v>68749987.5</v>
       </c>
       <c r="L789" s="9">
-        <v>24188.8751989176</v>
+        <v>34374948.29547746</v>
       </c>
       <c r="M789" s="9">
-        <v>30557.33041489141</v>
+        <v>137499912.4999542</v>
       </c>
       <c r="N789" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O789" s="8">
-        <v>14983.229312</v>
+        <v>339.528104</v>
       </c>
       <c r="P789" s="11">
-        <v>0.0651795403823824</v>
-      </c>
-      <c r="Q789" s="9">
-        <v>18.3357672256623</v>
-      </c>
-      <c r="R789" s="9">
-        <v>162.6826764963662</v>
-      </c>
-      <c r="S789" s="11">
-        <v>11.7959601299469</v>
+        <v>0.0014726321447605</v>
+      </c>
+      <c r="Q789" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R789" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S789" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T789" s="9">
-        <v>4.39559184774585</v>
+        <v>-0.27205206470927</v>
       </c>
       <c r="U789" s="9">
-        <v>12.7</v>
-      </c>
-      <c r="V789" s="11">
-        <v>45.06932548179872</v>
+        <v>12.1</v>
+      </c>
+      <c r="V789" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="790" spans="1:22">
       <c r="A790" s="6" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B790" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C790" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D790" s="7" t="s">
         <v>2234</v>
       </c>
-      <c r="B790" s="7" t="s">
-        <v>2235</v>
-      </c>
-      <c r="C790" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D790" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E790" s="8">
-        <v>3593.527898567871</v>
+      <c r="E790" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F790" s="7" t="s">
-        <v>2236</v>
+        <v>139</v>
       </c>
       <c r="G790" s="8">
-        <v>4.132</v>
+        <v>1.455188</v>
       </c>
       <c r="H790" s="7" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="I790" s="9">
-        <v>56.27836611195158</v>
+        <v>0</v>
       </c>
       <c r="J790" s="9">
-        <v>27446.66666666666</v>
+        <v>64632.56227758007</v>
       </c>
       <c r="K790" s="9">
-        <v>10415.82549634274</v>
-      </c>
-      <c r="L790" s="9">
-        <v>5168.856365319622</v>
+        <v>20308.48814749791</v>
+      </c>
+      <c r="L790" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M790" s="9">
-        <v>16970.88650660849</v>
+        <v>40795.11130923605</v>
       </c>
       <c r="N790" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O790" s="8">
-        <v>3415.832898567871</v>
-      </c>
-      <c r="P790" s="11">
-        <v>0.0012096610468657</v>
-      </c>
-      <c r="Q790" s="9">
-        <v>-7.923636466348261</v>
-      </c>
-      <c r="R790" s="9">
-        <v>-15.35009289609109</v>
-      </c>
-      <c r="S790" s="11">
-        <v>32.5264756998188</v>
+      <c r="O790" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P790" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q790" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R790" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S790" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T790" s="10" t="s">
         <v>30</v>
@@ -59024,61 +59084,61 @@
       <c r="U790" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V790" s="11">
-        <v>16.13597430406852</v>
+      <c r="V790" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="791" spans="1:22">
       <c r="A791" s="6" t="s">
-        <v>1033</v>
+        <v>2240</v>
       </c>
       <c r="B791" s="7" t="s">
-        <v>1034</v>
+        <v>2241</v>
       </c>
       <c r="C791" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D791" s="7" t="s">
-        <v>59</v>
+        <v>2234</v>
       </c>
       <c r="E791" s="8">
-        <v>2045.064322196083</v>
+        <v>38.23306</v>
       </c>
       <c r="F791" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G791" s="8">
-        <v>1.8</v>
+        <v>0.751</v>
       </c>
       <c r="H791" s="7" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="I791" s="9">
-        <v>0</v>
+        <v>-2.846054333764558</v>
       </c>
       <c r="J791" s="9">
-        <v>148.9626556016597</v>
+        <v>18675</v>
       </c>
       <c r="K791" s="9">
-        <v>3712.240663900415</v>
-      </c>
-      <c r="L791" s="9">
-        <v>2525.323060636554</v>
+        <v>33363.65740740741</v>
+      </c>
+      <c r="L791" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M791" s="9">
-        <v>7618.249868510107</v>
+        <v>38565.15356820235</v>
       </c>
       <c r="N791" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O791" s="8">
-        <v>2016.193322196083</v>
+        <v>20.46506</v>
       </c>
       <c r="P791" s="11">
-        <v>0.0008927715314716</v>
-      </c>
-      <c r="Q791" s="9">
-        <v>-28.90813072165297</v>
+        <v>0.0366966918249934</v>
+      </c>
+      <c r="Q791" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R791" s="10" t="s">
         <v>30</v>
@@ -59086,271 +59146,271 @@
       <c r="S791" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T791" s="10" t="s">
-        <v>30</v>
+      <c r="T791" s="9">
+        <v>30.06298737270833</v>
       </c>
       <c r="U791" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V791" s="11">
-        <v>81.87981798715204</v>
+      <c r="V791" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="792" spans="1:22">
       <c r="A792" s="6" t="s">
-        <v>2240</v>
+        <v>1736</v>
       </c>
       <c r="B792" s="7" t="s">
-        <v>2241</v>
+        <v>1737</v>
       </c>
       <c r="C792" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D792" s="7" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E792" s="8">
-        <v>308.4474645</v>
+        <v>12465.329152</v>
       </c>
       <c r="F792" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G792" s="8">
-        <v>2.216</v>
+        <v>976.6</v>
       </c>
       <c r="H792" s="7" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="I792" s="9">
-        <v>46.85222001325382</v>
+        <v>1.160140874249005</v>
       </c>
       <c r="J792" s="9">
-        <v>7286.666666666666</v>
+        <v>69657.14285714286</v>
       </c>
       <c r="K792" s="9">
-        <v>2990.416666666667</v>
+        <v>48473.71031746031</v>
       </c>
       <c r="L792" s="9">
-        <v>1466.035302843931</v>
+        <v>24188.8751989176</v>
       </c>
       <c r="M792" s="9">
-        <v>5842.819264069264</v>
-      </c>
-      <c r="N792" s="11">
-        <v>0.0534529753720722</v>
+        <v>30557.33041489141</v>
+      </c>
+      <c r="N792" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="O792" s="8">
-        <v>298.6534645</v>
+        <v>14983.229312</v>
       </c>
       <c r="P792" s="11">
-        <v>0.0074199708471823</v>
+        <v>0.0651795403823824</v>
       </c>
       <c r="Q792" s="9">
-        <v>5.05593634957493</v>
+        <v>18.3357672256623</v>
       </c>
       <c r="R792" s="9">
-        <v>200</v>
+        <v>162.6826764963662</v>
       </c>
       <c r="S792" s="11">
-        <v>14.70113042087128</v>
-      </c>
-      <c r="T792" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U792" s="10" t="s">
-        <v>30</v>
+        <v>11.7959601299469</v>
+      </c>
+      <c r="T792" s="9">
+        <v>4.39559184774585</v>
+      </c>
+      <c r="U792" s="9">
+        <v>12.7</v>
       </c>
       <c r="V792" s="11">
-        <v>77.94566381156316</v>
+        <v>45.06932548179872</v>
       </c>
     </row>
     <row r="793" spans="1:22">
       <c r="A793" s="6" t="s">
-        <v>947</v>
+        <v>2245</v>
       </c>
       <c r="B793" s="7" t="s">
-        <v>948</v>
+        <v>2246</v>
       </c>
       <c r="C793" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D793" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E793" s="8">
-        <v>98.13520722165777</v>
+        <v>885.4928</v>
       </c>
       <c r="F793" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G793" s="8">
-        <v>63.064</v>
+        <v>37.591</v>
       </c>
       <c r="H793" s="7" t="s">
-        <v>2243</v>
-      </c>
-      <c r="I793" s="9">
-        <v>44.60571874068469</v>
+        <v>2236</v>
+      </c>
+      <c r="I793" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J793" s="9">
-        <v>8297.336884154462</v>
+        <v>39890.42553191489</v>
       </c>
       <c r="K793" s="9">
-        <v>2129.27329053735</v>
-      </c>
-      <c r="L793" s="10" t="s">
-        <v>30</v>
+        <v>9897.606382978724</v>
+      </c>
+      <c r="L793" s="9">
+        <v>4913.14857559373</v>
       </c>
       <c r="M793" s="9">
-        <v>4430.313079842213</v>
+        <v>19989.84867889302</v>
       </c>
       <c r="N793" s="11">
-        <v>0.4801656793921028</v>
+        <v>3.7591</v>
       </c>
       <c r="O793" s="8">
-        <v>146.1832072216578</v>
-      </c>
-      <c r="P793" s="11">
-        <v>0.4314038609398957</v>
-      </c>
-      <c r="Q793" s="9">
-        <v>5.31940257538757</v>
-      </c>
-      <c r="R793" s="9">
-        <v>32.92317393230853</v>
+        <v>-49.322184</v>
+      </c>
+      <c r="P793" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q793" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R793" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S793" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T793" s="10" t="s">
-        <v>30</v>
+      <c r="T793" s="9">
+        <v>-6.09947093866827</v>
       </c>
       <c r="U793" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V793" s="11">
-        <v>32.24491434689508</v>
+      <c r="V793" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="794" spans="1:22">
       <c r="A794" s="6" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="B794" s="7" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="C794" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D794" s="7" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E794" s="8">
-        <v>10469.154816</v>
+        <v>3593.527898567871</v>
       </c>
       <c r="F794" s="7" t="s">
-        <v>2232</v>
+        <v>2249</v>
       </c>
       <c r="G794" s="8">
-        <v>322</v>
+        <v>4.132</v>
       </c>
       <c r="H794" s="7" t="s">
-        <v>2239</v>
+        <v>2250</v>
       </c>
       <c r="I794" s="9">
-        <v>-18.68686868686869</v>
+        <v>56.27836611195158</v>
       </c>
       <c r="J794" s="9">
-        <v>4500</v>
+        <v>27446.66666666666</v>
       </c>
       <c r="K794" s="9">
-        <v>4039.732142857143</v>
+        <v>10415.82549634274</v>
       </c>
       <c r="L794" s="9">
-        <v>2020.560515873016</v>
+        <v>5168.856365319622</v>
       </c>
       <c r="M794" s="9">
-        <v>3503.125</v>
+        <v>16970.88650660849</v>
       </c>
       <c r="N794" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O794" s="8">
-        <v>40622.155008</v>
+        <v>3415.832898567871</v>
       </c>
       <c r="P794" s="11">
-        <v>0.0079267089581187</v>
+        <v>0.0012096610468657</v>
       </c>
       <c r="Q794" s="9">
-        <v>-0.16753506019642</v>
-      </c>
-      <c r="R794" s="10" t="s">
-        <v>30</v>
+        <v>-7.923636466348261</v>
+      </c>
+      <c r="R794" s="9">
+        <v>-15.35009289609109</v>
       </c>
       <c r="S794" s="11">
-        <v>10.81815028379185</v>
-      </c>
-      <c r="T794" s="9">
-        <v>-28.32129229256017</v>
-      </c>
-      <c r="U794" s="9">
-        <v>8.699999999999999</v>
+        <v>32.5264756998188</v>
+      </c>
+      <c r="T794" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U794" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V794" s="11">
-        <v>65.95583511777302</v>
+        <v>16.13597430406852</v>
       </c>
     </row>
     <row r="795" spans="1:22">
       <c r="A795" s="6" t="s">
-        <v>1140</v>
+        <v>2251</v>
       </c>
       <c r="B795" s="7" t="s">
-        <v>1141</v>
+        <v>2252</v>
       </c>
       <c r="C795" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D795" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E795" s="8">
-        <v>58.82066565805078</v>
+        <v>2234</v>
+      </c>
+      <c r="E795" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F795" s="7" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
       <c r="G795" s="8">
-        <v>0.001709</v>
+        <v>0.335219</v>
       </c>
       <c r="H795" s="7" t="s">
-        <v>2246</v>
+        <v>2236</v>
       </c>
       <c r="I795" s="9">
-        <v>-88.80885338222775</v>
+        <v>95.48007114324868</v>
       </c>
       <c r="J795" s="9">
-        <v>481.2925170068027</v>
+        <v>4845.691944526409</v>
       </c>
       <c r="K795" s="9">
-        <v>1362.340140298289</v>
-      </c>
-      <c r="L795" s="10" t="s">
-        <v>30</v>
+        <v>4120.418795948415</v>
+      </c>
+      <c r="L795" s="9">
+        <v>2047.446811175428</v>
       </c>
       <c r="M795" s="9">
-        <v>2791.307993831289</v>
-      </c>
-      <c r="N795" s="11">
-        <v>9.229655872631827E-06</v>
-      </c>
-      <c r="O795" s="8">
-        <v>63.23466565805077</v>
-      </c>
-      <c r="P795" s="11">
-        <v>2.702631511079109E-05</v>
-      </c>
-      <c r="Q795" s="9">
-        <v>-14.94478982766374</v>
+        <v>8276.481895863155</v>
+      </c>
+      <c r="N795" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O795" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P795" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q795" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R795" s="10" t="s">
         <v>30</v>
@@ -59364,64 +59424,64 @@
       <c r="U795" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V795" s="11">
-        <v>59.91220556745181</v>
+      <c r="V795" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="796" spans="1:22">
       <c r="A796" s="6" t="s">
-        <v>2247</v>
+        <v>1033</v>
       </c>
       <c r="B796" s="7" t="s">
-        <v>2248</v>
+        <v>1034</v>
       </c>
       <c r="C796" s="7" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="D796" s="7" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="E796" s="8">
-        <v>28.99893278182984</v>
+        <v>2045.064322196083</v>
       </c>
       <c r="F796" s="7" t="s">
-        <v>139</v>
+        <v>2235</v>
       </c>
       <c r="G796" s="8">
-        <v>0.044525</v>
+        <v>1.8</v>
       </c>
       <c r="H796" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I796" s="9">
-        <v>-25.5845436464827</v>
+        <v>0</v>
       </c>
       <c r="J796" s="9">
-        <v>815.3988486842104</v>
+        <v>148.9626556016597</v>
       </c>
       <c r="K796" s="9">
-        <v>2743.042158823418</v>
+        <v>3712.240663900415</v>
       </c>
       <c r="L796" s="9">
-        <v>1351.599598900857</v>
+        <v>2525.323060636554</v>
       </c>
       <c r="M796" s="9">
-        <v>2594.605749077548</v>
+        <v>7618.249868510107</v>
       </c>
       <c r="N796" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O796" s="8">
-        <v>32.50425478182984</v>
+        <v>2016.193322196083</v>
       </c>
       <c r="P796" s="11">
-        <v>0.0013698206680588</v>
+        <v>0.0008927715314716</v>
       </c>
       <c r="Q796" s="9">
-        <v>-192.9559070228838</v>
-      </c>
-      <c r="R796" s="9">
-        <v>153.0167866828766</v>
+        <v>-28.90813072165297</v>
+      </c>
+      <c r="R796" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S796" s="10" t="s">
         <v>30</v>
@@ -59433,267 +59493,267 @@
         <v>30</v>
       </c>
       <c r="V796" s="11">
-        <v>5.859207708779443</v>
+        <v>81.87981798715204</v>
       </c>
     </row>
     <row r="797" spans="1:22">
       <c r="A797" s="6" t="s">
-        <v>812</v>
+        <v>2253</v>
       </c>
       <c r="B797" s="7" t="s">
-        <v>2249</v>
+        <v>2254</v>
       </c>
       <c r="C797" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D797" s="7" t="s">
-        <v>59</v>
+        <v>2234</v>
       </c>
       <c r="E797" s="8">
-        <v>1860.478791775177</v>
+        <v>24.165662</v>
       </c>
       <c r="F797" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G797" s="8">
-        <v>5</v>
+        <v>0.065</v>
       </c>
       <c r="H797" s="7" t="s">
-        <v>2250</v>
-      </c>
-      <c r="I797" s="10" t="s">
-        <v>30</v>
+        <v>2236</v>
+      </c>
+      <c r="I797" s="9">
+        <v>-99.94921875</v>
       </c>
       <c r="J797" s="9">
-        <v>4900</v>
+        <v>-54.22535211267605</v>
       </c>
       <c r="K797" s="9">
-        <v>1196.774193548387</v>
+        <v>3114.712639160606</v>
       </c>
       <c r="L797" s="9">
-        <v>579.7150729646697</v>
+        <v>1534.613858434113</v>
       </c>
       <c r="M797" s="9">
-        <v>2408.136520737327</v>
+        <v>6401.302243421133</v>
       </c>
       <c r="N797" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O797" s="8">
-        <v>1703.101791775177</v>
+        <v>89.01866200000001</v>
       </c>
       <c r="P797" s="11">
-        <v>0.002935819822483</v>
-      </c>
-      <c r="Q797" s="9">
-        <v>4.09292371790951</v>
-      </c>
-      <c r="R797" s="9">
-        <v>2046.863112716786</v>
-      </c>
-      <c r="S797" s="11">
-        <v>10.75563984827546</v>
-      </c>
-      <c r="T797" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U797" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V797" s="11">
-        <v>91.9563704496788</v>
+        <v>0.0007301839697388</v>
+      </c>
+      <c r="Q797" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R797" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S797" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T797" s="9">
+        <v>48.36873494299473</v>
+      </c>
+      <c r="U797" s="9">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="V797" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="798" spans="1:22">
       <c r="A798" s="6" t="s">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="B798" s="7" t="s">
-        <v>2252</v>
+        <v>2256</v>
       </c>
       <c r="C798" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D798" s="7" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E798" s="8">
-        <v>20235.227136</v>
+        <v>308.4474645</v>
       </c>
       <c r="F798" s="7" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="G798" s="8">
-        <v>93.09</v>
+        <v>2.216</v>
       </c>
       <c r="H798" s="7" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
       <c r="I798" s="9">
-        <v>41.90548780487804</v>
+        <v>46.85222001325382</v>
       </c>
       <c r="J798" s="9">
-        <v>4301.418439716312</v>
+        <v>7286.666666666666</v>
       </c>
       <c r="K798" s="9">
-        <v>1258.923222362419</v>
-      </c>
-      <c r="L798" s="10" t="s">
-        <v>30</v>
+        <v>2990.416666666667</v>
+      </c>
+      <c r="L798" s="9">
+        <v>1466.035302843931</v>
       </c>
       <c r="M798" s="9">
-        <v>2396.39346704372</v>
+        <v>5842.819264069264</v>
       </c>
       <c r="N798" s="11">
-        <v>0.0181012702778853</v>
+        <v>0.0534529753720722</v>
       </c>
       <c r="O798" s="8">
-        <v>21151.409152</v>
+        <v>298.6534645</v>
       </c>
       <c r="P798" s="11">
-        <v>0.0044011252078303</v>
+        <v>0.0074199708471823</v>
       </c>
       <c r="Q798" s="9">
-        <v>2.49351039779715</v>
+        <v>5.05593634957493</v>
       </c>
       <c r="R798" s="9">
         <v>200</v>
       </c>
       <c r="S798" s="11">
-        <v>19.81370686381566</v>
-      </c>
-      <c r="T798" s="9">
-        <v>3.54190115674518</v>
-      </c>
-      <c r="U798" s="9">
-        <v>32.7</v>
+        <v>14.70113042087128</v>
+      </c>
+      <c r="T798" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U798" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V798" s="11">
-        <v>52.1132226980728</v>
+        <v>77.94566381156316</v>
       </c>
     </row>
     <row r="799" spans="1:22">
       <c r="A799" s="6" t="s">
-        <v>1423</v>
+        <v>2258</v>
       </c>
       <c r="B799" s="7" t="s">
-        <v>1424</v>
+        <v>2259</v>
       </c>
       <c r="C799" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D799" s="7" t="s">
-        <v>59</v>
+        <v>2234</v>
       </c>
       <c r="E799" s="8">
-        <v>8879.377408</v>
+        <v>1639.343872</v>
       </c>
       <c r="F799" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G799" s="8">
-        <v>0.359</v>
+        <v>196.3</v>
       </c>
       <c r="H799" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I799" s="9">
-        <v>-91.49692089057318</v>
+        <v>-56.67623041271243</v>
       </c>
       <c r="J799" s="9">
-        <v>460.9375</v>
+        <v>10805.55555555556</v>
       </c>
       <c r="K799" s="9">
-        <v>977.8308282508048</v>
+        <v>2651.350325645169</v>
       </c>
       <c r="L799" s="9">
-        <v>459.7293783562617</v>
+        <v>1293.577410872229</v>
       </c>
       <c r="M799" s="9">
-        <v>2117.717401056614</v>
+        <v>5478.660861073403</v>
       </c>
       <c r="N799" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O799" s="8">
-        <v>8969.4774</v>
+        <v>5905.043936</v>
       </c>
       <c r="P799" s="11">
-        <v>4.002462841369108E-05</v>
-      </c>
-      <c r="Q799" s="9">
-        <v>-1.0018415074855</v>
-      </c>
-      <c r="R799" s="9">
-        <v>200</v>
-      </c>
-      <c r="S799" s="11">
-        <v>-241.7453413470609</v>
+        <v>0.0332427670526311</v>
+      </c>
+      <c r="Q799" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R799" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S799" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T799" s="9">
-        <v>0.2552403052446</v>
+        <v>1.39613783239249</v>
       </c>
       <c r="U799" s="9">
-        <v>43</v>
-      </c>
-      <c r="V799" s="11">
-        <v>80.40765524625267</v>
+        <v>-4.100000000000001</v>
+      </c>
+      <c r="V799" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="800" spans="1:22">
       <c r="A800" s="6" t="s">
-        <v>2254</v>
+        <v>947</v>
       </c>
       <c r="B800" s="7" t="s">
-        <v>2255</v>
+        <v>948</v>
       </c>
       <c r="C800" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D800" s="7" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="E800" s="8">
-        <v>24.43764225</v>
+        <v>98.13520722165777</v>
       </c>
       <c r="F800" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G800" s="8">
-        <v>0.208</v>
+        <v>63.064</v>
       </c>
       <c r="H800" s="7" t="s">
-        <v>2239</v>
+        <v>2260</v>
       </c>
       <c r="I800" s="9">
-        <v>-16.46586345381527</v>
+        <v>44.60571874068469</v>
       </c>
       <c r="J800" s="9">
-        <v>1500</v>
+        <v>8297.336884154462</v>
       </c>
       <c r="K800" s="9">
-        <v>879.2027428866719</v>
-      </c>
-      <c r="L800" s="9">
-        <v>400.8445734166899</v>
+        <v>2129.27329053735</v>
+      </c>
+      <c r="L800" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M800" s="9">
-        <v>1645.703405622395</v>
+        <v>4430.313079842213</v>
       </c>
       <c r="N800" s="11">
-        <v>0.1821366024518388</v>
+        <v>0.4801656793921028</v>
       </c>
       <c r="O800" s="8">
-        <v>24.20564725</v>
+        <v>146.1832072216578</v>
       </c>
       <c r="P800" s="11">
-        <v>0.0085930360734311</v>
+        <v>0.4314038609398957</v>
       </c>
       <c r="Q800" s="9">
-        <v>-84.36971799652343</v>
+        <v>5.31940257538757</v>
       </c>
       <c r="R800" s="9">
-        <v>11.8125312031952</v>
+        <v>32.92317393230853</v>
       </c>
       <c r="S800" s="10" t="s">
         <v>30</v>
@@ -59705,128 +59765,128 @@
         <v>30</v>
       </c>
       <c r="V800" s="11">
-        <v>54.3835653104925</v>
+        <v>32.24491434689508</v>
       </c>
     </row>
     <row r="801" spans="1:22">
       <c r="A801" s="6" t="s">
-        <v>2256</v>
+        <v>2261</v>
       </c>
       <c r="B801" s="7" t="s">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="C801" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D801" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E801" s="8">
-        <v>174.1593132094502</v>
+        <v>1.748465</v>
       </c>
       <c r="F801" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G801" s="8">
-        <v>0</v>
+        <v>4.475</v>
       </c>
       <c r="H801" s="7" t="s">
-        <v>2253</v>
+        <v>2236</v>
       </c>
       <c r="I801" s="9">
-        <v>-100</v>
+        <v>239.7873955960516</v>
       </c>
       <c r="J801" s="9">
-        <v>-100</v>
+        <v>6680.30303030303</v>
       </c>
       <c r="K801" s="9">
-        <v>1136.768761601338</v>
+        <v>2124.151467493859</v>
       </c>
       <c r="L801" s="9">
-        <v>522.6430629677895</v>
+        <v>1093.181647409416</v>
       </c>
       <c r="M801" s="9">
-        <v>1434.552234882852</v>
-      </c>
-      <c r="N801" s="10" t="s">
-        <v>30</v>
+        <v>4110.274263025621</v>
+      </c>
+      <c r="N801" s="11">
+        <v>0.3881179531656548</v>
       </c>
       <c r="O801" s="8">
-        <v>85.55931320945024</v>
+        <v>21.834465</v>
       </c>
       <c r="P801" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q801" s="9">
-        <v>-55.00834909375553</v>
-      </c>
-      <c r="R801" s="9">
-        <v>-187.8047754093862</v>
+        <v>0.2049512090174868</v>
+      </c>
+      <c r="Q801" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R801" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="S801" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T801" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U801" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V801" s="11">
-        <v>85.67398286937902</v>
+      <c r="T801" s="9">
+        <v>-1152.746895133732</v>
+      </c>
+      <c r="U801" s="9">
+        <v>73.7</v>
+      </c>
+      <c r="V801" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="802" spans="1:22">
       <c r="A802" s="6" t="s">
-        <v>2258</v>
+        <v>2263</v>
       </c>
       <c r="B802" s="7" t="s">
-        <v>2259</v>
+        <v>2264</v>
       </c>
       <c r="C802" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D802" s="7" t="s">
-        <v>275</v>
+        <v>2234</v>
       </c>
       <c r="E802" s="8">
-        <v>11.49093503085476</v>
+        <v>1987.683328</v>
       </c>
       <c r="F802" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G802" s="8">
-        <v>0.418</v>
+        <v>0.278128</v>
       </c>
       <c r="H802" s="7" t="s">
-        <v>2260</v>
+        <v>2265</v>
       </c>
       <c r="I802" s="9">
-        <v>1800</v>
+        <v>33.35762713489772</v>
       </c>
       <c r="J802" s="9">
-        <v>2686.666666666667</v>
+        <v>7617.203107658158</v>
       </c>
       <c r="K802" s="9">
-        <v>941.6666666666666</v>
+        <v>1870.464610234901</v>
       </c>
       <c r="L802" s="9">
-        <v>461.6987179487179</v>
+        <v>1213.300632903881</v>
       </c>
       <c r="M802" s="9">
-        <v>1321.842948717949</v>
-      </c>
-      <c r="N802" s="10" t="s">
-        <v>30</v>
+        <v>3812.739550986982</v>
+      </c>
+      <c r="N802" s="11">
+        <v>0.0018146193987699</v>
       </c>
       <c r="O802" s="8">
-        <v>11.35593503085476</v>
+        <v>2369.392416</v>
       </c>
       <c r="P802" s="11">
-        <v>0.0368089460589787</v>
-      </c>
-      <c r="Q802" s="9">
-        <v>-23.4322448250743</v>
+        <v>0.0001173836795128</v>
+      </c>
+      <c r="Q802" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R802" s="10" t="s">
         <v>30</v>
@@ -59837,200 +59897,200 @@
       <c r="T802" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U802" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V802" s="11">
-        <v>72.95208779443256</v>
+      <c r="U802" s="9">
+        <v>106.9</v>
+      </c>
+      <c r="V802" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="803" spans="1:22">
       <c r="A803" s="6" t="s">
-        <v>2261</v>
+        <v>2266</v>
       </c>
       <c r="B803" s="7" t="s">
-        <v>2262</v>
+        <v>2267</v>
       </c>
       <c r="C803" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D803" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E803" s="8">
-        <v>121.6679051485062</v>
+        <v>2556.752896</v>
       </c>
       <c r="F803" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G803" s="8">
-        <v>3.028</v>
+        <v>155.298</v>
       </c>
       <c r="H803" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I803" s="9">
-        <v>0</v>
+        <v>-4.047007068360442</v>
       </c>
       <c r="J803" s="9">
-        <v>1257.847533632287</v>
+        <v>5410.929737402413</v>
       </c>
       <c r="K803" s="9">
-        <v>658.7331710457566</v>
+        <v>2187.959349381943</v>
       </c>
       <c r="L803" s="9">
-        <v>307.7056459735916</v>
+        <v>1052.419596313114</v>
       </c>
       <c r="M803" s="9">
-        <v>1274.548766084603</v>
+        <v>3781.288456578456</v>
       </c>
       <c r="N803" s="11">
-        <v>0.0077674883923761</v>
+        <v>0.7100635544785332</v>
       </c>
       <c r="O803" s="8">
-        <v>124.6889051485062</v>
+        <v>1914.151872</v>
       </c>
       <c r="P803" s="11">
-        <v>0.0242844381093378</v>
-      </c>
-      <c r="Q803" s="9">
-        <v>5.50919798972899</v>
-      </c>
-      <c r="R803" s="9">
-        <v>76.58554383206992</v>
-      </c>
-      <c r="S803" s="11">
-        <v>6.094276888978796</v>
-      </c>
-      <c r="T803" s="10" t="s">
-        <v>30</v>
+        <v>0.08113149341579511</v>
+      </c>
+      <c r="Q803" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R803" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S803" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T803" s="9">
+        <v>-2.23934429054813</v>
       </c>
       <c r="U803" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V803" s="11">
-        <v>25.80085653104925</v>
+      <c r="V803" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="804" spans="1:22">
       <c r="A804" s="6" t="s">
-        <v>2263</v>
+        <v>2268</v>
       </c>
       <c r="B804" s="7" t="s">
-        <v>2264</v>
+        <v>2269</v>
       </c>
       <c r="C804" s="7" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="D804" s="7" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="E804" s="8">
-        <v>90.87370453641176</v>
+        <v>10469.154816</v>
       </c>
       <c r="F804" s="7" t="s">
-        <v>2232</v>
+        <v>2243</v>
       </c>
       <c r="G804" s="8">
-        <v>0.198592</v>
+        <v>322</v>
       </c>
       <c r="H804" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I804" s="9">
-        <v>551.48443394679</v>
+        <v>-18.68686868686869</v>
       </c>
       <c r="J804" s="9">
-        <v>1248.214528173795</v>
+        <v>4500</v>
       </c>
       <c r="K804" s="9">
-        <v>247.8361894037738</v>
+        <v>4039.732142857143</v>
       </c>
       <c r="L804" s="9">
-        <v>102.066190255658</v>
+        <v>2020.560515873016</v>
       </c>
       <c r="M804" s="9">
-        <v>662.4266507138248</v>
+        <v>3503.125</v>
       </c>
       <c r="N804" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O804" s="8">
-        <v>83.32959753641177</v>
+        <v>40622.155008</v>
       </c>
       <c r="P804" s="11">
-        <v>0.0023832108383005</v>
+        <v>0.0079267089581187</v>
       </c>
       <c r="Q804" s="9">
-        <v>-39.87834427298205</v>
-      </c>
-      <c r="R804" s="9">
-        <v>-136.0903274923221</v>
-      </c>
-      <c r="S804" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T804" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U804" s="10" t="s">
-        <v>30</v>
+        <v>-0.16753506019642</v>
+      </c>
+      <c r="R804" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S804" s="11">
+        <v>10.81815028379185</v>
+      </c>
+      <c r="T804" s="9">
+        <v>-28.32129229256017</v>
+      </c>
+      <c r="U804" s="9">
+        <v>8.699999999999999</v>
       </c>
       <c r="V804" s="11">
-        <v>59.96038543897217</v>
+        <v>65.95583511777302</v>
       </c>
     </row>
     <row r="805" spans="1:22">
       <c r="A805" s="6" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="B805" s="7" t="s">
-        <v>2266</v>
+        <v>2271</v>
       </c>
       <c r="C805" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D805" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E805" s="8">
-        <v>478.8987191348125</v>
+        <v>4516.312064</v>
       </c>
       <c r="F805" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G805" s="8">
-        <v>36.578</v>
+        <v>19.832</v>
       </c>
       <c r="H805" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I805" s="9">
-        <v>2805.321683876092</v>
+        <v>133.2902011528056</v>
       </c>
       <c r="J805" s="9">
-        <v>1282.911153119093</v>
+        <v>4329.554185651747</v>
       </c>
       <c r="K805" s="9">
-        <v>273.6469888056843</v>
-      </c>
-      <c r="L805" s="9">
-        <v>123.1066644578958</v>
+        <v>1925.413472567056</v>
+      </c>
+      <c r="L805" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M805" s="9">
-        <v>661.6131040333141</v>
+        <v>3233.741245058013</v>
       </c>
       <c r="N805" s="11">
-        <v>0.1349228890864358</v>
+        <v>0.39092468116142</v>
       </c>
       <c r="O805" s="8">
-        <v>407.2467191348124</v>
+        <v>3050.332072</v>
       </c>
       <c r="P805" s="11">
-        <v>0.08981778926963301</v>
-      </c>
-      <c r="Q805" s="9">
-        <v>-27.68875261121275</v>
+        <v>0.0065015872147312</v>
+      </c>
+      <c r="Q805" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R805" s="10" t="s">
         <v>30</v>
@@ -60038,73 +60098,73 @@
       <c r="S805" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T805" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U805" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V805" s="11">
-        <v>91.46520342612421</v>
+      <c r="T805" s="9">
+        <v>-0.34452395626131</v>
+      </c>
+      <c r="U805" s="9">
+        <v>1079.9</v>
+      </c>
+      <c r="V805" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="806" spans="1:22">
       <c r="A806" s="6" t="s">
-        <v>2267</v>
+        <v>1140</v>
       </c>
       <c r="B806" s="7" t="s">
-        <v>2268</v>
+        <v>1141</v>
       </c>
       <c r="C806" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D806" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E806" s="8">
-        <v>3561.385401522064</v>
+        <v>58.82066565805078</v>
       </c>
       <c r="F806" s="7" t="s">
-        <v>139</v>
+        <v>2235</v>
       </c>
       <c r="G806" s="8">
-        <v>68.40000000000001</v>
+        <v>0.001709</v>
       </c>
       <c r="H806" s="7" t="s">
-        <v>2239</v>
+        <v>2265</v>
       </c>
       <c r="I806" s="9">
-        <v>-3.661971830985911</v>
+        <v>-88.80885338222775</v>
       </c>
       <c r="J806" s="9">
-        <v>282.122905027933</v>
+        <v>481.2925170068027</v>
       </c>
       <c r="K806" s="9">
-        <v>297.5746054028445</v>
-      </c>
-      <c r="L806" s="9">
-        <v>122.9144914955602</v>
+        <v>1362.340140298289</v>
+      </c>
+      <c r="L806" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M806" s="9">
-        <v>643.0602972291047</v>
-      </c>
-      <c r="N806" s="10" t="s">
-        <v>30</v>
+        <v>2791.307993831289</v>
+      </c>
+      <c r="N806" s="11">
+        <v>9.229655872631827E-06</v>
       </c>
       <c r="O806" s="8">
-        <v>6168.685401522064</v>
+        <v>63.23466565805077</v>
       </c>
       <c r="P806" s="11">
-        <v>0.0110882620117282</v>
+        <v>2.702631511079109E-05</v>
       </c>
       <c r="Q806" s="9">
-        <v>2.66863929893312</v>
-      </c>
-      <c r="R806" s="9">
-        <v>13.06437768240343</v>
-      </c>
-      <c r="S806" s="11">
-        <v>8.827540643277139</v>
+        <v>-14.94478982766374</v>
+      </c>
+      <c r="R806" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S806" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T806" s="10" t="s">
         <v>30</v>
@@ -60113,66 +60173,66 @@
         <v>30</v>
       </c>
       <c r="V806" s="11">
-        <v>97.36884368308353</v>
+        <v>59.91220556745181</v>
       </c>
     </row>
     <row r="807" spans="1:22">
       <c r="A807" s="6" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="B807" s="7" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="C807" s="7" t="s">
-        <v>28</v>
+        <v>158</v>
       </c>
       <c r="D807" s="7" t="s">
-        <v>275</v>
+        <v>159</v>
       </c>
       <c r="E807" s="8">
-        <v>48.97052133011818</v>
+        <v>28.99893278182984</v>
       </c>
       <c r="F807" s="7" t="s">
-        <v>2238</v>
+        <v>139</v>
       </c>
       <c r="G807" s="8">
-        <v>10.547</v>
+        <v>0.044525</v>
       </c>
       <c r="H807" s="7" t="s">
-        <v>2260</v>
+        <v>2236</v>
       </c>
       <c r="I807" s="9">
-        <v>673.8077769625825</v>
+        <v>-25.5845436464827</v>
       </c>
       <c r="J807" s="9">
-        <v>-60.15639756714896</v>
+        <v>815.3988486842104</v>
       </c>
       <c r="K807" s="9">
-        <v>272.4174919381002</v>
-      </c>
-      <c r="L807" s="10" t="s">
-        <v>30</v>
+        <v>2743.042158823418</v>
+      </c>
+      <c r="L807" s="9">
+        <v>1351.599598900857</v>
       </c>
       <c r="M807" s="9">
-        <v>635.7042874135963</v>
+        <v>2594.605749077548</v>
       </c>
       <c r="N807" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O807" s="8">
-        <v>88.19952133011817</v>
+        <v>32.50425478182984</v>
       </c>
       <c r="P807" s="11">
-        <v>0.1195811478446021</v>
+        <v>0.0013698206680588</v>
       </c>
       <c r="Q807" s="9">
-        <v>-5.53381200735645</v>
+        <v>-192.9559070228838</v>
       </c>
       <c r="R807" s="9">
-        <v>251.7128900010426</v>
-      </c>
-      <c r="S807" s="11">
-        <v>1.020768720908723</v>
+        <v>153.0167866828766</v>
+      </c>
+      <c r="S807" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T807" s="10" t="s">
         <v>30</v>
@@ -60181,15 +60241,15 @@
         <v>30</v>
       </c>
       <c r="V807" s="11">
-        <v>3.960920770877944</v>
+        <v>5.859207708779443</v>
       </c>
     </row>
     <row r="808" spans="1:22">
       <c r="A808" s="6" t="s">
-        <v>471</v>
+        <v>812</v>
       </c>
       <c r="B808" s="7" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="C808" s="7" t="s">
         <v>28</v>
@@ -60198,49 +60258,49 @@
         <v>59</v>
       </c>
       <c r="E808" s="8">
-        <v>86.06846457688617</v>
+        <v>1860.478791775177</v>
       </c>
       <c r="F808" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G808" s="8">
-        <v>43.531</v>
+        <v>5</v>
       </c>
       <c r="H808" s="7" t="s">
-        <v>2239</v>
-      </c>
-      <c r="I808" s="9">
-        <v>26.26098558459262</v>
+        <v>2242</v>
+      </c>
+      <c r="I808" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J808" s="9">
-        <v>858.4103918978423</v>
+        <v>4900</v>
       </c>
       <c r="K808" s="9">
-        <v>318.6429832305471</v>
+        <v>1196.774193548387</v>
       </c>
       <c r="L808" s="9">
-        <v>141.5316848066163</v>
+        <v>579.7150729646697</v>
       </c>
       <c r="M808" s="9">
-        <v>591.4787659170375</v>
-      </c>
-      <c r="N808" s="11">
-        <v>0.1079811973656467</v>
+        <v>2408.136520737327</v>
+      </c>
+      <c r="N808" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="O808" s="8">
-        <v>-80.76153542311383</v>
-      </c>
-      <c r="P808" s="10" t="s">
-        <v>30</v>
+        <v>1703.101791775177</v>
+      </c>
+      <c r="P808" s="11">
+        <v>0.002935819822483</v>
       </c>
       <c r="Q808" s="9">
-        <v>-30.9163890684529</v>
+        <v>4.09292371790951</v>
       </c>
       <c r="R808" s="9">
-        <v>7.28503439826595</v>
+        <v>2046.863112716786</v>
       </c>
       <c r="S808" s="11">
-        <v>-1.337598718458939</v>
+        <v>10.75563984827546</v>
       </c>
       <c r="T808" s="10" t="s">
         <v>30</v>
@@ -60249,196 +60309,196 @@
         <v>30</v>
       </c>
       <c r="V808" s="11">
-        <v>85.99197002141327</v>
+        <v>91.9563704496788</v>
       </c>
     </row>
     <row r="809" spans="1:22">
       <c r="A809" s="6" t="s">
-        <v>1783</v>
+        <v>2275</v>
       </c>
       <c r="B809" s="7" t="s">
-        <v>1784</v>
+        <v>2276</v>
       </c>
       <c r="C809" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D809" s="7" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E809" s="8">
-        <v>488.6488407275962</v>
+        <v>20235.227136</v>
       </c>
       <c r="F809" s="7" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
       <c r="G809" s="8">
-        <v>0.419</v>
+        <v>93.09</v>
       </c>
       <c r="H809" s="7" t="s">
-        <v>2272</v>
+        <v>2277</v>
       </c>
       <c r="I809" s="9">
-        <v>-24.50450450450451</v>
+        <v>41.90548780487804</v>
       </c>
       <c r="J809" s="9">
-        <v>59.92366412213741</v>
+        <v>4301.418439716312</v>
       </c>
       <c r="K809" s="9">
-        <v>214.620609776686</v>
-      </c>
-      <c r="L809" s="9">
-        <v>84.02537428193357</v>
+        <v>1258.923222362419</v>
+      </c>
+      <c r="L809" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M809" s="9">
-        <v>546.0894778594306</v>
-      </c>
-      <c r="N809" s="10" t="s">
-        <v>30</v>
+        <v>2396.39346704372</v>
+      </c>
+      <c r="N809" s="11">
+        <v>0.0181012702778853</v>
       </c>
       <c r="O809" s="8">
-        <v>482.5738407275962</v>
+        <v>21151.409152</v>
       </c>
       <c r="P809" s="11">
-        <v>0.0008682609056642</v>
+        <v>0.0044011252078303</v>
       </c>
       <c r="Q809" s="9">
-        <v>-27.64249887755216</v>
+        <v>2.49351039779715</v>
       </c>
       <c r="R809" s="9">
         <v>200</v>
       </c>
-      <c r="S809" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T809" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U809" s="10" t="s">
-        <v>30</v>
+      <c r="S809" s="11">
+        <v>19.81370686381566</v>
+      </c>
+      <c r="T809" s="9">
+        <v>3.54190115674518</v>
+      </c>
+      <c r="U809" s="9">
+        <v>32.7</v>
       </c>
       <c r="V809" s="11">
-        <v>82.3543897216274</v>
+        <v>52.1132226980728</v>
       </c>
     </row>
     <row r="810" spans="1:22">
       <c r="A810" s="6" t="s">
-        <v>2202</v>
+        <v>1423</v>
       </c>
       <c r="B810" s="7" t="s">
-        <v>2203</v>
+        <v>1424</v>
       </c>
       <c r="C810" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D810" s="7" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E810" s="8">
-        <v>106215.161856</v>
+        <v>8879.377408</v>
       </c>
       <c r="F810" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G810" s="8">
-        <v>12034</v>
+        <v>0.359</v>
       </c>
       <c r="H810" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I810" s="9">
-        <v>1049.37917860554</v>
+        <v>-91.49692089057318</v>
       </c>
       <c r="J810" s="9">
-        <v>1296.055684454756</v>
+        <v>460.9375</v>
       </c>
       <c r="K810" s="9">
-        <v>374.5825645569677</v>
+        <v>977.8308282508048</v>
       </c>
       <c r="L810" s="9">
-        <v>229.9748856946905</v>
+        <v>459.7293783562617</v>
       </c>
       <c r="M810" s="9">
-        <v>532.2389833834241</v>
+        <v>2117.717401056614</v>
       </c>
       <c r="N810" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O810" s="8">
-        <v>127817.162752</v>
+        <v>8969.4774</v>
       </c>
       <c r="P810" s="11">
-        <v>0.09415011052427461</v>
+        <v>4.002462841369108E-05</v>
       </c>
       <c r="Q810" s="9">
-        <v>6.2917121643981</v>
+        <v>-1.0018415074855</v>
       </c>
       <c r="R810" s="9">
-        <v>-119.2543039402274</v>
+        <v>200</v>
       </c>
       <c r="S810" s="11">
-        <v>16.06348619678404</v>
+        <v>-241.7453413470609</v>
       </c>
       <c r="T810" s="9">
-        <v>-4.21679453077723</v>
+        <v>0.2552403052446</v>
       </c>
       <c r="U810" s="9">
-        <v>63.8</v>
+        <v>43</v>
       </c>
       <c r="V810" s="11">
-        <v>71.51525695931477</v>
+        <v>80.40765524625267</v>
       </c>
     </row>
     <row r="811" spans="1:22">
       <c r="A811" s="6" t="s">
-        <v>2273</v>
+        <v>2278</v>
       </c>
       <c r="B811" s="7" t="s">
-        <v>2274</v>
+        <v>2279</v>
       </c>
       <c r="C811" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D811" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E811" s="8">
-        <v>2911.235683953965</v>
+        <v>2234</v>
+      </c>
+      <c r="E811" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F811" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G811" s="8">
-        <v>0</v>
+        <v>59600</v>
       </c>
       <c r="H811" s="7" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="I811" s="9">
-        <v>-100</v>
-      </c>
-      <c r="J811" s="10" t="s">
-        <v>30</v>
+        <v>21949.57454679985</v>
+      </c>
+      <c r="J811" s="9">
+        <v>4157.142857142857</v>
       </c>
       <c r="K811" s="9">
-        <v>160.1987535802742</v>
+        <v>1006.163773309009</v>
       </c>
       <c r="L811" s="9">
-        <v>56.84798184746922</v>
+        <v>499.6762771410736</v>
       </c>
       <c r="M811" s="9">
-        <v>484.1715561584247</v>
+        <v>2062.773256682193</v>
       </c>
       <c r="N811" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O811" s="8">
-        <v>2705.909683953965</v>
-      </c>
-      <c r="P811" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q811" s="9">
-        <v>-34.12916382250216</v>
+      <c r="O811" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P811" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q811" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R811" s="10" t="s">
         <v>30</v>
@@ -60452,135 +60512,135 @@
       <c r="U811" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V811" s="11">
-        <v>13.33190578158458</v>
+      <c r="V811" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="812" spans="1:22">
       <c r="A812" s="6" t="s">
-        <v>1024</v>
+        <v>2280</v>
       </c>
       <c r="B812" s="7" t="s">
-        <v>1025</v>
+        <v>2281</v>
       </c>
       <c r="C812" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D812" s="7" t="s">
-        <v>275</v>
+        <v>2234</v>
       </c>
       <c r="E812" s="8">
-        <v>160.852192</v>
+        <v>2952.774656</v>
       </c>
       <c r="F812" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G812" s="8">
-        <v>0.097</v>
+        <v>3.9</v>
       </c>
       <c r="H812" s="7" t="s">
-        <v>2239</v>
-      </c>
-      <c r="I812" s="9">
-        <v>259.2592592592592</v>
+        <v>2282</v>
+      </c>
+      <c r="I812" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J812" s="9">
-        <v>781.8181818181819</v>
+        <v>3477.981651376147</v>
       </c>
       <c r="K812" s="9">
-        <v>233.7412587412588</v>
+        <v>801.0171519744714</v>
       </c>
       <c r="L812" s="9">
-        <v>94.43984934819208</v>
+        <v>380.6232697322979</v>
       </c>
       <c r="M812" s="9">
-        <v>443.8545713545714</v>
+        <v>1742.969086557638</v>
       </c>
       <c r="N812" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O812" s="8">
-        <v>125.243192</v>
+        <v>2762.948664</v>
       </c>
       <c r="P812" s="11">
-        <v>0.0007744931956061</v>
-      </c>
-      <c r="Q812" s="9">
-        <v>-100.7743805528934</v>
-      </c>
-      <c r="R812" s="9">
-        <v>174.6655254148012</v>
-      </c>
-      <c r="S812" s="11">
-        <v>-15.49033016913515</v>
-      </c>
-      <c r="T812" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U812" s="9">
-        <v>798.5</v>
-      </c>
-      <c r="V812" s="11">
-        <v>84.21145610278371</v>
+        <v>0.0014115354551516</v>
+      </c>
+      <c r="Q812" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R812" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S812" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T812" s="9">
+        <v>-1.22793820132273</v>
+      </c>
+      <c r="U812" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V812" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="813" spans="1:22">
       <c r="A813" s="6" t="s">
-        <v>2276</v>
+        <v>2283</v>
       </c>
       <c r="B813" s="7" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="C813" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D813" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E813" s="8">
-        <v>2244.875886780533</v>
+        <v>2234</v>
+      </c>
+      <c r="E813" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F813" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G813" s="8">
-        <v>107.712</v>
+        <v>3.9</v>
       </c>
       <c r="H813" s="7" t="s">
-        <v>2239</v>
-      </c>
-      <c r="I813" s="9">
-        <v>12.36386396828708</v>
+        <v>2282</v>
+      </c>
+      <c r="I813" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J813" s="9">
-        <v>421.9869154349406</v>
+        <v>3477.981651376147</v>
       </c>
       <c r="K813" s="9">
-        <v>175.1794539901406</v>
+        <v>801.0171519744714</v>
       </c>
       <c r="L813" s="9">
-        <v>52.23947999323383</v>
+        <v>380.6232697322979</v>
       </c>
       <c r="M813" s="9">
-        <v>394.0057855242201</v>
-      </c>
-      <c r="N813" s="11">
-        <v>0.050581338833265</v>
-      </c>
-      <c r="O813" s="8">
-        <v>1882.757886780533</v>
-      </c>
-      <c r="P813" s="11">
-        <v>0.0572096926303066</v>
-      </c>
-      <c r="Q813" s="9">
-        <v>38.76866695640053</v>
-      </c>
-      <c r="R813" s="9">
-        <v>-1837.92885689258</v>
-      </c>
-      <c r="S813" s="11">
-        <v>16.63831003358607</v>
+        <v>1742.969086557638</v>
+      </c>
+      <c r="N813" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O813" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P813" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q813" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R813" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S813" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T813" s="10" t="s">
         <v>30</v>
@@ -60588,67 +60648,67 @@
       <c r="U813" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V813" s="11">
-        <v>35.05861884368309</v>
+      <c r="V813" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="814" spans="1:22">
       <c r="A814" s="6" t="s">
-        <v>2278</v>
+        <v>2284</v>
       </c>
       <c r="B814" s="7" t="s">
-        <v>2279</v>
+        <v>2285</v>
       </c>
       <c r="C814" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D814" s="7" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="E814" s="8">
-        <v>110.1124877091591</v>
+        <v>24.43764225</v>
       </c>
       <c r="F814" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G814" s="8">
-        <v>2.079</v>
+        <v>0.208</v>
       </c>
       <c r="H814" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I814" s="9">
-        <v>-39.45835760046593</v>
+        <v>-16.46586345381527</v>
       </c>
       <c r="J814" s="9">
-        <v>477.5000000000001</v>
+        <v>1500</v>
       </c>
       <c r="K814" s="9">
-        <v>260.1838795070178</v>
-      </c>
-      <c r="L814" s="10" t="s">
-        <v>30</v>
+        <v>879.2027428866719</v>
+      </c>
+      <c r="L814" s="9">
+        <v>400.8445734166899</v>
       </c>
       <c r="M814" s="9">
-        <v>376.9477994025189</v>
+        <v>1645.703405622395</v>
       </c>
       <c r="N814" s="11">
-        <v>0.0210824130692707</v>
+        <v>0.1821366024518388</v>
       </c>
       <c r="O814" s="8">
-        <v>301.2234877091591</v>
+        <v>24.20564725</v>
       </c>
       <c r="P814" s="11">
-        <v>0.0069018522287589</v>
+        <v>0.0085930360734311</v>
       </c>
       <c r="Q814" s="9">
-        <v>-7.002080052003739</v>
+        <v>-84.36971799652343</v>
       </c>
       <c r="R814" s="9">
-        <v>200</v>
-      </c>
-      <c r="S814" s="11">
-        <v>14.48956119626529</v>
+        <v>11.8125312031952</v>
+      </c>
+      <c r="S814" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T814" s="10" t="s">
         <v>30</v>
@@ -60657,66 +60717,66 @@
         <v>30</v>
       </c>
       <c r="V814" s="11">
-        <v>15.41327623126338</v>
+        <v>54.3835653104925</v>
       </c>
     </row>
     <row r="815" spans="1:22">
       <c r="A815" s="6" t="s">
-        <v>2280</v>
+        <v>2286</v>
       </c>
       <c r="B815" s="7" t="s">
-        <v>2281</v>
+        <v>2287</v>
       </c>
       <c r="C815" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D815" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E815" s="8">
-        <v>3835.6261369468</v>
+        <v>2234</v>
+      </c>
+      <c r="E815" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F815" s="7" t="s">
-        <v>2238</v>
+        <v>139</v>
       </c>
       <c r="G815" s="8">
-        <v>104</v>
+        <v>0.004846</v>
       </c>
       <c r="H815" s="7" t="s">
-        <v>2239</v>
+        <v>2288</v>
       </c>
       <c r="I815" s="9">
-        <v>316</v>
+        <v>-3.041216486594633</v>
       </c>
       <c r="J815" s="9">
-        <v>271.4285714285714</v>
+        <v>238.8811188811189</v>
       </c>
       <c r="K815" s="9">
-        <v>104.5464339581987</v>
+        <v>660.8463094624429</v>
       </c>
       <c r="L815" s="9">
-        <v>29.11237104778168</v>
+        <v>298.8100842814509</v>
       </c>
       <c r="M815" s="9">
-        <v>371.244292858844</v>
-      </c>
-      <c r="N815" s="11">
-        <v>0.0557043385109801</v>
-      </c>
-      <c r="O815" s="8">
-        <v>4836.6261369468</v>
-      </c>
-      <c r="P815" s="11">
-        <v>0.0215025923144127</v>
-      </c>
-      <c r="Q815" s="9">
-        <v>2.07805985698824</v>
-      </c>
-      <c r="R815" s="9">
-        <v>179.0287769784173</v>
-      </c>
-      <c r="S815" s="11">
-        <v>9.993029208567769</v>
+        <v>1496.171955049395</v>
+      </c>
+      <c r="N815" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O815" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P815" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q815" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R815" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S815" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T815" s="10" t="s">
         <v>30</v>
@@ -60724,64 +60784,64 @@
       <c r="U815" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V815" s="11">
-        <v>55.61215203426124</v>
+      <c r="V815" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="816" spans="1:22">
       <c r="A816" s="6" t="s">
-        <v>2282</v>
+        <v>2289</v>
       </c>
       <c r="B816" s="7" t="s">
-        <v>2283</v>
+        <v>2290</v>
       </c>
       <c r="C816" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D816" s="7" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="E816" s="8">
-        <v>39.76181969904901</v>
+        <v>174.1593132094502</v>
       </c>
       <c r="F816" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G816" s="8">
-        <v>8.698</v>
+        <v>0</v>
       </c>
       <c r="H816" s="7" t="s">
-        <v>2239</v>
+        <v>2277</v>
       </c>
       <c r="I816" s="9">
-        <v>7.184226740603816</v>
+        <v>-100</v>
       </c>
       <c r="J816" s="9">
-        <v>150.0143719459615</v>
+        <v>-100</v>
       </c>
       <c r="K816" s="9">
-        <v>178.9843113473878</v>
+        <v>1136.768761601338</v>
       </c>
       <c r="L816" s="9">
-        <v>99.41551590347196</v>
+        <v>522.6430629677895</v>
       </c>
       <c r="M816" s="9">
-        <v>369.7614301785766</v>
+        <v>1434.552234882852</v>
       </c>
       <c r="N816" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O816" s="8">
-        <v>89.790819699049</v>
+        <v>85.55931320945024</v>
       </c>
       <c r="P816" s="11">
-        <v>0.0968695912249492</v>
+        <v>0</v>
       </c>
       <c r="Q816" s="9">
-        <v>-5.34485212061657</v>
+        <v>-55.00834909375553</v>
       </c>
       <c r="R816" s="9">
-        <v>-29.30997161778618</v>
+        <v>-187.8047754093862</v>
       </c>
       <c r="S816" s="10" t="s">
         <v>30</v>
@@ -60793,270 +60853,270 @@
         <v>30</v>
       </c>
       <c r="V816" s="11">
-        <v>70.98634903640257</v>
+        <v>85.67398286937902</v>
       </c>
     </row>
     <row r="817" spans="1:22">
       <c r="A817" s="6" t="s">
-        <v>2284</v>
+        <v>2291</v>
       </c>
       <c r="B817" s="7" t="s">
-        <v>2285</v>
+        <v>2292</v>
       </c>
       <c r="C817" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D817" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="E817" s="8">
-        <v>16297.617408</v>
+        <v>11.49093503085476</v>
       </c>
       <c r="F817" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G817" s="8">
-        <v>392.4</v>
+        <v>0.418</v>
       </c>
       <c r="H817" s="7" t="s">
-        <v>2239</v>
+        <v>2293</v>
       </c>
       <c r="I817" s="9">
-        <v>0.4094165813715467</v>
+        <v>1800</v>
       </c>
       <c r="J817" s="9">
-        <v>346.4163822525597</v>
+        <v>2686.666666666667</v>
       </c>
       <c r="K817" s="9">
-        <v>154.2822823737143</v>
+        <v>941.6666666666666</v>
       </c>
       <c r="L817" s="9">
-        <v>62.05062123915215</v>
+        <v>461.6987179487179</v>
       </c>
       <c r="M817" s="9">
-        <v>351.7024598773452</v>
+        <v>1321.842948717949</v>
       </c>
       <c r="N817" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O817" s="8">
-        <v>16066.600448</v>
+        <v>11.35593503085476</v>
       </c>
       <c r="P817" s="11">
-        <v>0.0244233371751549</v>
+        <v>0.0368089460589787</v>
       </c>
       <c r="Q817" s="9">
-        <v>11.54186549926638</v>
-      </c>
-      <c r="R817" s="9">
-        <v>9.296063575349619</v>
-      </c>
-      <c r="S817" s="11">
-        <v>13.44324479185353</v>
-      </c>
-      <c r="T817" s="9">
-        <v>-0.28928461639341</v>
-      </c>
-      <c r="U817" s="9">
-        <v>27.5</v>
+        <v>-23.4322448250743</v>
+      </c>
+      <c r="R817" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S817" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T817" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U817" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V817" s="11">
-        <v>29.23501070663811</v>
+        <v>72.95208779443256</v>
       </c>
     </row>
     <row r="818" spans="1:22">
       <c r="A818" s="6" t="s">
-        <v>2286</v>
+        <v>2294</v>
       </c>
       <c r="B818" s="7" t="s">
-        <v>2287</v>
+        <v>2295</v>
       </c>
       <c r="C818" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D818" s="7" t="s">
-        <v>49</v>
+        <v>2234</v>
       </c>
       <c r="E818" s="8">
-        <v>4355.019264</v>
+        <v>32.29668</v>
       </c>
       <c r="F818" s="7" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
       <c r="G818" s="8">
-        <v>30</v>
+        <v>1.65599</v>
       </c>
       <c r="H818" s="7" t="s">
-        <v>2288</v>
+        <v>2296</v>
       </c>
       <c r="I818" s="9">
-        <v>3.448275862068972</v>
+        <v>-2.152770227791623</v>
       </c>
       <c r="J818" s="9">
-        <v>-53.84615384615385</v>
+        <v>1593.76086734172</v>
       </c>
       <c r="K818" s="9">
-        <v>109.2054816869239</v>
-      </c>
-      <c r="L818" s="10" t="s">
-        <v>30</v>
+        <v>1222.56317573802</v>
+      </c>
+      <c r="L818" s="9">
+        <v>606.2967369012872</v>
       </c>
       <c r="M818" s="9">
-        <v>346.4728280985287</v>
+        <v>1317.26201447137</v>
       </c>
       <c r="N818" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O818" s="8">
-        <v>7431.019264</v>
+        <v>33.971092</v>
       </c>
       <c r="P818" s="11">
-        <v>0.0040371312378823</v>
-      </c>
-      <c r="Q818" s="9">
-        <v>8.892541790531471</v>
-      </c>
-      <c r="R818" s="9">
-        <v>23.82800732749847</v>
-      </c>
-      <c r="S818" s="11">
-        <v>8.660861613053614</v>
+        <v>0.0487470346846665</v>
+      </c>
+      <c r="Q818" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R818" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S818" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T818" s="9">
-        <v>2.9333968980579</v>
+        <v>-13.61075194106638</v>
       </c>
       <c r="U818" s="9">
-        <v>8</v>
-      </c>
-      <c r="V818" s="11">
-        <v>32.94967880085653</v>
+        <v>1508</v>
+      </c>
+      <c r="V818" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="819" spans="1:22">
       <c r="A819" s="6" t="s">
-        <v>1924</v>
+        <v>2297</v>
       </c>
       <c r="B819" s="7" t="s">
-        <v>1925</v>
+        <v>2298</v>
       </c>
       <c r="C819" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D819" s="7" t="s">
-        <v>49</v>
+        <v>307</v>
       </c>
       <c r="E819" s="8">
-        <v>4596.016128</v>
+        <v>121.6679051485062</v>
       </c>
       <c r="F819" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G819" s="8">
-        <v>0.621</v>
+        <v>3.028</v>
       </c>
       <c r="H819" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I819" s="9">
         <v>0</v>
       </c>
       <c r="J819" s="9">
-        <v>514.8514851485148</v>
+        <v>1257.847533632287</v>
       </c>
       <c r="K819" s="9">
-        <v>94.50966790084108</v>
+        <v>658.7331710457566</v>
       </c>
       <c r="L819" s="9">
-        <v>102.7798620924616</v>
+        <v>307.7056459735916</v>
       </c>
       <c r="M819" s="9">
-        <v>326.8664985984774</v>
-      </c>
-      <c r="N819" s="10" t="s">
-        <v>30</v>
+        <v>1274.548766084603</v>
+      </c>
+      <c r="N819" s="11">
+        <v>0.0077674883923761</v>
       </c>
       <c r="O819" s="8">
-        <v>4268.588128</v>
+        <v>124.6889051485062</v>
       </c>
       <c r="P819" s="11">
-        <v>0.0001454813585612</v>
+        <v>0.0242844381093378</v>
       </c>
       <c r="Q819" s="9">
-        <v>4.0228449328489</v>
+        <v>5.50919798972899</v>
       </c>
       <c r="R819" s="9">
-        <v>51.57783481534709</v>
+        <v>76.58554383206992</v>
       </c>
       <c r="S819" s="11">
-        <v>31.74922366438976</v>
-      </c>
-      <c r="T819" s="9">
-        <v>3.09196861025462</v>
-      </c>
-      <c r="U819" s="9">
-        <v>14.1</v>
+        <v>6.094276888978796</v>
+      </c>
+      <c r="T819" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U819" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="V819" s="11">
-        <v>60.26258029978587</v>
+        <v>25.80085653104925</v>
       </c>
     </row>
     <row r="820" spans="1:22">
       <c r="A820" s="6" t="s">
-        <v>1269</v>
+        <v>2299</v>
       </c>
       <c r="B820" s="7" t="s">
-        <v>1270</v>
+        <v>2300</v>
       </c>
       <c r="C820" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D820" s="7" t="s">
-        <v>49</v>
+        <v>2234</v>
       </c>
       <c r="E820" s="8">
-        <v>10995.61919360275</v>
+        <v>74.96236</v>
       </c>
       <c r="F820" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G820" s="8">
-        <v>55.229</v>
+        <v>0.5</v>
       </c>
       <c r="H820" s="7" t="s">
-        <v>2239</v>
+        <v>2301</v>
       </c>
       <c r="I820" s="9">
-        <v>-31.53712656501797</v>
-      </c>
-      <c r="J820" s="9">
-        <v>236.3315267036112</v>
+        <v>0</v>
+      </c>
+      <c r="J820" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="K820" s="9">
-        <v>188.9625461918627</v>
-      </c>
-      <c r="L820" s="10" t="s">
-        <v>30</v>
+        <v>525.8139275052935</v>
+      </c>
+      <c r="L820" s="9">
+        <v>273.4401331530191</v>
       </c>
       <c r="M820" s="9">
-        <v>321.7457924482902</v>
-      </c>
-      <c r="N820" s="11">
-        <v>0.0382982588989762</v>
+        <v>1209.149254860081</v>
+      </c>
+      <c r="N820" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="O820" s="8">
-        <v>11011.60619360275</v>
+        <v>71.50836</v>
       </c>
       <c r="P820" s="11">
-        <v>0.0050155262573851</v>
-      </c>
-      <c r="Q820" s="9">
-        <v>17.79581484188693</v>
-      </c>
-      <c r="R820" s="9">
-        <v>-88.97705134473316</v>
-      </c>
-      <c r="S820" s="11">
-        <v>48.84516961840122</v>
+        <v>0.0069921894447026</v>
+      </c>
+      <c r="Q820" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R820" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S820" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T820" s="10" t="s">
         <v>30</v>
@@ -61064,543 +61124,543 @@
       <c r="U820" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V820" s="11">
-        <v>25.82012847965738</v>
+      <c r="V820" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="821" spans="1:22">
       <c r="A821" s="6" t="s">
-        <v>2289</v>
+        <v>2302</v>
       </c>
       <c r="B821" s="7" t="s">
-        <v>2290</v>
+        <v>2303</v>
       </c>
       <c r="C821" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D821" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E821" s="8">
-        <v>1960815.624192</v>
+        <v>2234</v>
+      </c>
+      <c r="E821" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F821" s="7" t="s">
-        <v>2232</v>
+        <v>2249</v>
       </c>
       <c r="G821" s="8">
-        <v>164600</v>
+        <v>0.01</v>
       </c>
       <c r="H821" s="7" t="s">
-        <v>2291</v>
+        <v>2236</v>
       </c>
       <c r="I821" s="9">
-        <v>265.7777777777778</v>
+        <v>0</v>
       </c>
       <c r="J821" s="9">
-        <v>566.3967611336031</v>
+        <v>900</v>
       </c>
       <c r="K821" s="9">
-        <v>189.8614059496949</v>
+        <v>400.0919770278175</v>
       </c>
       <c r="L821" s="9">
-        <v>93.5278692544897</v>
+        <v>173.0315691003408</v>
       </c>
       <c r="M821" s="9">
-        <v>313.4241357572719</v>
-      </c>
-      <c r="N821" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O821" s="8">
-        <v>2012698.622976</v>
-      </c>
-      <c r="P821" s="11">
-        <v>0.08178074855371061</v>
-      </c>
-      <c r="Q821" s="9">
-        <v>11.0112121540463</v>
-      </c>
-      <c r="R821" s="9">
-        <v>-10.8307179914174</v>
-      </c>
-      <c r="S821" s="11">
-        <v>54.07863330973037</v>
-      </c>
-      <c r="T821" s="9">
-        <v>1.30067048779812</v>
-      </c>
-      <c r="U821" s="9">
-        <v>29.5</v>
-      </c>
-      <c r="V821" s="11">
-        <v>56.4973233404711</v>
+        <v>999.8241469610572</v>
+      </c>
+      <c r="N821" s="11">
+        <v>0.2583979328165374</v>
+      </c>
+      <c r="O821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U821" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V821" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="822" spans="1:22">
       <c r="A822" s="6" t="s">
-        <v>2113</v>
+        <v>2304</v>
       </c>
       <c r="B822" s="7" t="s">
-        <v>2114</v>
+        <v>2305</v>
       </c>
       <c r="C822" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D822" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E822" s="8">
-        <v>51.97174673283005</v>
+        <v>1989.49632</v>
       </c>
       <c r="F822" s="7" t="s">
-        <v>2238</v>
+        <v>139</v>
       </c>
       <c r="G822" s="8">
-        <v>24.428</v>
+        <v>2.2</v>
       </c>
       <c r="H822" s="7" t="s">
-        <v>2253</v>
+        <v>2306</v>
       </c>
       <c r="I822" s="9">
-        <v>248.5233271508061</v>
+        <v>-3.169014084507038</v>
       </c>
       <c r="J822" s="9">
-        <v>517.4924165824065</v>
+        <v>1000</v>
       </c>
       <c r="K822" s="9">
-        <v>167.7944624310711</v>
-      </c>
-      <c r="L822" s="9">
-        <v>81.82622858551376</v>
+        <v>546.5</v>
+      </c>
+      <c r="L822" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M822" s="9">
-        <v>264.8222064236053</v>
-      </c>
-      <c r="N822" s="10" t="s">
-        <v>30</v>
+        <v>963.8333333333334</v>
+      </c>
+      <c r="N822" s="11">
+        <v>0.0035311584607359</v>
       </c>
       <c r="O822" s="8">
-        <v>165.59443673283</v>
+        <v>1665.866312</v>
       </c>
       <c r="P822" s="11">
-        <v>0.1475170330716612</v>
-      </c>
-      <c r="Q822" s="9">
-        <v>-0.24148789738567</v>
-      </c>
-      <c r="R822" s="9">
-        <v>200</v>
-      </c>
-      <c r="S822" s="11">
-        <v>26.43589347586686</v>
-      </c>
-      <c r="T822" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="U822" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V822" s="11">
-        <v>21.44539614561028</v>
+        <v>0.0013206341854399</v>
+      </c>
+      <c r="Q822" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R822" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S822" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T822" s="9">
+        <v>8.075598953608509</v>
+      </c>
+      <c r="U822" s="9">
+        <v>41</v>
+      </c>
+      <c r="V822" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="823" spans="1:22">
       <c r="A823" s="6" t="s">
-        <v>2118</v>
+        <v>2307</v>
       </c>
       <c r="B823" s="7" t="s">
-        <v>2114</v>
+        <v>2308</v>
       </c>
       <c r="C823" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D823" s="7" t="s">
-        <v>307</v>
+        <v>2234</v>
       </c>
       <c r="E823" s="8">
-        <v>60.26884763805008</v>
+        <v>36.406964</v>
       </c>
       <c r="F823" s="7" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="G823" s="8">
-        <v>24.428</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H823" s="7" t="s">
-        <v>2253</v>
+        <v>2309</v>
       </c>
       <c r="I823" s="9">
-        <v>248.5233271508061</v>
+        <v>6.014150943396235</v>
       </c>
       <c r="J823" s="9">
-        <v>517.4924165824065</v>
+        <v>1596.22641509434</v>
       </c>
       <c r="K823" s="9">
-        <v>167.7944624310711</v>
-      </c>
-      <c r="L823" s="9">
-        <v>81.82622858551376</v>
+        <v>1234.038352973427</v>
+      </c>
+      <c r="L823" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="M823" s="9">
-        <v>264.8222064236053</v>
+        <v>931.1311334034548</v>
       </c>
       <c r="N823" s="10" t="s">
         <v>30</v>
       </c>
       <c r="O823" s="8">
-        <v>173.8915376380501</v>
+        <v>28.862964</v>
       </c>
       <c r="P823" s="11">
-        <v>0.1404783713560928</v>
-      </c>
-      <c r="Q823" s="9">
-        <v>-0.24148789738567</v>
-      </c>
-      <c r="R823" s="9">
-        <v>200</v>
-      </c>
-      <c r="S823" s="11">
-        <v>27.76046258589561</v>
-      </c>
-      <c r="T823" s="10" t="s">
-        <v>30</v>
+        <v>3.114718225058244</v>
+      </c>
+      <c r="Q823" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R823" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S823" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T823" s="9">
+        <v>-39.02618740744216</v>
       </c>
       <c r="U823" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V823" s="11">
-        <v>82.09421841541756</v>
+      <c r="V823" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="824" spans="1:22">
       <c r="A824" s="6" t="s">
-        <v>2292</v>
+        <v>2310</v>
       </c>
       <c r="B824" s="7" t="s">
-        <v>2293</v>
+        <v>2311</v>
       </c>
       <c r="C824" s="7" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="D824" s="7" t="s">
-        <v>29</v>
+        <v>2234</v>
       </c>
       <c r="E824" s="8">
-        <v>26628.888576</v>
+        <v>76.98868</v>
       </c>
       <c r="F824" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G824" s="8">
-        <v>165.5</v>
+        <v>2.501</v>
       </c>
       <c r="H824" s="7" t="s">
-        <v>2239</v>
+        <v>2312</v>
       </c>
       <c r="I824" s="9">
-        <v>-6.391402714932126</v>
+        <v>693.968253968254</v>
       </c>
       <c r="J824" s="9">
-        <v>583.8842975206612</v>
+        <v>950.8403361344538</v>
       </c>
       <c r="K824" s="9">
-        <v>646.9382419072057</v>
+        <v>365.4101294520522</v>
       </c>
       <c r="L824" s="9">
-        <v>345.8981819005685</v>
+        <v>193.5947611729981</v>
       </c>
       <c r="M824" s="9">
-        <v>261.1769169288284</v>
+        <v>840.4401155042299</v>
       </c>
       <c r="N824" s="11">
-        <v>0.0425111093986797</v>
+        <v>0.4375437368789363</v>
       </c>
       <c r="O824" s="8">
-        <v>28136.28864</v>
+        <v>103.16368</v>
       </c>
       <c r="P824" s="11">
-        <v>0.005882083529834</v>
-      </c>
-      <c r="Q824" s="9">
-        <v>8.118229074269429</v>
-      </c>
-      <c r="R824" s="9">
-        <v>200</v>
-      </c>
-      <c r="S824" s="11">
-        <v>30.44393923393205</v>
+        <v>0.024243028166502</v>
+      </c>
+      <c r="Q824" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R824" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S824" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T824" s="9">
-        <v>0.78814783200961</v>
+        <v>-23.95644398631071</v>
       </c>
       <c r="U824" s="9">
-        <v>53.5</v>
-      </c>
-      <c r="V824" s="11">
-        <v>81.00160599571734</v>
+        <v>-40.1</v>
+      </c>
+      <c r="V824" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="825" spans="1:22">
       <c r="A825" s="6" t="s">
-        <v>2294</v>
+        <v>2313</v>
       </c>
       <c r="B825" s="7" t="s">
-        <v>2295</v>
+        <v>2314</v>
       </c>
       <c r="C825" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D825" s="7" t="s">
-        <v>106</v>
+        <v>2234</v>
       </c>
       <c r="E825" s="8">
-        <v>4639851.282432</v>
+        <v>1230.078592</v>
       </c>
       <c r="F825" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G825" s="8">
-        <v>467600</v>
+        <v>0.149</v>
       </c>
       <c r="H825" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I825" s="9">
-        <v>92.58649093904448</v>
+        <v>-81.09137055837563</v>
       </c>
       <c r="J825" s="9">
-        <v>406.0606060606061</v>
+        <v>2.758620689655178</v>
       </c>
       <c r="K825" s="9">
-        <v>171.3918249599135</v>
+        <v>445.5465193760228</v>
       </c>
       <c r="L825" s="9">
-        <v>100.3210974111782</v>
+        <v>230.9672876779952</v>
       </c>
       <c r="M825" s="9">
-        <v>240.233832112555</v>
-      </c>
-      <c r="N825" s="11">
-        <v>1.16077013970946</v>
+        <v>827.6715262277987</v>
+      </c>
+      <c r="N825" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="O825" s="8">
-        <v>4608887.283712</v>
+        <v>1434.773592</v>
       </c>
       <c r="P825" s="11">
-        <v>0.1014561587679781</v>
-      </c>
-      <c r="Q825" s="9">
-        <v>25.03282644465509</v>
-      </c>
-      <c r="R825" s="9">
-        <v>11.12911157064614</v>
-      </c>
-      <c r="S825" s="11">
-        <v>28.57055349779965</v>
+        <v>0.0001038491374742</v>
+      </c>
+      <c r="Q825" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R825" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S825" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T825" s="9">
-        <v>0.60178114160082</v>
+        <v>-0.41019736729147</v>
       </c>
       <c r="U825" s="9">
-        <v>21.8</v>
-      </c>
-      <c r="V825" s="11">
-        <v>41.17612419700214</v>
+        <v>-7.6</v>
+      </c>
+      <c r="V825" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="826" spans="1:22">
       <c r="A826" s="6" t="s">
-        <v>2296</v>
+        <v>2315</v>
       </c>
       <c r="B826" s="7" t="s">
-        <v>2295</v>
+        <v>2316</v>
       </c>
       <c r="C826" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D826" s="7" t="s">
-        <v>106</v>
+        <v>2234</v>
       </c>
       <c r="E826" s="8">
-        <v>4596356.87424</v>
+        <v>2.660022</v>
       </c>
       <c r="F826" s="7" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G826" s="8">
-        <v>467600</v>
+        <v>0.03</v>
       </c>
       <c r="H826" s="7" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="I826" s="9">
-        <v>92.58649093904448</v>
+        <v>-90.99099099099099</v>
       </c>
       <c r="J826" s="9">
-        <v>406.0606060606061</v>
+        <v>-62.0253164556962</v>
       </c>
       <c r="K826" s="9">
-        <v>171.3918249599135</v>
+        <v>379.0272565282734</v>
       </c>
       <c r="L826" s="9">
-        <v>100.3210974111782</v>
+        <v>166.1650801034549</v>
       </c>
       <c r="M826" s="9">
-        <v>240.233832112555</v>
-      </c>
-      <c r="N826" s="11">
-        <v>1.16077013970946</v>
+        <v>792.2623913213265</v>
+      </c>
+      <c r="N826" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="O826" s="8">
-        <v>4565392.87552</v>
-      </c>
-      <c r="P826" s="11">
-        <v>0.1024227295984335</v>
-      </c>
-      <c r="Q826" s="9">
-        <v>25.03282644465509</v>
-      </c>
-      <c r="R826" s="9">
-        <v>11.12911157064614</v>
-      </c>
-      <c r="S826" s="11">
-        <v>28.30093108362253</v>
+        <v>-5.568978</v>
+      </c>
+      <c r="P826" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q826" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R826" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S826" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T826" s="9">
-        <v>0.6074756764968701</v>
+        <v>-502.3031764398941</v>
       </c>
       <c r="U826" s="9">
-        <v>21.8</v>
-      </c>
-      <c r="V826" s="11">
-        <v>41.17612419700214</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="V826" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="827" spans="1:22">
       <c r="A827" s="6" t="s">
-        <v>2297</v>
+        <v>2317</v>
       </c>
       <c r="B827" s="7" t="s">
-        <v>2298</v>
+        <v>2318</v>
       </c>
       <c r="C827" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D827" s="7" t="s">
-        <v>275</v>
+        <v>2234</v>
       </c>
       <c r="E827" s="8">
-        <v>0.243934</v>
+        <v>3.821762</v>
       </c>
       <c r="F827" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G827" s="8">
-        <v>1.751</v>
+        <v>0.2108</v>
       </c>
       <c r="H827" s="7" t="s">
-        <v>2242</v>
+        <v>2236</v>
       </c>
       <c r="I827" s="9">
-        <v>87450</v>
+        <v>-46.75853429376762</v>
       </c>
       <c r="J827" s="9">
-        <v>714.4186046511628</v>
+        <v>1586.4</v>
       </c>
       <c r="K827" s="9">
-        <v>256.8758336473517</v>
+        <v>691.0159326687772</v>
       </c>
       <c r="L827" s="9">
-        <v>107.4867881481619</v>
+        <v>341.6305883569818</v>
       </c>
       <c r="M827" s="9">
-        <v>227.3095289211809</v>
+        <v>785.1462062351299</v>
       </c>
       <c r="N827" s="11">
-        <v>0.07668389244109659</v>
+        <v>0.0142248566548778</v>
       </c>
       <c r="O827" s="8">
-        <v>9.016933999999999</v>
+        <v>1.558995</v>
       </c>
       <c r="P827" s="11">
-        <v>0.1941901759511603</v>
-      </c>
-      <c r="Q827" s="9">
-        <v>-74.14299950469531</v>
+        <v>0.1352153149945958</v>
+      </c>
+      <c r="Q827" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="R827" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="S827" s="11">
-        <v>-6.482339324227175</v>
+      <c r="S827" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T827" s="9">
-        <v>382.2242901768511</v>
+        <v>-25.10611597477812</v>
       </c>
       <c r="U827" s="9">
-        <v>-1.3</v>
-      </c>
-      <c r="V827" s="11">
-        <v>45.90283725910064</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V827" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="828" spans="1:22">
       <c r="A828" s="6" t="s">
-        <v>2299</v>
+        <v>2319</v>
       </c>
       <c r="B828" s="7" t="s">
-        <v>2300</v>
+        <v>2320</v>
       </c>
       <c r="C828" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D828" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E828" s="8">
-        <v>107.931804</v>
+        <v>2234</v>
+      </c>
+      <c r="E828" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F828" s="7" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="G828" s="8">
-        <v>0.450579</v>
+        <v>0.428346</v>
       </c>
       <c r="H828" s="7" t="s">
-        <v>2301</v>
-      </c>
-      <c r="I828" s="9">
-        <v>89.28391389827091</v>
+        <v>2236</v>
+      </c>
+      <c r="I828" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J828" s="9">
-        <v>316.8939674315322</v>
+        <v>1684.775</v>
       </c>
       <c r="K828" s="9">
-        <v>61.89283681371892</v>
+        <v>396.19375</v>
       </c>
       <c r="L828" s="9">
-        <v>4.480610146636074</v>
+        <v>203.7923340551517</v>
       </c>
       <c r="M828" s="9">
-        <v>224.157364702105</v>
+        <v>736.9363721804511</v>
       </c>
       <c r="N828" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O828" s="8">
-        <v>103.473736</v>
-      </c>
-      <c r="P828" s="11">
-        <v>0.0043545252874603</v>
-      </c>
-      <c r="Q828" s="9">
-        <v>0.18734908473256</v>
-      </c>
-      <c r="R828" s="9">
-        <v>41.82000153020221</v>
-      </c>
-      <c r="S828" s="11">
-        <v>99.00229724493262</v>
+      <c r="O828" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P828" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q828" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R828" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S828" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="T828" s="10" t="s">
         <v>30</v>
@@ -61608,13 +61668,13 @@
       <c r="U828" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="V828" s="11">
-        <v>22.72216274089936</v>
+      <c r="V828" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="830" spans="1:22" ht="22" customHeight="1">
       <c r="A830" s="4" t="s">
-        <v>2302</v>
+        <v>2321</v>
       </c>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -61844,10 +61904,10 @@
     </row>
     <row r="834" spans="1:22">
       <c r="A834" s="6" t="s">
-        <v>2303</v>
+        <v>2322</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>2304</v>
+        <v>2323</v>
       </c>
       <c r="C834" s="7" t="s">
         <v>579</v>
@@ -61912,10 +61972,10 @@
     </row>
     <row r="835" spans="1:22">
       <c r="A835" s="6" t="s">
-        <v>2305</v>
+        <v>2324</v>
       </c>
       <c r="B835" s="7" t="s">
-        <v>2306</v>
+        <v>2325</v>
       </c>
       <c r="C835" s="7" t="s">
         <v>671</v>
@@ -61980,10 +62040,10 @@
     </row>
     <row r="836" spans="1:22">
       <c r="A836" s="6" t="s">
-        <v>2307</v>
+        <v>2326</v>
       </c>
       <c r="B836" s="7" t="s">
-        <v>2308</v>
+        <v>2327</v>
       </c>
       <c r="C836" s="7" t="s">
         <v>452</v>
@@ -62048,10 +62108,10 @@
     </row>
     <row r="837" spans="1:22">
       <c r="A837" s="6" t="s">
-        <v>2309</v>
+        <v>2328</v>
       </c>
       <c r="B837" s="7" t="s">
-        <v>2310</v>
+        <v>2329</v>
       </c>
       <c r="C837" s="7" t="s">
         <v>28</v>
@@ -62116,10 +62176,10 @@
     </row>
     <row r="838" spans="1:22">
       <c r="A838" s="6" t="s">
-        <v>2311</v>
+        <v>2330</v>
       </c>
       <c r="B838" s="7" t="s">
-        <v>2312</v>
+        <v>2331</v>
       </c>
       <c r="C838" s="7" t="s">
         <v>710</v>
@@ -62184,7 +62244,7 @@
     </row>
     <row r="839" spans="1:22">
       <c r="A839" s="6" t="s">
-        <v>2313</v>
+        <v>2332</v>
       </c>
       <c r="B839" s="7" t="s">
         <v>709</v>
@@ -62252,16 +62312,16 @@
     </row>
     <row r="840" spans="1:22">
       <c r="A840" s="6" t="s">
-        <v>2314</v>
+        <v>2333</v>
       </c>
       <c r="B840" s="7" t="s">
-        <v>2315</v>
+        <v>2334</v>
       </c>
       <c r="C840" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D840" s="7" t="s">
-        <v>2316</v>
+        <v>2234</v>
       </c>
       <c r="E840" s="10" t="s">
         <v>30</v>
@@ -62320,10 +62380,10 @@
     </row>
     <row r="841" spans="1:22">
       <c r="A841" s="6" t="s">
-        <v>2317</v>
+        <v>2335</v>
       </c>
       <c r="B841" s="7" t="s">
-        <v>2318</v>
+        <v>2336</v>
       </c>
       <c r="C841" s="7" t="s">
         <v>28</v>
@@ -62388,10 +62448,10 @@
     </row>
     <row r="842" spans="1:22">
       <c r="A842" s="6" t="s">
-        <v>2319</v>
+        <v>2337</v>
       </c>
       <c r="B842" s="7" t="s">
-        <v>2320</v>
+        <v>2338</v>
       </c>
       <c r="C842" s="7" t="s">
         <v>28</v>
@@ -62456,10 +62516,10 @@
     </row>
     <row r="843" spans="1:22">
       <c r="A843" s="6" t="s">
-        <v>2321</v>
+        <v>2339</v>
       </c>
       <c r="B843" s="7" t="s">
-        <v>2322</v>
+        <v>2340</v>
       </c>
       <c r="C843" s="7" t="s">
         <v>666</v>
@@ -62524,10 +62584,10 @@
     </row>
     <row r="844" spans="1:22">
       <c r="A844" s="6" t="s">
-        <v>2323</v>
+        <v>2341</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>2324</v>
+        <v>2342</v>
       </c>
       <c r="C844" s="7" t="s">
         <v>620</v>
@@ -62592,7 +62652,7 @@
     </row>
     <row r="845" spans="1:22">
       <c r="A845" s="6" t="s">
-        <v>2325</v>
+        <v>2343</v>
       </c>
       <c r="B845" s="7" t="s">
         <v>437</v>
@@ -62660,10 +62720,10 @@
     </row>
     <row r="846" spans="1:22">
       <c r="A846" s="6" t="s">
-        <v>2326</v>
+        <v>2344</v>
       </c>
       <c r="B846" s="7" t="s">
-        <v>2327</v>
+        <v>2345</v>
       </c>
       <c r="C846" s="7" t="s">
         <v>597</v>
@@ -62728,10 +62788,10 @@
     </row>
     <row r="847" spans="1:22">
       <c r="A847" s="6" t="s">
-        <v>2328</v>
+        <v>2346</v>
       </c>
       <c r="B847" s="7" t="s">
-        <v>2329</v>
+        <v>2347</v>
       </c>
       <c r="C847" s="7" t="s">
         <v>296</v>
@@ -62796,10 +62856,10 @@
     </row>
     <row r="848" spans="1:22">
       <c r="A848" s="6" t="s">
-        <v>2330</v>
+        <v>2348</v>
       </c>
       <c r="B848" s="7" t="s">
-        <v>2331</v>
+        <v>2349</v>
       </c>
       <c r="C848" s="7" t="s">
         <v>257</v>
@@ -62932,10 +62992,10 @@
     </row>
     <row r="850" spans="1:22">
       <c r="A850" s="6" t="s">
-        <v>2332</v>
+        <v>2350</v>
       </c>
       <c r="B850" s="7" t="s">
-        <v>2333</v>
+        <v>2351</v>
       </c>
       <c r="C850" s="7" t="s">
         <v>710</v>
@@ -63000,10 +63060,10 @@
     </row>
     <row r="851" spans="1:22">
       <c r="A851" s="6" t="s">
-        <v>2334</v>
+        <v>2352</v>
       </c>
       <c r="B851" s="7" t="s">
-        <v>2335</v>
+        <v>2353</v>
       </c>
       <c r="C851" s="7" t="s">
         <v>494</v>
@@ -63068,10 +63128,10 @@
     </row>
     <row r="852" spans="1:22">
       <c r="A852" s="6" t="s">
-        <v>2336</v>
+        <v>2354</v>
       </c>
       <c r="B852" s="7" t="s">
-        <v>2337</v>
+        <v>2355</v>
       </c>
       <c r="C852" s="7" t="s">
         <v>579</v>
@@ -63136,10 +63196,10 @@
     </row>
     <row r="853" spans="1:22">
       <c r="A853" s="6" t="s">
-        <v>2338</v>
+        <v>2356</v>
       </c>
       <c r="B853" s="7" t="s">
-        <v>2339</v>
+        <v>2357</v>
       </c>
       <c r="C853" s="7" t="s">
         <v>257</v>
@@ -63204,10 +63264,10 @@
     </row>
     <row r="854" spans="1:22">
       <c r="A854" s="6" t="s">
-        <v>2340</v>
+        <v>2358</v>
       </c>
       <c r="B854" s="7" t="s">
-        <v>2341</v>
+        <v>2359</v>
       </c>
       <c r="C854" s="7" t="s">
         <v>431</v>
@@ -63272,10 +63332,10 @@
     </row>
     <row r="855" spans="1:22">
       <c r="A855" s="6" t="s">
-        <v>2342</v>
+        <v>2360</v>
       </c>
       <c r="B855" s="7" t="s">
-        <v>2343</v>
+        <v>2361</v>
       </c>
       <c r="C855" s="7" t="s">
         <v>318</v>
@@ -63340,10 +63400,10 @@
     </row>
     <row r="856" spans="1:22">
       <c r="A856" s="6" t="s">
-        <v>2344</v>
+        <v>2362</v>
       </c>
       <c r="B856" s="7" t="s">
-        <v>2345</v>
+        <v>2363</v>
       </c>
       <c r="C856" s="7" t="s">
         <v>666</v>
@@ -63408,7 +63468,7 @@
     </row>
     <row r="858" spans="1:22" ht="22" customHeight="1">
       <c r="A858" s="4" t="s">
-        <v>2346</v>
+        <v>2364</v>
       </c>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -63638,7 +63698,7 @@
     </row>
     <row r="862" spans="1:22">
       <c r="A862" s="6" t="s">
-        <v>2347</v>
+        <v>2365</v>
       </c>
       <c r="B862" s="10" t="s">
         <v>30</v>
@@ -63706,7 +63766,7 @@
     </row>
     <row r="863" spans="1:22">
       <c r="A863" s="6" t="s">
-        <v>2348</v>
+        <v>2366</v>
       </c>
       <c r="B863" s="10" t="s">
         <v>30</v>
@@ -63774,10 +63834,10 @@
     </row>
     <row r="864" spans="1:22">
       <c r="A864" s="6" t="s">
-        <v>2349</v>
+        <v>2367</v>
       </c>
       <c r="B864" s="7" t="s">
-        <v>2350</v>
+        <v>2368</v>
       </c>
       <c r="C864" s="7" t="s">
         <v>414</v>
@@ -63842,10 +63902,10 @@
     </row>
     <row r="865" spans="1:22">
       <c r="A865" s="6" t="s">
-        <v>2351</v>
+        <v>2369</v>
       </c>
       <c r="B865" s="7" t="s">
-        <v>2352</v>
+        <v>2370</v>
       </c>
       <c r="C865" s="7" t="s">
         <v>253</v>
@@ -63978,10 +64038,10 @@
     </row>
     <row r="867" spans="1:22">
       <c r="A867" s="6" t="s">
-        <v>2353</v>
+        <v>2371</v>
       </c>
       <c r="B867" s="7" t="s">
-        <v>2354</v>
+        <v>2372</v>
       </c>
       <c r="C867" s="7" t="s">
         <v>431</v>
@@ -64046,10 +64106,10 @@
     </row>
     <row r="868" spans="1:22">
       <c r="A868" s="6" t="s">
-        <v>2355</v>
+        <v>2373</v>
       </c>
       <c r="B868" s="7" t="s">
-        <v>2356</v>
+        <v>2374</v>
       </c>
       <c r="C868" s="7" t="s">
         <v>431</v>
@@ -64114,13 +64174,13 @@
     </row>
     <row r="869" spans="1:22">
       <c r="A869" s="6" t="s">
-        <v>2357</v>
+        <v>2375</v>
       </c>
       <c r="B869" s="7" t="s">
-        <v>2358</v>
+        <v>2376</v>
       </c>
       <c r="C869" s="7" t="s">
-        <v>2359</v>
+        <v>2377</v>
       </c>
       <c r="D869" s="7" t="s">
         <v>59</v>
@@ -64182,10 +64242,10 @@
     </row>
     <row r="870" spans="1:22">
       <c r="A870" s="6" t="s">
-        <v>2360</v>
+        <v>2378</v>
       </c>
       <c r="B870" s="7" t="s">
-        <v>2361</v>
+        <v>2379</v>
       </c>
       <c r="C870" s="7" t="s">
         <v>296</v>
@@ -64250,10 +64310,10 @@
     </row>
     <row r="871" spans="1:22">
       <c r="A871" s="6" t="s">
-        <v>2362</v>
+        <v>2380</v>
       </c>
       <c r="B871" s="7" t="s">
-        <v>2363</v>
+        <v>2381</v>
       </c>
       <c r="C871" s="7" t="s">
         <v>620</v>
@@ -64386,10 +64446,10 @@
     </row>
     <row r="873" spans="1:22">
       <c r="A873" s="6" t="s">
-        <v>2364</v>
+        <v>2382</v>
       </c>
       <c r="B873" s="7" t="s">
-        <v>2365</v>
+        <v>2383</v>
       </c>
       <c r="C873" s="7" t="s">
         <v>710</v>
@@ -64454,10 +64514,10 @@
     </row>
     <row r="874" spans="1:22">
       <c r="A874" s="6" t="s">
-        <v>2366</v>
+        <v>2384</v>
       </c>
       <c r="B874" s="7" t="s">
-        <v>2367</v>
+        <v>2385</v>
       </c>
       <c r="C874" s="7" t="s">
         <v>431</v>
@@ -64522,10 +64582,10 @@
     </row>
     <row r="875" spans="1:22">
       <c r="A875" s="6" t="s">
-        <v>2368</v>
+        <v>2386</v>
       </c>
       <c r="B875" s="7" t="s">
-        <v>2369</v>
+        <v>2387</v>
       </c>
       <c r="C875" s="7" t="s">
         <v>710</v>
@@ -64590,10 +64650,10 @@
     </row>
     <row r="876" spans="1:22">
       <c r="A876" s="6" t="s">
-        <v>2370</v>
+        <v>2388</v>
       </c>
       <c r="B876" s="7" t="s">
-        <v>2371</v>
+        <v>2389</v>
       </c>
       <c r="C876" s="7" t="s">
         <v>620</v>
@@ -64658,10 +64718,10 @@
     </row>
     <row r="877" spans="1:22">
       <c r="A877" s="6" t="s">
-        <v>2372</v>
+        <v>2390</v>
       </c>
       <c r="B877" s="7" t="s">
-        <v>2373</v>
+        <v>2391</v>
       </c>
       <c r="C877" s="7" t="s">
         <v>710</v>
@@ -64726,10 +64786,10 @@
     </row>
     <row r="878" spans="1:22">
       <c r="A878" s="6" t="s">
-        <v>2374</v>
+        <v>2392</v>
       </c>
       <c r="B878" s="7" t="s">
-        <v>2375</v>
+        <v>2393</v>
       </c>
       <c r="C878" s="7" t="s">
         <v>431</v>
@@ -64794,10 +64854,10 @@
     </row>
     <row r="879" spans="1:22">
       <c r="A879" s="6" t="s">
-        <v>2376</v>
+        <v>2394</v>
       </c>
       <c r="B879" s="7" t="s">
-        <v>2377</v>
+        <v>2395</v>
       </c>
       <c r="C879" s="7" t="s">
         <v>710</v>
@@ -64862,10 +64922,10 @@
     </row>
     <row r="880" spans="1:22">
       <c r="A880" s="6" t="s">
-        <v>2378</v>
+        <v>2396</v>
       </c>
       <c r="B880" s="7" t="s">
-        <v>2379</v>
+        <v>2397</v>
       </c>
       <c r="C880" s="7" t="s">
         <v>710</v>
@@ -64930,7 +64990,7 @@
     </row>
     <row r="881" spans="1:22">
       <c r="A881" s="6" t="s">
-        <v>2380</v>
+        <v>2398</v>
       </c>
       <c r="B881" s="7" t="s">
         <v>428</v>
@@ -64998,10 +65058,10 @@
     </row>
     <row r="882" spans="1:22">
       <c r="A882" s="6" t="s">
-        <v>2381</v>
+        <v>2399</v>
       </c>
       <c r="B882" s="7" t="s">
-        <v>2382</v>
+        <v>2400</v>
       </c>
       <c r="C882" s="7" t="s">
         <v>710</v>
@@ -65066,10 +65126,10 @@
     </row>
     <row r="883" spans="1:22">
       <c r="A883" s="6" t="s">
-        <v>2383</v>
+        <v>2401</v>
       </c>
       <c r="B883" s="7" t="s">
-        <v>2384</v>
+        <v>2402</v>
       </c>
       <c r="C883" s="7" t="s">
         <v>417</v>
@@ -65134,10 +65194,10 @@
     </row>
     <row r="884" spans="1:22">
       <c r="A884" s="6" t="s">
-        <v>2385</v>
+        <v>2403</v>
       </c>
       <c r="B884" s="7" t="s">
-        <v>2386</v>
+        <v>2404</v>
       </c>
       <c r="C884" s="7" t="s">
         <v>710</v>
@@ -65202,7 +65262,7 @@
     </row>
     <row r="886" spans="1:22" ht="22" customHeight="1">
       <c r="A886" s="4" t="s">
-        <v>2387</v>
+        <v>2405</v>
       </c>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -65944,7 +66004,7 @@
         <v>30</v>
       </c>
       <c r="M897" s="7" t="s">
-        <v>2388</v>
+        <v>2406</v>
       </c>
       <c r="N897" s="9">
         <v>45.82568729484686</v>
@@ -65976,7 +66036,7 @@
     </row>
     <row r="898" spans="1:22">
       <c r="A898" s="6" t="s">
-        <v>2389</v>
+        <v>2407</v>
       </c>
       <c r="B898" s="10" t="s">
         <v>30</v>
@@ -66112,10 +66172,10 @@
     </row>
     <row r="900" spans="1:22">
       <c r="A900" s="6" t="s">
-        <v>2390</v>
+        <v>2408</v>
       </c>
       <c r="B900" s="7" t="s">
-        <v>2391</v>
+        <v>2409</v>
       </c>
       <c r="C900" s="7" t="s">
         <v>318</v>
@@ -66248,10 +66308,10 @@
     </row>
     <row r="902" spans="1:22">
       <c r="A902" s="6" t="s">
-        <v>2392</v>
+        <v>2410</v>
       </c>
       <c r="B902" s="7" t="s">
-        <v>2393</v>
+        <v>2411</v>
       </c>
       <c r="C902" s="7" t="s">
         <v>579</v>
@@ -66384,7 +66444,7 @@
     </row>
     <row r="904" spans="1:22">
       <c r="A904" s="6" t="s">
-        <v>2394</v>
+        <v>2412</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>454</v>
@@ -66588,10 +66648,10 @@
     </row>
     <row r="907" spans="1:22">
       <c r="A907" s="6" t="s">
-        <v>2395</v>
+        <v>2413</v>
       </c>
       <c r="B907" s="7" t="s">
-        <v>2396</v>
+        <v>2414</v>
       </c>
       <c r="C907" s="7" t="s">
         <v>676</v>
@@ -66656,10 +66716,10 @@
     </row>
     <row r="908" spans="1:22">
       <c r="A908" s="6" t="s">
-        <v>2267</v>
+        <v>2415</v>
       </c>
       <c r="B908" s="7" t="s">
-        <v>2268</v>
+        <v>2416</v>
       </c>
       <c r="C908" s="7" t="s">
         <v>28</v>
@@ -66692,7 +66752,7 @@
         <v>30</v>
       </c>
       <c r="M908" s="7" t="s">
-        <v>2397</v>
+        <v>2417</v>
       </c>
       <c r="N908" s="9">
         <v>114.9863387978142</v>
@@ -66724,10 +66784,10 @@
     </row>
     <row r="909" spans="1:22">
       <c r="A909" s="6" t="s">
-        <v>2398</v>
+        <v>2418</v>
       </c>
       <c r="B909" s="7" t="s">
-        <v>2399</v>
+        <v>2419</v>
       </c>
       <c r="C909" s="7" t="s">
         <v>28</v>
@@ -66760,13 +66820,13 @@
         <v>30</v>
       </c>
       <c r="M909" s="7" t="s">
-        <v>2400</v>
+        <v>2420</v>
       </c>
       <c r="N909" s="9">
         <v>27.3723092205045</v>
       </c>
       <c r="O909" s="7" t="s">
-        <v>2401</v>
+        <v>2421</v>
       </c>
       <c r="P909" s="9">
         <v>201.9615894876492</v>
@@ -66792,10 +66852,10 @@
     </row>
     <row r="910" spans="1:22">
       <c r="A910" s="6" t="s">
-        <v>2402</v>
+        <v>2422</v>
       </c>
       <c r="B910" s="7" t="s">
-        <v>2403</v>
+        <v>2423</v>
       </c>
       <c r="C910" s="7" t="s">
         <v>615</v>
@@ -66860,7 +66920,7 @@
     </row>
     <row r="911" spans="1:22">
       <c r="A911" s="6" t="s">
-        <v>2404</v>
+        <v>2424</v>
       </c>
       <c r="B911" s="7" t="s">
         <v>447</v>
@@ -66928,10 +66988,10 @@
     </row>
     <row r="912" spans="1:22">
       <c r="A912" s="6" t="s">
-        <v>2405</v>
+        <v>2425</v>
       </c>
       <c r="B912" s="7" t="s">
-        <v>2406</v>
+        <v>2426</v>
       </c>
       <c r="C912" s="7" t="s">
         <v>597</v>
@@ -66996,7 +67056,7 @@
     </row>
     <row r="914" spans="1:22" ht="22" customHeight="1">
       <c r="A914" s="4" t="s">
-        <v>2407</v>
+        <v>2427</v>
       </c>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -67702,10 +67762,10 @@
     </row>
     <row r="925" spans="1:22">
       <c r="A925" s="6" t="s">
-        <v>2408</v>
+        <v>2428</v>
       </c>
       <c r="B925" s="7" t="s">
-        <v>2409</v>
+        <v>2429</v>
       </c>
       <c r="C925" s="7" t="s">
         <v>253</v>
@@ -67838,7 +67898,7 @@
     </row>
     <row r="927" spans="1:22">
       <c r="A927" s="6" t="s">
-        <v>2394</v>
+        <v>2412</v>
       </c>
       <c r="B927" s="7" t="s">
         <v>454</v>
@@ -67906,10 +67966,10 @@
     </row>
     <row r="928" spans="1:22">
       <c r="A928" s="6" t="s">
-        <v>2402</v>
+        <v>2422</v>
       </c>
       <c r="B928" s="7" t="s">
-        <v>2403</v>
+        <v>2423</v>
       </c>
       <c r="C928" s="7" t="s">
         <v>615</v>
@@ -67974,10 +68034,10 @@
     </row>
     <row r="929" spans="1:22">
       <c r="A929" s="6" t="s">
-        <v>2405</v>
+        <v>2425</v>
       </c>
       <c r="B929" s="7" t="s">
-        <v>2406</v>
+        <v>2426</v>
       </c>
       <c r="C929" s="7" t="s">
         <v>597</v>
@@ -68042,10 +68102,10 @@
     </row>
     <row r="930" spans="1:22">
       <c r="A930" s="6" t="s">
-        <v>2410</v>
+        <v>2430</v>
       </c>
       <c r="B930" s="7" t="s">
-        <v>2411</v>
+        <v>2431</v>
       </c>
       <c r="C930" s="7" t="s">
         <v>417</v>
@@ -68178,10 +68238,10 @@
     </row>
     <row r="932" spans="1:22">
       <c r="A932" s="6" t="s">
-        <v>2412</v>
+        <v>2432</v>
       </c>
       <c r="B932" s="7" t="s">
-        <v>2413</v>
+        <v>2433</v>
       </c>
       <c r="C932" s="7" t="s">
         <v>417</v>
@@ -68314,7 +68374,7 @@
     </row>
     <row r="934" spans="1:22">
       <c r="A934" s="6" t="s">
-        <v>2414</v>
+        <v>2434</v>
       </c>
       <c r="B934" s="7" t="s">
         <v>449</v>
@@ -68382,10 +68442,10 @@
     </row>
     <row r="935" spans="1:22">
       <c r="A935" s="6" t="s">
-        <v>2415</v>
+        <v>2435</v>
       </c>
       <c r="B935" s="7" t="s">
-        <v>2416</v>
+        <v>2436</v>
       </c>
       <c r="C935" s="7" t="s">
         <v>431</v>
@@ -68450,10 +68510,10 @@
     </row>
     <row r="936" spans="1:22">
       <c r="A936" s="6" t="s">
-        <v>2417</v>
+        <v>2437</v>
       </c>
       <c r="B936" s="7" t="s">
-        <v>2418</v>
+        <v>2438</v>
       </c>
       <c r="C936" s="7" t="s">
         <v>676</v>
@@ -68518,10 +68578,10 @@
     </row>
     <row r="937" spans="1:22">
       <c r="A937" s="6" t="s">
-        <v>2419</v>
+        <v>2439</v>
       </c>
       <c r="B937" s="7" t="s">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="C937" s="7" t="s">
         <v>452</v>
@@ -68586,10 +68646,10 @@
     </row>
     <row r="938" spans="1:22">
       <c r="A938" s="6" t="s">
-        <v>2421</v>
+        <v>2441</v>
       </c>
       <c r="B938" s="7" t="s">
-        <v>2422</v>
+        <v>2442</v>
       </c>
       <c r="C938" s="7" t="s">
         <v>253</v>
@@ -68654,10 +68714,10 @@
     </row>
     <row r="939" spans="1:22">
       <c r="A939" s="6" t="s">
-        <v>2423</v>
+        <v>2443</v>
       </c>
       <c r="B939" s="7" t="s">
-        <v>2424</v>
+        <v>2444</v>
       </c>
       <c r="C939" s="7" t="s">
         <v>253</v>
@@ -68722,10 +68782,10 @@
     </row>
     <row r="940" spans="1:22">
       <c r="A940" s="6" t="s">
-        <v>2425</v>
+        <v>2445</v>
       </c>
       <c r="B940" s="7" t="s">
-        <v>2426</v>
+        <v>2446</v>
       </c>
       <c r="C940" s="7" t="s">
         <v>417</v>
@@ -68790,7 +68850,7 @@
     </row>
     <row r="942" spans="1:22" ht="22" customHeight="1">
       <c r="A942" s="4" t="s">
-        <v>2427</v>
+        <v>2447</v>
       </c>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -69020,10 +69080,10 @@
     </row>
     <row r="946" spans="1:22">
       <c r="A946" s="6" t="s">
-        <v>2408</v>
+        <v>2428</v>
       </c>
       <c r="B946" s="7" t="s">
-        <v>2409</v>
+        <v>2429</v>
       </c>
       <c r="C946" s="7" t="s">
         <v>253</v>
@@ -69088,7 +69148,7 @@
     </row>
     <row r="947" spans="1:22">
       <c r="A947" s="6" t="s">
-        <v>2394</v>
+        <v>2412</v>
       </c>
       <c r="B947" s="7" t="s">
         <v>454</v>
@@ -69156,10 +69216,10 @@
     </row>
     <row r="948" spans="1:22">
       <c r="A948" s="6" t="s">
-        <v>2428</v>
+        <v>2448</v>
       </c>
       <c r="B948" s="7" t="s">
-        <v>2429</v>
+        <v>2449</v>
       </c>
       <c r="C948" s="7" t="s">
         <v>417</v>
@@ -69292,10 +69352,10 @@
     </row>
     <row r="950" spans="1:22">
       <c r="A950" s="6" t="s">
-        <v>2430</v>
+        <v>2450</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>2431</v>
+        <v>2451</v>
       </c>
       <c r="C950" s="7" t="s">
         <v>579</v>
@@ -69360,10 +69420,10 @@
     </row>
     <row r="951" spans="1:22">
       <c r="A951" s="6" t="s">
-        <v>2432</v>
+        <v>2452</v>
       </c>
       <c r="B951" s="7" t="s">
-        <v>2433</v>
+        <v>2453</v>
       </c>
       <c r="C951" s="7" t="s">
         <v>253</v>
@@ -69428,10 +69488,10 @@
     </row>
     <row r="952" spans="1:22">
       <c r="A952" s="6" t="s">
-        <v>2434</v>
+        <v>2454</v>
       </c>
       <c r="B952" s="7" t="s">
-        <v>2435</v>
+        <v>2455</v>
       </c>
       <c r="C952" s="7" t="s">
         <v>579</v>
@@ -69496,10 +69556,10 @@
     </row>
     <row r="953" spans="1:22">
       <c r="A953" s="6" t="s">
-        <v>2436</v>
+        <v>2456</v>
       </c>
       <c r="B953" s="7" t="s">
-        <v>2437</v>
+        <v>2457</v>
       </c>
       <c r="C953" s="7" t="s">
         <v>28</v>
@@ -69564,10 +69624,10 @@
     </row>
     <row r="954" spans="1:22">
       <c r="A954" s="6" t="s">
-        <v>2438</v>
+        <v>2458</v>
       </c>
       <c r="B954" s="7" t="s">
-        <v>2439</v>
+        <v>2459</v>
       </c>
       <c r="C954" s="7" t="s">
         <v>688</v>
@@ -69632,10 +69692,10 @@
     </row>
     <row r="955" spans="1:22">
       <c r="A955" s="6" t="s">
-        <v>2311</v>
+        <v>2330</v>
       </c>
       <c r="B955" s="7" t="s">
-        <v>2312</v>
+        <v>2331</v>
       </c>
       <c r="C955" s="7" t="s">
         <v>710</v>
@@ -69700,10 +69760,10 @@
     </row>
     <row r="956" spans="1:22">
       <c r="A956" s="6" t="s">
-        <v>2440</v>
+        <v>2460</v>
       </c>
       <c r="B956" s="7" t="s">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="C956" s="7" t="s">
         <v>431</v>
@@ -69768,10 +69828,10 @@
     </row>
     <row r="957" spans="1:22">
       <c r="A957" s="6" t="s">
-        <v>2442</v>
+        <v>2462</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>2443</v>
+        <v>2463</v>
       </c>
       <c r="C957" s="7" t="s">
         <v>28</v>
@@ -69836,10 +69896,10 @@
     </row>
     <row r="958" spans="1:22">
       <c r="A958" s="6" t="s">
-        <v>2444</v>
+        <v>2464</v>
       </c>
       <c r="B958" s="7" t="s">
-        <v>2445</v>
+        <v>2465</v>
       </c>
       <c r="C958" s="7" t="s">
         <v>28</v>
@@ -69904,10 +69964,10 @@
     </row>
     <row r="959" spans="1:22">
       <c r="A959" s="6" t="s">
-        <v>2446</v>
+        <v>2466</v>
       </c>
       <c r="B959" s="7" t="s">
-        <v>2447</v>
+        <v>2467</v>
       </c>
       <c r="C959" s="7" t="s">
         <v>597</v>
@@ -69972,10 +70032,10 @@
     </row>
     <row r="960" spans="1:22">
       <c r="A960" s="6" t="s">
-        <v>2448</v>
+        <v>2468</v>
       </c>
       <c r="B960" s="7" t="s">
-        <v>2449</v>
+        <v>2469</v>
       </c>
       <c r="C960" s="7" t="s">
         <v>688</v>
@@ -70040,10 +70100,10 @@
     </row>
     <row r="961" spans="1:22">
       <c r="A961" s="6" t="s">
-        <v>2450</v>
+        <v>2470</v>
       </c>
       <c r="B961" s="7" t="s">
-        <v>2451</v>
+        <v>2471</v>
       </c>
       <c r="C961" s="7" t="s">
         <v>494</v>
@@ -70108,10 +70168,10 @@
     </row>
     <row r="962" spans="1:22">
       <c r="A962" s="6" t="s">
-        <v>2452</v>
+        <v>2472</v>
       </c>
       <c r="B962" s="7" t="s">
-        <v>2453</v>
+        <v>2473</v>
       </c>
       <c r="C962" s="7" t="s">
         <v>710</v>
@@ -70176,10 +70236,10 @@
     </row>
     <row r="963" spans="1:22">
       <c r="A963" s="6" t="s">
-        <v>2330</v>
+        <v>2348</v>
       </c>
       <c r="B963" s="7" t="s">
-        <v>2331</v>
+        <v>2349</v>
       </c>
       <c r="C963" s="7" t="s">
         <v>257</v>
@@ -70244,10 +70304,10 @@
     </row>
     <row r="964" spans="1:22">
       <c r="A964" s="6" t="s">
-        <v>2454</v>
+        <v>2474</v>
       </c>
       <c r="B964" s="7" t="s">
-        <v>2455</v>
+        <v>2475</v>
       </c>
       <c r="C964" s="7" t="s">
         <v>376</v>
@@ -70312,10 +70372,10 @@
     </row>
     <row r="965" spans="1:22">
       <c r="A965" s="6" t="s">
-        <v>2456</v>
+        <v>2476</v>
       </c>
       <c r="B965" s="7" t="s">
-        <v>2457</v>
+        <v>2477</v>
       </c>
       <c r="C965" s="7" t="s">
         <v>28</v>
@@ -70348,13 +70408,13 @@
         <v>30</v>
       </c>
       <c r="M965" s="7" t="s">
-        <v>2458</v>
+        <v>2478</v>
       </c>
       <c r="N965" s="9">
         <v>59.53168685927307</v>
       </c>
       <c r="O965" s="7" t="s">
-        <v>2459</v>
+        <v>2479</v>
       </c>
       <c r="P965" s="9">
         <v>9.249709639953551</v>
@@ -70380,10 +70440,10 @@
     </row>
     <row r="966" spans="1:22">
       <c r="A966" s="6" t="s">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="B966" s="7" t="s">
-        <v>2461</v>
+        <v>2481</v>
       </c>
       <c r="C966" s="7" t="s">
         <v>620</v>
@@ -70448,10 +70508,10 @@
     </row>
     <row r="967" spans="1:22">
       <c r="A967" s="6" t="s">
-        <v>2462</v>
+        <v>2482</v>
       </c>
       <c r="B967" s="7" t="s">
-        <v>2463</v>
+        <v>2483</v>
       </c>
       <c r="C967" s="7" t="s">
         <v>710</v>
@@ -70516,10 +70576,10 @@
     </row>
     <row r="968" spans="1:22">
       <c r="A968" s="6" t="s">
-        <v>2464</v>
+        <v>2484</v>
       </c>
       <c r="B968" s="7" t="s">
-        <v>2465</v>
+        <v>2485</v>
       </c>
       <c r="C968" s="7" t="s">
         <v>257</v>
@@ -70584,7 +70644,7 @@
     </row>
     <row r="970" spans="1:22" ht="22" customHeight="1">
       <c r="A970" s="4" t="s">
-        <v>2466</v>
+        <v>2486</v>
       </c>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -70817,7 +70877,7 @@
         <v>1083</v>
       </c>
       <c r="B974" s="7" t="s">
-        <v>2467</v>
+        <v>2487</v>
       </c>
       <c r="C974" s="7" t="s">
         <v>28</v>
@@ -70924,7 +70984,7 @@
         <v>53.42455018949013</v>
       </c>
       <c r="O975" s="7" t="s">
-        <v>2468</v>
+        <v>2488</v>
       </c>
       <c r="P975" s="9">
         <v>26.88567771615129</v>
@@ -70950,10 +71010,10 @@
     </row>
     <row r="976" spans="1:22">
       <c r="A976" s="6" t="s">
-        <v>2469</v>
+        <v>2489</v>
       </c>
       <c r="B976" s="7" t="s">
-        <v>2470</v>
+        <v>2490</v>
       </c>
       <c r="C976" s="7" t="s">
         <v>431</v>
@@ -71225,7 +71285,7 @@
         <v>1986</v>
       </c>
       <c r="B980" s="7" t="s">
-        <v>2471</v>
+        <v>2491</v>
       </c>
       <c r="C980" s="7" t="s">
         <v>28</v>
@@ -71264,7 +71324,7 @@
         <v>12.7768650489863</v>
       </c>
       <c r="O980" s="7" t="s">
-        <v>2472</v>
+        <v>2492</v>
       </c>
       <c r="P980" s="9">
         <v>71.59090909090908</v>
@@ -71426,10 +71486,10 @@
     </row>
     <row r="983" spans="1:22">
       <c r="A983" s="6" t="s">
-        <v>2473</v>
+        <v>2493</v>
       </c>
       <c r="B983" s="7" t="s">
-        <v>2474</v>
+        <v>2494</v>
       </c>
       <c r="C983" s="7" t="s">
         <v>431</v>
@@ -71497,7 +71557,7 @@
         <v>1429</v>
       </c>
       <c r="B984" s="7" t="s">
-        <v>2475</v>
+        <v>2495</v>
       </c>
       <c r="C984" s="7" t="s">
         <v>28</v>
@@ -71740,7 +71800,7 @@
         <v>24.41986345619947</v>
       </c>
       <c r="O987" s="7" t="s">
-        <v>2476</v>
+        <v>2496</v>
       </c>
       <c r="P987" s="9">
         <v>22.48766554141781</v>
@@ -71766,10 +71826,10 @@
     </row>
     <row r="988" spans="1:22">
       <c r="A988" s="6" t="s">
-        <v>2477</v>
+        <v>2497</v>
       </c>
       <c r="B988" s="7" t="s">
-        <v>2478</v>
+        <v>2498</v>
       </c>
       <c r="C988" s="7" t="s">
         <v>28</v>
@@ -71802,13 +71862,13 @@
         <v>5.4</v>
       </c>
       <c r="M988" s="7" t="s">
-        <v>2479</v>
+        <v>2499</v>
       </c>
       <c r="N988" s="9">
         <v>18.86635609511109</v>
       </c>
       <c r="O988" s="7" t="s">
-        <v>2480</v>
+        <v>2500</v>
       </c>
       <c r="P988" s="9">
         <v>128.5714285714286</v>
@@ -71834,10 +71894,10 @@
     </row>
     <row r="989" spans="1:22">
       <c r="A989" s="6" t="s">
-        <v>2481</v>
+        <v>2501</v>
       </c>
       <c r="B989" s="7" t="s">
-        <v>2482</v>
+        <v>2502</v>
       </c>
       <c r="C989" s="7" t="s">
         <v>28</v>
@@ -71876,7 +71936,7 @@
         <v>49.53504632057333</v>
       </c>
       <c r="O989" s="7" t="s">
-        <v>2483</v>
+        <v>2503</v>
       </c>
       <c r="P989" s="9">
         <v>17617.64705882353</v>
@@ -71970,10 +72030,10 @@
     </row>
     <row r="991" spans="1:22">
       <c r="A991" s="6" t="s">
-        <v>2484</v>
+        <v>2504</v>
       </c>
       <c r="B991" s="7" t="s">
-        <v>2485</v>
+        <v>2505</v>
       </c>
       <c r="C991" s="7" t="s">
         <v>431</v>
@@ -72174,10 +72234,10 @@
     </row>
     <row r="994" spans="1:22">
       <c r="A994" s="6" t="s">
-        <v>2486</v>
+        <v>2506</v>
       </c>
       <c r="B994" s="7" t="s">
-        <v>2487</v>
+        <v>2507</v>
       </c>
       <c r="C994" s="7" t="s">
         <v>28</v>
@@ -72210,7 +72270,7 @@
         <v>11</v>
       </c>
       <c r="M994" s="7" t="s">
-        <v>2488</v>
+        <v>2508</v>
       </c>
       <c r="N994" s="9">
         <v>35.82748302678579</v>
@@ -72310,10 +72370,10 @@
     </row>
     <row r="996" spans="1:22">
       <c r="A996" s="6" t="s">
-        <v>2489</v>
+        <v>2509</v>
       </c>
       <c r="B996" s="7" t="s">
-        <v>2490</v>
+        <v>2510</v>
       </c>
       <c r="C996" s="7" t="s">
         <v>28</v>
